--- a/Monadisk overblik.xlsx
+++ b/Monadisk overblik.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aaudk-my.sharepoint.com/personal/bo62rk_id_aau_dk/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="8_{6C2A7B69-2C62-4B80-ACF4-E8008D3DDFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E314C1B3-A014-4992-A383-C151BC79410C}"/>
+  <xr:revisionPtr revIDLastSave="696" documentId="8_{6C2A7B69-2C62-4B80-ACF4-E8008D3DDFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F5DC8B6-555F-44DA-A855-8DE81DEEF8FE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E14E365F-4887-4C07-BAAD-AE51F23AD0DA}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{E14E365F-4887-4C07-BAAD-AE51F23AD0DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="364">
   <si>
     <t>Corona0</t>
   </si>
@@ -239,9 +240,6 @@
     <t>Politisk tillid</t>
   </si>
   <si>
-    <t>Grundlæggende tryghed</t>
-  </si>
-  <si>
     <t>Tryghed efter mørkets frembrud</t>
   </si>
   <si>
@@ -315,13 +313,832 @@
   </si>
   <si>
     <t>At unge drikker meget</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>sp1_01B</t>
+  </si>
+  <si>
+    <t>sp1_02B</t>
+  </si>
+  <si>
+    <t>sp1_03B</t>
+  </si>
+  <si>
+    <t>sp1_04B</t>
+  </si>
+  <si>
+    <t>sp1_05B</t>
+  </si>
+  <si>
+    <t>sp1_06B</t>
+  </si>
+  <si>
+    <t>sp1_07B</t>
+  </si>
+  <si>
+    <t>sp1_08B</t>
+  </si>
+  <si>
+    <t>sp1_09B</t>
+  </si>
+  <si>
+    <t>sp1_10B</t>
+  </si>
+  <si>
+    <t>sp1_11B</t>
+  </si>
+  <si>
+    <t>sp1_12B</t>
+  </si>
+  <si>
+    <t>sp1_13B</t>
+  </si>
+  <si>
+    <t>sp1_14B</t>
+  </si>
+  <si>
+    <t>Q34_1</t>
+  </si>
+  <si>
+    <t>Q34_2</t>
+  </si>
+  <si>
+    <t>Q34_3</t>
+  </si>
+  <si>
+    <t>Q34_4</t>
+  </si>
+  <si>
+    <t>Q34_5</t>
+  </si>
+  <si>
+    <t>Q34_6</t>
+  </si>
+  <si>
+    <t>Q34_7</t>
+  </si>
+  <si>
+    <t>Q34_8</t>
+  </si>
+  <si>
+    <t>Q34_9</t>
+  </si>
+  <si>
+    <t>Q34_10</t>
+  </si>
+  <si>
+    <t>Q34_11</t>
+  </si>
+  <si>
+    <t>Q34_12</t>
+  </si>
+  <si>
+    <t>Q34_13</t>
+  </si>
+  <si>
+    <t>Q34_14</t>
+  </si>
+  <si>
+    <t>S09_Q45_1</t>
+  </si>
+  <si>
+    <t>S09_Q45_2</t>
+  </si>
+  <si>
+    <t>S09_Q45_3</t>
+  </si>
+  <si>
+    <t>S09_Q45_4</t>
+  </si>
+  <si>
+    <t>S09_Q45_5</t>
+  </si>
+  <si>
+    <t>S09_Q45_6</t>
+  </si>
+  <si>
+    <t>S09_Q45_7</t>
+  </si>
+  <si>
+    <t>S09_Q45_8</t>
+  </si>
+  <si>
+    <t>S09_Q45_9</t>
+  </si>
+  <si>
+    <t>S09_Q45_10</t>
+  </si>
+  <si>
+    <t>S09_Q45_11</t>
+  </si>
+  <si>
+    <t>S09_Q45_12</t>
+  </si>
+  <si>
+    <t>S09_Q45_13</t>
+  </si>
+  <si>
+    <t>S09_Q45_14</t>
+  </si>
+  <si>
+    <t>Den globale opvarmning</t>
+  </si>
+  <si>
+    <t>S09_Q45_15</t>
+  </si>
+  <si>
+    <t>q38_1</t>
+  </si>
+  <si>
+    <t>q38_2</t>
+  </si>
+  <si>
+    <t>q38_3</t>
+  </si>
+  <si>
+    <t>q38_4</t>
+  </si>
+  <si>
+    <t>q38_5</t>
+  </si>
+  <si>
+    <t>q38_6</t>
+  </si>
+  <si>
+    <t>q38_7</t>
+  </si>
+  <si>
+    <t>q38_8</t>
+  </si>
+  <si>
+    <t>q38_9</t>
+  </si>
+  <si>
+    <t>q38_10</t>
+  </si>
+  <si>
+    <t>q38_11</t>
+  </si>
+  <si>
+    <t>q38_12</t>
+  </si>
+  <si>
+    <t>q38_13</t>
+  </si>
+  <si>
+    <t>q38_14</t>
+  </si>
+  <si>
+    <t>q38_15</t>
+  </si>
+  <si>
+    <t>q28_1</t>
+  </si>
+  <si>
+    <t>q28_2</t>
+  </si>
+  <si>
+    <t>q28_5</t>
+  </si>
+  <si>
+    <t>q28_6</t>
+  </si>
+  <si>
+    <t>q28_7</t>
+  </si>
+  <si>
+    <t>q28_8</t>
+  </si>
+  <si>
+    <t>q28_9</t>
+  </si>
+  <si>
+    <t>q28_10</t>
+  </si>
+  <si>
+    <t>q28_11</t>
+  </si>
+  <si>
+    <t>q28_12</t>
+  </si>
+  <si>
+    <t>q28_13</t>
+  </si>
+  <si>
+    <t>q28_14</t>
+  </si>
+  <si>
+    <t>q28_15</t>
+  </si>
+  <si>
+    <t>q28_16</t>
+  </si>
+  <si>
+    <t>q28_17</t>
+  </si>
+  <si>
+    <t>q45_1</t>
+  </si>
+  <si>
+    <t>q45_2</t>
+  </si>
+  <si>
+    <t>q45_5</t>
+  </si>
+  <si>
+    <t>q45_8</t>
+  </si>
+  <si>
+    <t>q45_9</t>
+  </si>
+  <si>
+    <t>q45_10</t>
+  </si>
+  <si>
+    <t>q45_11</t>
+  </si>
+  <si>
+    <t>q45_12</t>
+  </si>
+  <si>
+    <t>q45_13</t>
+  </si>
+  <si>
+    <t>q45_14</t>
+  </si>
+  <si>
+    <t>q45_15</t>
+  </si>
+  <si>
+    <t>q45_16</t>
+  </si>
+  <si>
+    <t>q45_17</t>
+  </si>
+  <si>
+    <t>q45_18</t>
+  </si>
+  <si>
+    <t>q45a_1</t>
+  </si>
+  <si>
+    <t>q45a_2</t>
+  </si>
+  <si>
+    <t>q45a_4</t>
+  </si>
+  <si>
+    <t>q45a_5</t>
+  </si>
+  <si>
+    <t>q45a_7</t>
+  </si>
+  <si>
+    <t>q45a_8</t>
+  </si>
+  <si>
+    <t>q45a_9</t>
+  </si>
+  <si>
+    <t>q45a_10</t>
+  </si>
+  <si>
+    <t>q45a_11</t>
+  </si>
+  <si>
+    <t>q45a_12</t>
+  </si>
+  <si>
+    <t>q45a_13</t>
+  </si>
+  <si>
+    <t>q45a_14</t>
+  </si>
+  <si>
+    <t>q45a_6</t>
+  </si>
+  <si>
+    <t>q45b_1</t>
+  </si>
+  <si>
+    <t>q45_a8</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>GUT3_4</t>
+  </si>
+  <si>
+    <t>GUT3_2</t>
+  </si>
+  <si>
+    <t>GUT3_5</t>
+  </si>
+  <si>
+    <t>GUT3_9</t>
+  </si>
+  <si>
+    <t>GUT3_8</t>
+  </si>
+  <si>
+    <t>GUT3_7</t>
+  </si>
+  <si>
+    <t>GUT3_1</t>
+  </si>
+  <si>
+    <t>Q27_1</t>
+  </si>
+  <si>
+    <t>Q27_2</t>
+  </si>
+  <si>
+    <t>Q27_3</t>
+  </si>
+  <si>
+    <t>Q27_9</t>
+  </si>
+  <si>
+    <t>Q27_10</t>
+  </si>
+  <si>
+    <t>Q27_11</t>
+  </si>
+  <si>
+    <t>Q27_17</t>
+  </si>
+  <si>
+    <t>S09_Q25_1</t>
+  </si>
+  <si>
+    <t>S09_Q25_2</t>
+  </si>
+  <si>
+    <t>S09_Q25_3</t>
+  </si>
+  <si>
+    <t>S09_Q25_8</t>
+  </si>
+  <si>
+    <t>S09_Q25_9</t>
+  </si>
+  <si>
+    <t>S09_Q25_10</t>
+  </si>
+  <si>
+    <t>S09_Q25_13</t>
+  </si>
+  <si>
+    <t>For ikke at have helbred til at kunne klare et arbejde</t>
+  </si>
+  <si>
+    <t>For at miste penge på min bolig</t>
+  </si>
+  <si>
+    <t>For at klimaproblemerne kommer ud af kontrol</t>
+  </si>
+  <si>
+    <t>For ikke at få tilstrækkelig pleje, når jeg bliver gammel</t>
+  </si>
+  <si>
+    <t>For ikke at have penge nok, når jeg holder op med at arbejde</t>
+  </si>
+  <si>
+    <t>For ikke at kunne forlade arbejdsmarkedet på en værdig måde, når den tid kommer</t>
+  </si>
+  <si>
+    <t>For ikke at kunne finde et arbejde, når jeg er færdig med min uddannelse</t>
+  </si>
+  <si>
+    <t>For at blive udsat for et seksuelt overgreb</t>
+  </si>
+  <si>
+    <t>For at jobs, som passer til mig, bliver overtaget af østeuropæere</t>
+  </si>
+  <si>
+    <t>For at familien økonomi trues af dårligt helbred</t>
+  </si>
+  <si>
+    <t>S09_Q25_14</t>
+  </si>
+  <si>
+    <t>S09_q25_15</t>
+  </si>
+  <si>
+    <t>S09_Q25_17</t>
+  </si>
+  <si>
+    <t>S09_Q25_20</t>
+  </si>
+  <si>
+    <t>For ikke at få den tilstrækkelige behandling, hvis jeg bliver syg</t>
+  </si>
+  <si>
+    <t>S09_Q25_19</t>
+  </si>
+  <si>
+    <t>S09_Q25_21</t>
+  </si>
+  <si>
+    <t>q25_1</t>
+  </si>
+  <si>
+    <t>q25_2</t>
+  </si>
+  <si>
+    <t>q25_3</t>
+  </si>
+  <si>
+    <t>q25_8</t>
+  </si>
+  <si>
+    <t>q25_9</t>
+  </si>
+  <si>
+    <t>q25_10</t>
+  </si>
+  <si>
+    <t>q25_12</t>
+  </si>
+  <si>
+    <t>q25_13</t>
+  </si>
+  <si>
+    <t>q25_14</t>
+  </si>
+  <si>
+    <t>q25_16</t>
+  </si>
+  <si>
+    <t>q25_18</t>
+  </si>
+  <si>
+    <t>q25_19</t>
+  </si>
+  <si>
+    <t>q25_20</t>
+  </si>
+  <si>
+    <t>q24_1</t>
+  </si>
+  <si>
+    <t>q24_2</t>
+  </si>
+  <si>
+    <t>q24_3</t>
+  </si>
+  <si>
+    <t>q24_7</t>
+  </si>
+  <si>
+    <t>q24_8</t>
+  </si>
+  <si>
+    <t>q24_9</t>
+  </si>
+  <si>
+    <t>q24_11</t>
+  </si>
+  <si>
+    <t>q24_12</t>
+  </si>
+  <si>
+    <t>q24_13</t>
+  </si>
+  <si>
+    <t>q24_15</t>
+  </si>
+  <si>
+    <t>q24_16</t>
+  </si>
+  <si>
+    <t>q24_17</t>
+  </si>
+  <si>
+    <t>q24_18</t>
+  </si>
+  <si>
+    <t>q24_20</t>
+  </si>
+  <si>
+    <t>q24_25</t>
+  </si>
+  <si>
+    <t>q35_1</t>
+  </si>
+  <si>
+    <t>q35_2</t>
+  </si>
+  <si>
+    <t>q35_3</t>
+  </si>
+  <si>
+    <t>q35_5</t>
+  </si>
+  <si>
+    <t>q35_6</t>
+  </si>
+  <si>
+    <t>q35_7</t>
+  </si>
+  <si>
+    <t>q35_8</t>
+  </si>
+  <si>
+    <t>q35_9</t>
+  </si>
+  <si>
+    <t>q35_11</t>
+  </si>
+  <si>
+    <t>q35_13</t>
+  </si>
+  <si>
+    <t>q35_14</t>
+  </si>
+  <si>
+    <t>q35_15</t>
+  </si>
+  <si>
+    <t>q35_16</t>
+  </si>
+  <si>
+    <t>q35_17</t>
+  </si>
+  <si>
+    <t>q35_18</t>
+  </si>
+  <si>
+    <t>q35_22</t>
+  </si>
+  <si>
+    <t>q35_23</t>
+  </si>
+  <si>
+    <t>q35_10</t>
+  </si>
+  <si>
+    <t>q35_4</t>
+  </si>
+  <si>
+    <t>q35_12</t>
+  </si>
+  <si>
+    <t>GUT3_3</t>
+  </si>
+  <si>
+    <t>GUT3_6</t>
+  </si>
+  <si>
+    <t>GUT3_10</t>
+  </si>
+  <si>
+    <t>Q27_5</t>
+  </si>
+  <si>
+    <t>Q27_8</t>
+  </si>
+  <si>
+    <t>Q27_16</t>
+  </si>
+  <si>
+    <t>S09_Q25_4</t>
+  </si>
+  <si>
+    <t>S09_Q25_12</t>
+  </si>
+  <si>
+    <t>q25_4</t>
+  </si>
+  <si>
+    <t>q25_7</t>
+  </si>
+  <si>
+    <t>q25_11</t>
+  </si>
+  <si>
+    <t>q24_4</t>
+  </si>
+  <si>
+    <t>q24_6</t>
+  </si>
+  <si>
+    <t>q24_10</t>
+  </si>
+  <si>
+    <t>q35_32</t>
+  </si>
+  <si>
+    <t>q35_31</t>
+  </si>
+  <si>
+    <t>q35_30</t>
+  </si>
+  <si>
+    <t>q30</t>
+  </si>
+  <si>
+    <t>S05_ØB4</t>
+  </si>
+  <si>
+    <t>S05_ØB5</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Grundlæggende tryghed (GUT)</t>
+  </si>
+  <si>
+    <t>Q25</t>
+  </si>
+  <si>
+    <t>Q26</t>
+  </si>
+  <si>
+    <t>S07_Q20</t>
+  </si>
+  <si>
+    <t>Q50</t>
+  </si>
+  <si>
+    <t>S09_Q1</t>
+  </si>
+  <si>
+    <t>S09_Q2</t>
+  </si>
+  <si>
+    <t>S09_Q23</t>
+  </si>
+  <si>
+    <t>S09_Q24</t>
+  </si>
+  <si>
+    <t>S09_Q50</t>
+  </si>
+  <si>
+    <t>q23</t>
+  </si>
+  <si>
+    <t>q24</t>
+  </si>
+  <si>
+    <t>q21</t>
+  </si>
+  <si>
+    <t>q22</t>
+  </si>
+  <si>
+    <t>q13</t>
+  </si>
+  <si>
+    <t>q57</t>
+  </si>
+  <si>
+    <t>q33</t>
+  </si>
+  <si>
+    <t>q34</t>
+  </si>
+  <si>
+    <t>q25</t>
+  </si>
+  <si>
+    <t>q16</t>
+  </si>
+  <si>
+    <t>q18</t>
+  </si>
+  <si>
+    <t>S09_Q59</t>
+  </si>
+  <si>
+    <t>q28</t>
+  </si>
+  <si>
+    <t>q17</t>
+  </si>
+  <si>
+    <t>q29</t>
+  </si>
+  <si>
+    <t>MANKANIALMINDELIGHEDSTOLEPATVORE</t>
+  </si>
+  <si>
+    <t>q59_1</t>
+  </si>
+  <si>
+    <t>Q30_2</t>
+  </si>
+  <si>
+    <t>S09_Q27_2</t>
+  </si>
+  <si>
+    <t>q27_2</t>
+  </si>
+  <si>
+    <t>q19</t>
+  </si>
+  <si>
+    <t>q31</t>
+  </si>
+  <si>
+    <t>q59_4</t>
+  </si>
+  <si>
+    <t>HVADERDITKN</t>
+  </si>
+  <si>
+    <t>HVADERDINALDER</t>
+  </si>
+  <si>
+    <t>HVADERDINHJESTGENNEMFRTEUDDANNELSE</t>
+  </si>
+  <si>
+    <t>HVADERHUSSTANDENSSAMLEDEBRUTTOINDKOMSTER</t>
+  </si>
+  <si>
+    <t>HVADSTEMTEDUPVEDFOLKETINGSVALGETDEN5</t>
+  </si>
+  <si>
+    <t>HVILENAFFLGENDECIVILSTATUSBESKRIVELSERP</t>
+  </si>
+  <si>
+    <t>HVORDANSYNESDUDITHELBREDERALTIALT</t>
+  </si>
+  <si>
+    <t>PENSKALAFRA1TIL7HVOR1ERJEGFLER</t>
+  </si>
+  <si>
+    <t>profile_education</t>
+  </si>
+  <si>
+    <t>q10</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>urban</t>
+  </si>
+  <si>
+    <t>q14a_1</t>
+  </si>
+  <si>
+    <t>q14a_2</t>
+  </si>
+  <si>
+    <t>q14a_5</t>
+  </si>
+  <si>
+    <t>q14a_6</t>
+  </si>
+  <si>
+    <t>q15</t>
+  </si>
+  <si>
+    <t>q27</t>
+  </si>
+  <si>
+    <t>At der ikke bliver penge nok til de mange ældre</t>
+  </si>
+  <si>
+    <t>q45a_3</t>
+  </si>
+  <si>
+    <t>At Rusland truer sine naboer</t>
+  </si>
+  <si>
+    <t>At samarbejdet i EU ikke fungere</t>
+  </si>
+  <si>
+    <t>At børn og unge trives dårligt</t>
+  </si>
+  <si>
+    <t>q45a_16</t>
+  </si>
+  <si>
+    <t>At Kina med tiden kommer til at dominere hele verden</t>
+  </si>
+  <si>
+    <t>q45a_17</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,6 +1151,12 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -399,6 +1222,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -718,11 +1545,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDCC2279-7CC5-471A-AC30-1F8A606C7178}">
-  <dimension ref="A1:AO53"/>
+  <dimension ref="A1:AO70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="65.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -865,36 +1693,144 @@
       <c r="A2" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="B2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L2" t="s">
+        <v>303</v>
+      </c>
+      <c r="M2" t="s">
+        <v>310</v>
+      </c>
+      <c r="O2" t="s">
+        <v>91</v>
+      </c>
+      <c r="P2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>91</v>
+      </c>
+      <c r="R2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S2" t="s">
+        <v>91</v>
+      </c>
+      <c r="U2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V2" t="s">
+        <v>91</v>
+      </c>
+      <c r="W2" t="s">
+        <v>91</v>
+      </c>
+      <c r="X2" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="B3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" t="s">
+        <v>304</v>
+      </c>
+      <c r="M3" t="s">
+        <v>311</v>
+      </c>
+      <c r="O3" t="s">
+        <v>92</v>
+      </c>
+      <c r="P3" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>92</v>
+      </c>
+      <c r="R3" t="s">
+        <v>92</v>
+      </c>
+      <c r="S3" t="s">
+        <v>92</v>
+      </c>
+      <c r="U3" t="s">
+        <v>92</v>
+      </c>
+      <c r="V3" t="s">
+        <v>92</v>
+      </c>
+      <c r="W3" t="s">
+        <v>92</v>
+      </c>
+      <c r="X3" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="B4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C4" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="C5" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="B6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C6" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="C7" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="C8" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -905,223 +1841,1932 @@
       <c r="A10" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="B10" t="s">
+        <v>341</v>
+      </c>
+      <c r="C10" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="B11" t="s">
+        <v>342</v>
+      </c>
+      <c r="C11" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="C12" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="B13" t="s">
+        <v>344</v>
+      </c>
+      <c r="C13" t="s">
+        <v>323</v>
+      </c>
+      <c r="K13" t="s">
+        <v>302</v>
+      </c>
+      <c r="L13" t="s">
+        <v>309</v>
+      </c>
+      <c r="M13" t="s">
+        <v>314</v>
+      </c>
+      <c r="O13" t="s">
+        <v>320</v>
+      </c>
+      <c r="P13" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>323</v>
+      </c>
+      <c r="R13" t="s">
+        <v>323</v>
+      </c>
+      <c r="S13" t="s">
+        <v>323</v>
+      </c>
+      <c r="U13" t="s">
+        <v>323</v>
+      </c>
+      <c r="V13" t="s">
+        <v>323</v>
+      </c>
+      <c r="W13" t="s">
+        <v>323</v>
+      </c>
+      <c r="X13" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="C14" t="s">
+        <v>300</v>
+      </c>
+      <c r="D14" t="s">
+        <v>300</v>
+      </c>
+      <c r="F14" t="s">
+        <v>300</v>
+      </c>
+      <c r="G14" t="s">
+        <v>300</v>
+      </c>
+      <c r="K14" t="s">
+        <v>301</v>
+      </c>
+      <c r="L14" t="s">
+        <v>308</v>
+      </c>
+      <c r="O14" t="s">
+        <v>324</v>
+      </c>
+      <c r="P14" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>300</v>
+      </c>
+      <c r="R14" t="s">
+        <v>300</v>
+      </c>
+      <c r="S14" t="s">
+        <v>300</v>
+      </c>
+      <c r="U14" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="C15" t="s">
+        <v>329</v>
+      </c>
+      <c r="D15" t="s">
+        <v>329</v>
+      </c>
+      <c r="M15" t="s">
+        <v>326</v>
+      </c>
+      <c r="O15" t="s">
+        <v>327</v>
+      </c>
+      <c r="P15" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>329</v>
+      </c>
+      <c r="R15" t="s">
+        <v>329</v>
+      </c>
+      <c r="S15" t="s">
+        <v>329</v>
+      </c>
+      <c r="U15" t="s">
+        <v>329</v>
+      </c>
+      <c r="W15" t="s">
+        <v>329</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>329</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>330</v>
+      </c>
+      <c r="F26" t="s">
+        <v>331</v>
+      </c>
+      <c r="G26" t="s">
+        <v>331</v>
+      </c>
+      <c r="L26" t="s">
+        <v>332</v>
+      </c>
+      <c r="M26" t="s">
+        <v>333</v>
+      </c>
+      <c r="O26" t="s">
+        <v>334</v>
+      </c>
+      <c r="P26" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>336</v>
+      </c>
+      <c r="R26" t="s">
+        <v>337</v>
+      </c>
+      <c r="S26" t="s">
+        <v>331</v>
+      </c>
+      <c r="U26" t="s">
+        <v>337</v>
+      </c>
+      <c r="X26" t="s">
+        <v>331</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>331</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B28" t="s">
+        <v>345</v>
+      </c>
+      <c r="C28" t="s">
+        <v>321</v>
+      </c>
+      <c r="L28" t="s">
+        <v>306</v>
+      </c>
+      <c r="M28" t="s">
+        <v>312</v>
+      </c>
+      <c r="O28" t="s">
+        <v>315</v>
+      </c>
+      <c r="P28" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>321</v>
+      </c>
+      <c r="R28" t="s">
+        <v>321</v>
+      </c>
+      <c r="S28" t="s">
+        <v>321</v>
+      </c>
+      <c r="U28" t="s">
+        <v>321</v>
+      </c>
+      <c r="V28" t="s">
+        <v>321</v>
+      </c>
+      <c r="W28" t="s">
+        <v>321</v>
+      </c>
+      <c r="X28" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="L29" t="s">
+        <v>307</v>
+      </c>
+      <c r="M29" t="s">
+        <v>313</v>
+      </c>
+      <c r="O29" t="s">
+        <v>316</v>
+      </c>
+      <c r="P29" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>322</v>
+      </c>
+      <c r="R29" t="s">
+        <v>322</v>
+      </c>
+      <c r="S29" t="s">
+        <v>322</v>
+      </c>
+      <c r="U29" t="s">
+        <v>322</v>
+      </c>
+      <c r="V29" t="s">
+        <v>322</v>
+      </c>
+      <c r="W29" t="s">
+        <v>322</v>
+      </c>
+      <c r="X29" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" t="s">
+        <v>268</v>
+      </c>
+      <c r="K30" t="s">
+        <v>203</v>
+      </c>
+      <c r="L30" t="s">
+        <v>210</v>
+      </c>
+      <c r="M30" t="s">
+        <v>217</v>
+      </c>
+      <c r="O30" t="s">
+        <v>241</v>
+      </c>
+      <c r="P30" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>269</v>
+      </c>
+      <c r="R30" t="s">
+        <v>268</v>
+      </c>
+      <c r="S30" t="s">
+        <v>268</v>
+      </c>
+      <c r="U30" t="s">
+        <v>268</v>
+      </c>
+      <c r="V30" t="s">
+        <v>268</v>
+      </c>
+      <c r="W30" t="s">
+        <v>196</v>
+      </c>
+      <c r="X30" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" t="s">
+        <v>264</v>
+      </c>
+      <c r="K31" t="s">
+        <v>198</v>
+      </c>
+      <c r="L31" t="s">
+        <v>205</v>
+      </c>
+      <c r="M31" t="s">
+        <v>212</v>
+      </c>
+      <c r="O31" t="s">
+        <v>236</v>
+      </c>
+      <c r="P31" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>264</v>
+      </c>
+      <c r="R31" t="s">
+        <v>264</v>
+      </c>
+      <c r="S31" t="s">
+        <v>264</v>
+      </c>
+      <c r="U31" t="s">
+        <v>264</v>
+      </c>
+      <c r="V31" t="s">
+        <v>264</v>
+      </c>
+      <c r="W31" t="s">
+        <v>196</v>
+      </c>
+      <c r="X31" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K32" t="s">
+        <v>283</v>
+      </c>
+      <c r="L32" t="s">
+        <v>286</v>
+      </c>
+      <c r="M32" t="s">
+        <v>289</v>
+      </c>
+      <c r="O32" t="s">
+        <v>291</v>
+      </c>
+      <c r="P32" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>196</v>
+      </c>
+      <c r="R32" t="s">
+        <v>196</v>
+      </c>
+      <c r="U32" t="s">
+        <v>196</v>
+      </c>
+      <c r="V32" t="s">
+        <v>196</v>
+      </c>
+      <c r="W32" t="s">
+        <v>196</v>
+      </c>
+      <c r="X32" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="C33" t="s">
+        <v>263</v>
+      </c>
+      <c r="K33" t="s">
+        <v>197</v>
+      </c>
+      <c r="L33" t="s">
+        <v>204</v>
+      </c>
+      <c r="M33" t="s">
+        <v>211</v>
+      </c>
+      <c r="O33" t="s">
+        <v>235</v>
+      </c>
+      <c r="P33" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>263</v>
+      </c>
+      <c r="R33" t="s">
+        <v>263</v>
+      </c>
+      <c r="S33" t="s">
+        <v>263</v>
+      </c>
+      <c r="U33" t="s">
+        <v>263</v>
+      </c>
+      <c r="V33" t="s">
+        <v>263</v>
+      </c>
+      <c r="W33" t="s">
+        <v>263</v>
+      </c>
+      <c r="X33" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
+        <v>265</v>
+      </c>
+      <c r="K34" t="s">
+        <v>199</v>
+      </c>
+      <c r="L34" t="s">
+        <v>206</v>
+      </c>
+      <c r="M34" t="s">
+        <v>213</v>
+      </c>
+      <c r="O34" t="s">
+        <v>237</v>
+      </c>
+      <c r="P34" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>265</v>
+      </c>
+      <c r="R34" t="s">
+        <v>265</v>
+      </c>
+      <c r="S34" t="s">
+        <v>265</v>
+      </c>
+      <c r="U34" t="s">
+        <v>265</v>
+      </c>
+      <c r="V34" t="s">
+        <v>265</v>
+      </c>
+      <c r="W34" t="s">
+        <v>265</v>
+      </c>
+      <c r="X34" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="K35" t="s">
+        <v>284</v>
+      </c>
+      <c r="L35" t="s">
+        <v>287</v>
+      </c>
+      <c r="M35" t="s">
+        <v>290</v>
+      </c>
+      <c r="O35" t="s">
+        <v>292</v>
+      </c>
+      <c r="P35" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>281</v>
+      </c>
+      <c r="R35" t="s">
+        <v>196</v>
+      </c>
+      <c r="U35" t="s">
+        <v>196</v>
+      </c>
+      <c r="V35" t="s">
+        <v>196</v>
+      </c>
+      <c r="W35" t="s">
+        <v>196</v>
+      </c>
+      <c r="X35" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="C36" t="s">
+        <v>267</v>
+      </c>
+      <c r="K36" t="s">
+        <v>202</v>
+      </c>
+      <c r="L36" t="s">
+        <v>209</v>
+      </c>
+      <c r="M36" t="s">
+        <v>216</v>
+      </c>
+      <c r="O36" t="s">
+        <v>240</v>
+      </c>
+      <c r="P36" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>268</v>
+      </c>
+      <c r="R36" t="s">
+        <v>267</v>
+      </c>
+      <c r="S36" t="s">
+        <v>267</v>
+      </c>
+      <c r="U36" t="s">
+        <v>267</v>
+      </c>
+      <c r="V36" t="s">
+        <v>267</v>
+      </c>
+      <c r="W36" t="s">
+        <v>196</v>
+      </c>
+      <c r="X36" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="C37" t="s">
+        <v>266</v>
+      </c>
+      <c r="K37" t="s">
+        <v>201</v>
+      </c>
+      <c r="L37" t="s">
+        <v>208</v>
+      </c>
+      <c r="M37" t="s">
+        <v>215</v>
+      </c>
+      <c r="O37" t="s">
+        <v>239</v>
+      </c>
+      <c r="P37" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>267</v>
+      </c>
+      <c r="R37" t="s">
+        <v>266</v>
+      </c>
+      <c r="S37" t="s">
+        <v>266</v>
+      </c>
+      <c r="U37" t="s">
+        <v>266</v>
+      </c>
+      <c r="V37" t="s">
+        <v>266</v>
+      </c>
+      <c r="W37" t="s">
+        <v>196</v>
+      </c>
+      <c r="X37" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="C38" t="s">
+        <v>281</v>
+      </c>
+      <c r="K38" t="s">
+        <v>200</v>
+      </c>
+      <c r="L38" t="s">
+        <v>207</v>
+      </c>
+      <c r="M38" t="s">
+        <v>214</v>
+      </c>
+      <c r="O38" t="s">
+        <v>238</v>
+      </c>
+      <c r="P38" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>266</v>
+      </c>
+      <c r="R38" t="s">
+        <v>281</v>
+      </c>
+      <c r="S38" t="s">
+        <v>281</v>
+      </c>
+      <c r="U38" t="s">
+        <v>281</v>
+      </c>
+      <c r="V38" t="s">
+        <v>281</v>
+      </c>
+      <c r="W38" t="s">
+        <v>196</v>
+      </c>
+      <c r="X38" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+      <c r="K39" t="s">
+        <v>285</v>
+      </c>
+      <c r="L39" t="s">
+        <v>288</v>
+      </c>
+      <c r="M39" t="s">
+        <v>290</v>
+      </c>
+      <c r="O39" t="s">
+        <v>293</v>
+      </c>
+      <c r="P39" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>196</v>
+      </c>
+      <c r="R39" t="s">
+        <v>196</v>
+      </c>
+      <c r="U39" t="s">
+        <v>196</v>
+      </c>
+      <c r="V39" t="s">
+        <v>196</v>
+      </c>
+      <c r="W39" t="s">
+        <v>196</v>
+      </c>
+      <c r="X39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C40" t="s">
+        <v>269</v>
+      </c>
+      <c r="K40" t="s">
+        <v>196</v>
+      </c>
+      <c r="L40" t="s">
+        <v>196</v>
+      </c>
+      <c r="M40" t="s">
+        <v>228</v>
+      </c>
+      <c r="O40" t="s">
+        <v>242</v>
+      </c>
+      <c r="P40" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>270</v>
+      </c>
+      <c r="R40" t="s">
+        <v>269</v>
+      </c>
+      <c r="S40" t="s">
+        <v>269</v>
+      </c>
+      <c r="U40" t="s">
+        <v>269</v>
+      </c>
+      <c r="V40" t="s">
+        <v>269</v>
+      </c>
+      <c r="W40" t="s">
+        <v>196</v>
+      </c>
+      <c r="X40" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C41" t="s">
+        <v>280</v>
+      </c>
+      <c r="K41" t="s">
+        <v>196</v>
+      </c>
+      <c r="L41" t="s">
+        <v>196</v>
+      </c>
+      <c r="M41" t="s">
+        <v>229</v>
+      </c>
+      <c r="O41" t="s">
+        <v>243</v>
+      </c>
+      <c r="P41" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>271</v>
+      </c>
+      <c r="R41" t="s">
+        <v>280</v>
+      </c>
+      <c r="U41" t="s">
+        <v>196</v>
+      </c>
+      <c r="V41" t="s">
+        <v>297</v>
+      </c>
+      <c r="W41" t="s">
+        <v>196</v>
+      </c>
+      <c r="X41" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="K42" t="s">
+        <v>196</v>
+      </c>
+      <c r="L42" t="s">
+        <v>196</v>
+      </c>
+      <c r="M42" t="s">
+        <v>230</v>
+      </c>
+      <c r="O42" t="s">
+        <v>244</v>
+      </c>
+      <c r="P42" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>272</v>
+      </c>
+      <c r="R42" t="s">
+        <v>196</v>
+      </c>
+      <c r="U42" t="s">
+        <v>196</v>
+      </c>
+      <c r="V42" t="s">
+        <v>298</v>
+      </c>
+      <c r="W42" t="s">
+        <v>196</v>
+      </c>
+      <c r="X42" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="K43" t="s">
+        <v>196</v>
+      </c>
+      <c r="L43" t="s">
+        <v>196</v>
+      </c>
+      <c r="M43" t="s">
+        <v>233</v>
+      </c>
+      <c r="O43" t="s">
+        <v>245</v>
+      </c>
+      <c r="P43" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>273</v>
+      </c>
+      <c r="R43" t="s">
+        <v>196</v>
+      </c>
+      <c r="U43" t="s">
+        <v>196</v>
+      </c>
+      <c r="V43" t="s">
+        <v>299</v>
+      </c>
+      <c r="W43" t="s">
+        <v>299</v>
+      </c>
+      <c r="X43" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C44" t="s">
+        <v>271</v>
+      </c>
+      <c r="K44" t="s">
+        <v>196</v>
+      </c>
+      <c r="L44" t="s">
+        <v>196</v>
+      </c>
+      <c r="M44" t="s">
+        <v>231</v>
+      </c>
+      <c r="O44" t="s">
+        <v>246</v>
+      </c>
+      <c r="P44" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>274</v>
+      </c>
+      <c r="R44" t="s">
+        <v>271</v>
+      </c>
+      <c r="S44" t="s">
+        <v>271</v>
+      </c>
+      <c r="U44" t="s">
+        <v>271</v>
+      </c>
+      <c r="V44" t="s">
+        <v>271</v>
+      </c>
+      <c r="W44" t="s">
+        <v>271</v>
+      </c>
+      <c r="X44" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C45" t="s">
+        <v>282</v>
+      </c>
+      <c r="K45" t="s">
+        <v>196</v>
+      </c>
+      <c r="L45" t="s">
+        <v>196</v>
+      </c>
+      <c r="M45" t="s">
+        <v>234</v>
+      </c>
+      <c r="O45" t="s">
+        <v>247</v>
+      </c>
+      <c r="P45" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>275</v>
+      </c>
+      <c r="R45" t="s">
+        <v>282</v>
+      </c>
+      <c r="S45" t="s">
+        <v>282</v>
+      </c>
+      <c r="U45" t="s">
+        <v>282</v>
+      </c>
+      <c r="V45" t="s">
+        <v>282</v>
+      </c>
+      <c r="W45" t="s">
+        <v>282</v>
+      </c>
+      <c r="X45" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C46" t="s">
+        <v>272</v>
+      </c>
+      <c r="K46" t="s">
+        <v>196</v>
+      </c>
+      <c r="L46" t="s">
+        <v>196</v>
+      </c>
+      <c r="M46" t="s">
+        <v>196</v>
+      </c>
+      <c r="O46" t="s">
+        <v>196</v>
+      </c>
+      <c r="P46" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>276</v>
+      </c>
+      <c r="R46" t="s">
+        <v>272</v>
+      </c>
+      <c r="S46" t="s">
+        <v>272</v>
+      </c>
+      <c r="U46" t="s">
+        <v>272</v>
+      </c>
+      <c r="V46" t="s">
+        <v>272</v>
+      </c>
+      <c r="W46" t="s">
+        <v>196</v>
+      </c>
+      <c r="X46" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C47" t="s">
+        <v>273</v>
+      </c>
+      <c r="K47" t="s">
+        <v>196</v>
+      </c>
+      <c r="L47" t="s">
+        <v>196</v>
+      </c>
+      <c r="M47" t="s">
+        <v>196</v>
+      </c>
+      <c r="O47" t="s">
+        <v>236</v>
+      </c>
+      <c r="P47" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>277</v>
+      </c>
+      <c r="R47" t="s">
+        <v>273</v>
+      </c>
+      <c r="S47" t="s">
+        <v>273</v>
+      </c>
+      <c r="U47" t="s">
+        <v>273</v>
+      </c>
+      <c r="V47" t="s">
+        <v>273</v>
+      </c>
+      <c r="W47" t="s">
+        <v>196</v>
+      </c>
+      <c r="X47" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C48" t="s">
+        <v>276</v>
+      </c>
+      <c r="K48" t="s">
+        <v>196</v>
+      </c>
+      <c r="L48" t="s">
+        <v>196</v>
+      </c>
+      <c r="M48" t="s">
+        <v>196</v>
+      </c>
+      <c r="O48" t="s">
+        <v>196</v>
+      </c>
+      <c r="P48" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>278</v>
+      </c>
+      <c r="R48" t="s">
+        <v>276</v>
+      </c>
+      <c r="S48" t="s">
+        <v>276</v>
+      </c>
+      <c r="U48" t="s">
+        <v>276</v>
+      </c>
+      <c r="V48" t="s">
+        <v>276</v>
+      </c>
+      <c r="W48" t="s">
+        <v>196</v>
+      </c>
+      <c r="X48" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C49" t="s">
+        <v>277</v>
+      </c>
+      <c r="K49" t="s">
+        <v>196</v>
+      </c>
+      <c r="L49" t="s">
+        <v>196</v>
+      </c>
+      <c r="M49" t="s">
+        <v>196</v>
+      </c>
+      <c r="O49" t="s">
+        <v>196</v>
+      </c>
+      <c r="P49" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>279</v>
+      </c>
+      <c r="R49" t="s">
+        <v>277</v>
+      </c>
+      <c r="S49" t="s">
+        <v>277</v>
+      </c>
+      <c r="U49" t="s">
+        <v>277</v>
+      </c>
+      <c r="V49" t="s">
+        <v>196</v>
+      </c>
+      <c r="W49" t="s">
+        <v>196</v>
+      </c>
+      <c r="X49" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C50" t="s">
+        <v>270</v>
+      </c>
+      <c r="K50" t="s">
+        <v>196</v>
+      </c>
+      <c r="L50" t="s">
+        <v>196</v>
+      </c>
+      <c r="M50" t="s">
+        <v>196</v>
+      </c>
+      <c r="O50" t="s">
+        <v>196</v>
+      </c>
+      <c r="P50" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>280</v>
+      </c>
+      <c r="R50" t="s">
+        <v>270</v>
+      </c>
+      <c r="S50" t="s">
+        <v>270</v>
+      </c>
+      <c r="U50" t="s">
+        <v>270</v>
+      </c>
+      <c r="V50" t="s">
+        <v>270</v>
+      </c>
+      <c r="W50" t="s">
+        <v>196</v>
+      </c>
+      <c r="X50" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="C51" t="s">
+        <v>181</v>
+      </c>
+      <c r="K51" t="s">
+        <v>93</v>
+      </c>
+      <c r="L51" t="s">
+        <v>107</v>
+      </c>
+      <c r="M51" t="s">
+        <v>121</v>
+      </c>
+      <c r="O51" t="s">
+        <v>137</v>
+      </c>
+      <c r="P51" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>167</v>
+      </c>
+      <c r="R51" t="s">
+        <v>181</v>
+      </c>
+      <c r="S51" t="s">
+        <v>181</v>
+      </c>
+      <c r="U51" t="s">
+        <v>181</v>
+      </c>
+      <c r="V51" t="s">
+        <v>181</v>
+      </c>
+      <c r="W51" t="s">
+        <v>181</v>
+      </c>
+      <c r="X51" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="K52" t="s">
+        <v>94</v>
+      </c>
+      <c r="L52" t="s">
+        <v>108</v>
+      </c>
+      <c r="M52" t="s">
+        <v>122</v>
+      </c>
+      <c r="O52" t="s">
+        <v>138</v>
+      </c>
+      <c r="P52" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>168</v>
+      </c>
+      <c r="R52" t="s">
+        <v>182</v>
+      </c>
+      <c r="S52" t="s">
+        <v>182</v>
+      </c>
+      <c r="U52" t="s">
+        <v>196</v>
+      </c>
+      <c r="V52" t="s">
+        <v>196</v>
+      </c>
+      <c r="W52" t="s">
+        <v>196</v>
+      </c>
+      <c r="X52" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="C53" t="s">
+        <v>182</v>
+      </c>
+      <c r="K53" t="s">
+        <v>95</v>
+      </c>
+      <c r="L53" t="s">
+        <v>109</v>
+      </c>
+      <c r="M53" t="s">
+        <v>123</v>
+      </c>
+      <c r="O53" t="s">
+        <v>139</v>
+      </c>
+      <c r="P53" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>169</v>
+      </c>
+      <c r="R53" t="s">
+        <v>183</v>
+      </c>
+      <c r="S53" t="s">
+        <v>183</v>
+      </c>
+      <c r="U53" t="s">
+        <v>182</v>
+      </c>
+      <c r="V53" t="s">
+        <v>182</v>
+      </c>
+      <c r="W53" t="s">
+        <v>196</v>
+      </c>
+      <c r="X53" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="K54" t="s">
+        <v>96</v>
+      </c>
+      <c r="L54" t="s">
+        <v>110</v>
+      </c>
+      <c r="M54" t="s">
+        <v>124</v>
+      </c>
+      <c r="O54" t="s">
+        <v>140</v>
+      </c>
+      <c r="P54" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>170</v>
+      </c>
+      <c r="R54" t="s">
+        <v>193</v>
+      </c>
+      <c r="S54" t="s">
+        <v>196</v>
+      </c>
+      <c r="U54" t="s">
+        <v>196</v>
+      </c>
+      <c r="V54" t="s">
+        <v>196</v>
+      </c>
+      <c r="W54" t="s">
+        <v>196</v>
+      </c>
+      <c r="X54" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="C55" t="s">
+        <v>183</v>
+      </c>
+      <c r="K55" t="s">
+        <v>97</v>
+      </c>
+      <c r="L55" t="s">
+        <v>111</v>
+      </c>
+      <c r="M55" t="s">
+        <v>125</v>
+      </c>
+      <c r="O55" t="s">
+        <v>141</v>
+      </c>
+      <c r="P55" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>171</v>
+      </c>
+      <c r="R55" t="s">
+        <v>185</v>
+      </c>
+      <c r="S55" t="s">
+        <v>185</v>
+      </c>
+      <c r="U55" t="s">
+        <v>183</v>
+      </c>
+      <c r="V55" t="s">
+        <v>183</v>
+      </c>
+      <c r="W55" t="s">
+        <v>196</v>
+      </c>
+      <c r="X55" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+      <c r="K56" t="s">
+        <v>98</v>
+      </c>
+      <c r="L56" t="s">
+        <v>112</v>
+      </c>
+      <c r="M56" t="s">
+        <v>126</v>
+      </c>
+      <c r="O56" t="s">
+        <v>142</v>
+      </c>
+      <c r="P56" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>196</v>
+      </c>
+      <c r="R56" t="s">
+        <v>196</v>
+      </c>
+      <c r="S56" t="s">
+        <v>196</v>
+      </c>
+      <c r="U56" t="s">
+        <v>196</v>
+      </c>
+      <c r="V56" t="s">
+        <v>196</v>
+      </c>
+      <c r="W56" t="s">
+        <v>196</v>
+      </c>
+      <c r="X56" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="C57" t="s">
+        <v>184</v>
+      </c>
+      <c r="K57" t="s">
+        <v>99</v>
+      </c>
+      <c r="L57" t="s">
+        <v>113</v>
+      </c>
+      <c r="M57" t="s">
+        <v>127</v>
+      </c>
+      <c r="O57" t="s">
+        <v>143</v>
+      </c>
+      <c r="P57" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>172</v>
+      </c>
+      <c r="R57" t="s">
+        <v>186</v>
+      </c>
+      <c r="S57" t="s">
+        <v>195</v>
+      </c>
+      <c r="U57" t="s">
+        <v>184</v>
+      </c>
+      <c r="V57" t="s">
+        <v>184</v>
+      </c>
+      <c r="W57" t="s">
+        <v>184</v>
+      </c>
+      <c r="X57" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="K58" t="s">
+        <v>100</v>
+      </c>
+      <c r="L58" t="s">
+        <v>114</v>
+      </c>
+      <c r="M58" t="s">
+        <v>128</v>
+      </c>
+      <c r="O58" t="s">
+        <v>144</v>
+      </c>
+      <c r="P58" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>173</v>
+      </c>
+      <c r="R58" t="s">
+        <v>187</v>
+      </c>
+      <c r="S58" t="s">
+        <v>187</v>
+      </c>
+      <c r="U58" t="s">
+        <v>196</v>
+      </c>
+      <c r="V58" t="s">
+        <v>196</v>
+      </c>
+      <c r="W58" t="s">
+        <v>196</v>
+      </c>
+      <c r="X58" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="C59" t="s">
+        <v>193</v>
+      </c>
+      <c r="K59" t="s">
+        <v>101</v>
+      </c>
+      <c r="L59" t="s">
+        <v>115</v>
+      </c>
+      <c r="M59" t="s">
+        <v>129</v>
+      </c>
+      <c r="O59" t="s">
+        <v>145</v>
+      </c>
+      <c r="P59" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>174</v>
+      </c>
+      <c r="R59" t="s">
+        <v>188</v>
+      </c>
+      <c r="S59" t="s">
+        <v>188</v>
+      </c>
+      <c r="U59" t="s">
+        <v>193</v>
+      </c>
+      <c r="V59" t="s">
+        <v>193</v>
+      </c>
+      <c r="W59" t="s">
+        <v>193</v>
+      </c>
+      <c r="X59" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="C60" t="s">
+        <v>185</v>
+      </c>
+      <c r="K60" t="s">
+        <v>102</v>
+      </c>
+      <c r="L60" t="s">
+        <v>116</v>
+      </c>
+      <c r="M60" t="s">
+        <v>130</v>
+      </c>
+      <c r="O60" t="s">
+        <v>146</v>
+      </c>
+      <c r="P60" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>175</v>
+      </c>
+      <c r="R60" t="s">
+        <v>189</v>
+      </c>
+      <c r="S60" t="s">
+        <v>189</v>
+      </c>
+      <c r="U60" t="s">
+        <v>185</v>
+      </c>
+      <c r="V60" t="s">
+        <v>185</v>
+      </c>
+      <c r="W60" t="s">
+        <v>185</v>
+      </c>
+      <c r="X60" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="K61" t="s">
+        <v>103</v>
+      </c>
+      <c r="L61" t="s">
+        <v>117</v>
+      </c>
+      <c r="M61" t="s">
+        <v>131</v>
+      </c>
+      <c r="O61" t="s">
+        <v>147</v>
+      </c>
+      <c r="P61" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>176</v>
+      </c>
+      <c r="R61" t="s">
+        <v>190</v>
+      </c>
+      <c r="S61" t="s">
+        <v>190</v>
+      </c>
+      <c r="U61" t="s">
+        <v>196</v>
+      </c>
+      <c r="V61" t="s">
+        <v>196</v>
+      </c>
+      <c r="W61" t="s">
+        <v>190</v>
+      </c>
+      <c r="X61" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="C62" t="s">
+        <v>186</v>
+      </c>
+      <c r="K62" t="s">
+        <v>104</v>
+      </c>
+      <c r="L62" t="s">
+        <v>118</v>
+      </c>
+      <c r="M62" t="s">
+        <v>132</v>
+      </c>
+      <c r="O62" t="s">
+        <v>148</v>
+      </c>
+      <c r="P62" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>177</v>
+      </c>
+      <c r="R62" t="s">
+        <v>191</v>
+      </c>
+      <c r="S62" t="s">
+        <v>191</v>
+      </c>
+      <c r="U62" t="s">
+        <v>186</v>
+      </c>
+      <c r="V62" t="s">
+        <v>186</v>
+      </c>
+      <c r="W62" t="s">
+        <v>186</v>
+      </c>
+      <c r="X62" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="K63" t="s">
+        <v>105</v>
+      </c>
+      <c r="L63" t="s">
+        <v>119</v>
+      </c>
+      <c r="M63" t="s">
+        <v>133</v>
+      </c>
+      <c r="O63" t="s">
+        <v>149</v>
+      </c>
+      <c r="P63" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>178</v>
+      </c>
+      <c r="R63" t="s">
+        <v>192</v>
+      </c>
+      <c r="S63" t="s">
+        <v>192</v>
+      </c>
+      <c r="U63" t="s">
+        <v>196</v>
+      </c>
+      <c r="V63" t="s">
+        <v>196</v>
+      </c>
+      <c r="W63" t="s">
+        <v>196</v>
+      </c>
+      <c r="X63" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>91</v>
+      <c r="K64" t="s">
+        <v>106</v>
+      </c>
+      <c r="L64" t="s">
+        <v>120</v>
+      </c>
+      <c r="M64" t="s">
+        <v>134</v>
+      </c>
+      <c r="O64" t="s">
+        <v>150</v>
+      </c>
+      <c r="P64" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>179</v>
+      </c>
+      <c r="R64" t="s">
+        <v>196</v>
+      </c>
+      <c r="S64" t="s">
+        <v>196</v>
+      </c>
+      <c r="U64" t="s">
+        <v>196</v>
+      </c>
+      <c r="V64" t="s">
+        <v>196</v>
+      </c>
+      <c r="W64" t="s">
+        <v>196</v>
+      </c>
+      <c r="X64" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C65" t="s">
+        <v>187</v>
+      </c>
+      <c r="K65" t="s">
+        <v>196</v>
+      </c>
+      <c r="L65" t="s">
+        <v>196</v>
+      </c>
+      <c r="M65" t="s">
+        <v>136</v>
+      </c>
+      <c r="O65" t="s">
+        <v>151</v>
+      </c>
+      <c r="P65" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>180</v>
+      </c>
+      <c r="R65" t="s">
+        <v>194</v>
+      </c>
+      <c r="S65" t="s">
+        <v>194</v>
+      </c>
+      <c r="U65" t="s">
+        <v>187</v>
+      </c>
+      <c r="V65" t="s">
+        <v>187</v>
+      </c>
+      <c r="W65" t="s">
+        <v>187</v>
+      </c>
+      <c r="X65" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C66" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C67" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C68" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C69" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C70" t="s">
+        <v>363</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Monadisk overblik.xlsx
+++ b/Monadisk overblik.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aaudk-my.sharepoint.com/personal/bo62rk_id_aau_dk/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="696" documentId="8_{6C2A7B69-2C62-4B80-ACF4-E8008D3DDFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F5DC8B6-555F-44DA-A855-8DE81DEEF8FE}"/>
+  <xr:revisionPtr revIDLastSave="1122" documentId="8_{6C2A7B69-2C62-4B80-ACF4-E8008D3DDFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F17C4624-94B3-4AC8-B807-EB0B5E8C0666}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{E14E365F-4887-4C07-BAAD-AE51F23AD0DA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E14E365F-4887-4C07-BAAD-AE51F23AD0DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="393">
   <si>
     <t>Corona0</t>
   </si>
@@ -1132,6 +1131,93 @@
   </si>
   <si>
     <t>q45a_17</t>
+  </si>
+  <si>
+    <t>q60_4</t>
+  </si>
+  <si>
+    <t>q60_6</t>
+  </si>
+  <si>
+    <t>q60_5</t>
+  </si>
+  <si>
+    <t>q60_2</t>
+  </si>
+  <si>
+    <t>q60_3</t>
+  </si>
+  <si>
+    <t>q60_1</t>
+  </si>
+  <si>
+    <t>q60_7</t>
+  </si>
+  <si>
+    <t>q60_8</t>
+  </si>
+  <si>
+    <t>q60_9</t>
+  </si>
+  <si>
+    <t>At USA ikke længere er en troværdig allieret</t>
+  </si>
+  <si>
+    <t>q45a_24</t>
+  </si>
+  <si>
+    <t>q32</t>
+  </si>
+  <si>
+    <t>household_income</t>
+  </si>
+  <si>
+    <t>personal_income</t>
+  </si>
+  <si>
+    <t>q1_1</t>
+  </si>
+  <si>
+    <t>q1_3</t>
+  </si>
+  <si>
+    <t>q1_4</t>
+  </si>
+  <si>
+    <t>q1_6</t>
+  </si>
+  <si>
+    <t>q1_7</t>
+  </si>
+  <si>
+    <t>q1_9</t>
+  </si>
+  <si>
+    <t>q1_10</t>
+  </si>
+  <si>
+    <t>q1_12</t>
+  </si>
+  <si>
+    <t>q1_13</t>
+  </si>
+  <si>
+    <t>q1_15</t>
+  </si>
+  <si>
+    <t>q1_16</t>
+  </si>
+  <si>
+    <t>q1_2</t>
+  </si>
+  <si>
+    <t>q1_8</t>
+  </si>
+  <si>
+    <t>q1_11</t>
+  </si>
+  <si>
+    <t>q1_14</t>
   </si>
 </sst>
 </file>
@@ -1203,10 +1289,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1545,7 +1632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDCC2279-7CC5-471A-AC30-1F8A606C7178}">
-  <dimension ref="A1:AO70"/>
+  <dimension ref="A1:AO71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="65.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -1699,6 +1786,24 @@
       <c r="C2" t="s">
         <v>91</v>
       </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I2" t="s">
+        <v>91</v>
+      </c>
       <c r="L2" t="s">
         <v>303</v>
       </c>
@@ -1746,10 +1851,19 @@
       <c r="D3" t="s">
         <v>92</v>
       </c>
+      <c r="E3" t="s">
+        <v>92</v>
+      </c>
       <c r="F3" t="s">
         <v>92</v>
       </c>
       <c r="G3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I3" t="s">
         <v>92</v>
       </c>
       <c r="L3" t="s">
@@ -1796,13 +1910,52 @@
       <c r="C4" t="s">
         <v>346</v>
       </c>
+      <c r="D4" t="s">
+        <v>346</v>
+      </c>
+      <c r="E4" t="s">
+        <v>346</v>
+      </c>
+      <c r="F4" t="s">
+        <v>346</v>
+      </c>
+      <c r="G4" t="s">
+        <v>346</v>
+      </c>
+      <c r="H4" t="s">
+        <v>346</v>
+      </c>
+      <c r="I4" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="B5" t="s">
+        <v>196</v>
+      </c>
       <c r="C5" t="s">
         <v>347</v>
+      </c>
+      <c r="D5" t="s">
+        <v>347</v>
+      </c>
+      <c r="E5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F5" t="s">
+        <v>347</v>
+      </c>
+      <c r="G5" t="s">
+        <v>347</v>
+      </c>
+      <c r="H5" t="s">
+        <v>196</v>
+      </c>
+      <c r="I5" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
@@ -1815,12 +1968,51 @@
       <c r="C6" t="s">
         <v>354</v>
       </c>
+      <c r="D6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H6" t="s">
+        <v>196</v>
+      </c>
+      <c r="I6" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="B7" t="s">
+        <v>196</v>
+      </c>
       <c r="C7" t="s">
+        <v>348</v>
+      </c>
+      <c r="D7" t="s">
+        <v>348</v>
+      </c>
+      <c r="E7" t="s">
+        <v>348</v>
+      </c>
+      <c r="F7" t="s">
+        <v>348</v>
+      </c>
+      <c r="G7" t="s">
+        <v>348</v>
+      </c>
+      <c r="H7" t="s">
+        <v>348</v>
+      </c>
+      <c r="I7" t="s">
         <v>348</v>
       </c>
     </row>
@@ -1828,14 +2020,59 @@
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="B8" t="s">
+        <v>196</v>
+      </c>
       <c r="C8" t="s">
         <v>349</v>
+      </c>
+      <c r="D8" t="s">
+        <v>349</v>
+      </c>
+      <c r="E8" t="s">
+        <v>349</v>
+      </c>
+      <c r="F8" t="s">
+        <v>349</v>
+      </c>
+      <c r="G8" t="s">
+        <v>349</v>
+      </c>
+      <c r="H8" t="s">
+        <v>196</v>
+      </c>
+      <c r="I8" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="B9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E9" t="s">
+        <v>196</v>
+      </c>
+      <c r="F9" t="s">
+        <v>196</v>
+      </c>
+      <c r="G9" t="s">
+        <v>196</v>
+      </c>
+      <c r="H9" t="s">
+        <v>377</v>
+      </c>
+      <c r="I9" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1847,6 +2084,24 @@
       <c r="C10" t="s">
         <v>325</v>
       </c>
+      <c r="D10" t="s">
+        <v>196</v>
+      </c>
+      <c r="E10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G10" t="s">
+        <v>376</v>
+      </c>
+      <c r="H10" t="s">
+        <v>376</v>
+      </c>
+      <c r="I10" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1858,13 +2113,52 @@
       <c r="C11" t="s">
         <v>327</v>
       </c>
+      <c r="D11" t="s">
+        <v>327</v>
+      </c>
+      <c r="E11" t="s">
+        <v>196</v>
+      </c>
+      <c r="F11" t="s">
+        <v>327</v>
+      </c>
+      <c r="G11" t="s">
+        <v>196</v>
+      </c>
+      <c r="H11" t="s">
+        <v>196</v>
+      </c>
+      <c r="I11" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="B12" t="s">
+        <v>196</v>
+      </c>
       <c r="C12" t="s">
         <v>355</v>
+      </c>
+      <c r="D12" t="s">
+        <v>355</v>
+      </c>
+      <c r="E12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F12" t="s">
+        <v>355</v>
+      </c>
+      <c r="G12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H12" t="s">
+        <v>196</v>
+      </c>
+      <c r="I12" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
@@ -1877,6 +2171,24 @@
       <c r="C13" t="s">
         <v>323</v>
       </c>
+      <c r="D13" t="s">
+        <v>323</v>
+      </c>
+      <c r="E13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F13" t="s">
+        <v>323</v>
+      </c>
+      <c r="G13" t="s">
+        <v>323</v>
+      </c>
+      <c r="H13" t="s">
+        <v>196</v>
+      </c>
+      <c r="I13" t="s">
+        <v>196</v>
+      </c>
       <c r="K13" t="s">
         <v>302</v>
       </c>
@@ -1918,17 +2230,29 @@
       <c r="A14" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="B14" t="s">
+        <v>196</v>
+      </c>
       <c r="C14" t="s">
         <v>300</v>
       </c>
       <c r="D14" t="s">
         <v>300</v>
       </c>
+      <c r="E14" t="s">
+        <v>196</v>
+      </c>
       <c r="F14" t="s">
         <v>300</v>
       </c>
       <c r="G14" t="s">
         <v>300</v>
+      </c>
+      <c r="H14" t="s">
+        <v>196</v>
+      </c>
+      <c r="I14" t="s">
+        <v>196</v>
       </c>
       <c r="K14" t="s">
         <v>301</v>
@@ -1959,11 +2283,29 @@
       <c r="A15" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="B15" t="s">
+        <v>196</v>
+      </c>
       <c r="C15" t="s">
         <v>329</v>
       </c>
       <c r="D15" t="s">
         <v>329</v>
+      </c>
+      <c r="E15" t="s">
+        <v>196</v>
+      </c>
+      <c r="F15" t="s">
+        <v>196</v>
+      </c>
+      <c r="G15" t="s">
+        <v>196</v>
+      </c>
+      <c r="H15" t="s">
+        <v>196</v>
+      </c>
+      <c r="I15" t="s">
+        <v>196</v>
       </c>
       <c r="M15" t="s">
         <v>326</v>
@@ -2000,63 +2342,291 @@
       <c r="A16" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="B16" t="s">
+        <v>196</v>
+      </c>
       <c r="C16" t="s">
         <v>352</v>
+      </c>
+      <c r="D16" t="s">
+        <v>364</v>
+      </c>
+      <c r="E16" t="s">
+        <v>196</v>
+      </c>
+      <c r="F16" t="s">
+        <v>364</v>
+      </c>
+      <c r="G16" t="s">
+        <v>196</v>
+      </c>
+      <c r="H16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I16" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="B17" t="s">
+        <v>196</v>
+      </c>
       <c r="C17" t="s">
         <v>350</v>
+      </c>
+      <c r="D17" t="s">
+        <v>365</v>
+      </c>
+      <c r="E17" t="s">
+        <v>196</v>
+      </c>
+      <c r="F17" t="s">
+        <v>365</v>
+      </c>
+      <c r="G17" t="s">
+        <v>196</v>
+      </c>
+      <c r="H17" t="s">
+        <v>196</v>
+      </c>
+      <c r="I17" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="B18" t="s">
+        <v>196</v>
+      </c>
       <c r="C18" t="s">
         <v>351</v>
+      </c>
+      <c r="D18" t="s">
+        <v>366</v>
+      </c>
+      <c r="E18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F18" t="s">
+        <v>366</v>
+      </c>
+      <c r="G18" t="s">
+        <v>196</v>
+      </c>
+      <c r="H18" t="s">
+        <v>196</v>
+      </c>
+      <c r="I18" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="B19" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D19" t="s">
+        <v>367</v>
+      </c>
+      <c r="E19" t="s">
+        <v>196</v>
+      </c>
+      <c r="F19" t="s">
+        <v>367</v>
+      </c>
+      <c r="G19" t="s">
+        <v>196</v>
+      </c>
+      <c r="H19" t="s">
+        <v>196</v>
+      </c>
+      <c r="I19" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="B20" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" t="s">
+        <v>196</v>
+      </c>
+      <c r="D20" t="s">
+        <v>368</v>
+      </c>
+      <c r="E20" t="s">
+        <v>196</v>
+      </c>
+      <c r="F20" t="s">
+        <v>368</v>
+      </c>
+      <c r="G20" t="s">
+        <v>196</v>
+      </c>
+      <c r="H20" t="s">
+        <v>196</v>
+      </c>
+      <c r="I20" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="B21" t="s">
+        <v>196</v>
+      </c>
       <c r="C21" t="s">
         <v>353</v>
+      </c>
+      <c r="D21" t="s">
+        <v>369</v>
+      </c>
+      <c r="E21" t="s">
+        <v>196</v>
+      </c>
+      <c r="F21" t="s">
+        <v>369</v>
+      </c>
+      <c r="G21" t="s">
+        <v>196</v>
+      </c>
+      <c r="H21" t="s">
+        <v>196</v>
+      </c>
+      <c r="I21" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="B22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" t="s">
+        <v>196</v>
+      </c>
+      <c r="D22" t="s">
+        <v>370</v>
+      </c>
+      <c r="E22" t="s">
+        <v>196</v>
+      </c>
+      <c r="F22" t="s">
+        <v>370</v>
+      </c>
+      <c r="G22" t="s">
+        <v>196</v>
+      </c>
+      <c r="H22" t="s">
+        <v>196</v>
+      </c>
+      <c r="I22" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
+      <c r="B23" t="s">
+        <v>196</v>
+      </c>
+      <c r="C23" t="s">
+        <v>196</v>
+      </c>
+      <c r="D23" t="s">
+        <v>196</v>
+      </c>
+      <c r="E23" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" t="s">
+        <v>196</v>
+      </c>
+      <c r="G23" t="s">
+        <v>196</v>
+      </c>
+      <c r="H23" t="s">
+        <v>196</v>
+      </c>
+      <c r="I23" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="B24" t="s">
+        <v>196</v>
+      </c>
+      <c r="C24" t="s">
+        <v>196</v>
+      </c>
+      <c r="D24" t="s">
+        <v>371</v>
+      </c>
+      <c r="E24" t="s">
+        <v>196</v>
+      </c>
+      <c r="F24" t="s">
+        <v>371</v>
+      </c>
+      <c r="G24" t="s">
+        <v>196</v>
+      </c>
+      <c r="H24" t="s">
+        <v>196</v>
+      </c>
+      <c r="I24" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="B25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" t="s">
+        <v>196</v>
+      </c>
+      <c r="D25" t="s">
+        <v>372</v>
+      </c>
+      <c r="E25" t="s">
+        <v>196</v>
+      </c>
+      <c r="F25" t="s">
+        <v>372</v>
+      </c>
+      <c r="G25" t="s">
+        <v>196</v>
+      </c>
+      <c r="H25" t="s">
+        <v>196</v>
+      </c>
+      <c r="I25" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -2065,11 +2635,26 @@
       <c r="B26" t="s">
         <v>330</v>
       </c>
+      <c r="C26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D26" t="s">
+        <v>331</v>
+      </c>
+      <c r="E26" t="s">
+        <v>196</v>
+      </c>
       <c r="F26" t="s">
         <v>331</v>
       </c>
       <c r="G26" t="s">
         <v>331</v>
+      </c>
+      <c r="H26" t="s">
+        <v>196</v>
+      </c>
+      <c r="I26" t="s">
+        <v>196</v>
       </c>
       <c r="L26" t="s">
         <v>332</v>
@@ -2112,6 +2697,30 @@
       <c r="A27" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="B27" t="s">
+        <v>196</v>
+      </c>
+      <c r="C27" t="s">
+        <v>196</v>
+      </c>
+      <c r="D27" t="s">
+        <v>196</v>
+      </c>
+      <c r="E27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F27" t="s">
+        <v>375</v>
+      </c>
+      <c r="G27" t="s">
+        <v>196</v>
+      </c>
+      <c r="H27" t="s">
+        <v>196</v>
+      </c>
+      <c r="I27" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -2123,6 +2732,24 @@
       <c r="C28" t="s">
         <v>321</v>
       </c>
+      <c r="D28" t="s">
+        <v>321</v>
+      </c>
+      <c r="E28" t="s">
+        <v>196</v>
+      </c>
+      <c r="F28" t="s">
+        <v>321</v>
+      </c>
+      <c r="G28" t="s">
+        <v>196</v>
+      </c>
+      <c r="H28" t="s">
+        <v>196</v>
+      </c>
+      <c r="I28" t="s">
+        <v>196</v>
+      </c>
       <c r="L28" t="s">
         <v>306</v>
       </c>
@@ -2161,6 +2788,30 @@
       <c r="A29" s="1" t="s">
         <v>66</v>
       </c>
+      <c r="B29" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" t="s">
+        <v>196</v>
+      </c>
+      <c r="D29" t="s">
+        <v>196</v>
+      </c>
+      <c r="E29" t="s">
+        <v>196</v>
+      </c>
+      <c r="F29" t="s">
+        <v>196</v>
+      </c>
+      <c r="G29" t="s">
+        <v>196</v>
+      </c>
+      <c r="H29" t="s">
+        <v>196</v>
+      </c>
+      <c r="I29" t="s">
+        <v>196</v>
+      </c>
       <c r="L29" t="s">
         <v>307</v>
       </c>
@@ -2199,8 +2850,29 @@
       <c r="A30" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="B30" t="s">
+        <v>196</v>
+      </c>
       <c r="C30" t="s">
         <v>268</v>
+      </c>
+      <c r="D30" t="s">
+        <v>268</v>
+      </c>
+      <c r="E30" t="s">
+        <v>196</v>
+      </c>
+      <c r="F30" t="s">
+        <v>268</v>
+      </c>
+      <c r="G30" t="s">
+        <v>196</v>
+      </c>
+      <c r="H30" t="s">
+        <v>382</v>
+      </c>
+      <c r="I30" t="s">
+        <v>382</v>
       </c>
       <c r="K30" t="s">
         <v>203</v>
@@ -2243,8 +2915,29 @@
       <c r="A31" s="1" t="s">
         <v>68</v>
       </c>
+      <c r="B31" t="s">
+        <v>196</v>
+      </c>
       <c r="C31" t="s">
         <v>264</v>
+      </c>
+      <c r="D31" t="s">
+        <v>264</v>
+      </c>
+      <c r="E31" t="s">
+        <v>196</v>
+      </c>
+      <c r="F31" t="s">
+        <v>264</v>
+      </c>
+      <c r="G31" t="s">
+        <v>264</v>
+      </c>
+      <c r="H31" t="s">
+        <v>389</v>
+      </c>
+      <c r="I31" t="s">
+        <v>389</v>
       </c>
       <c r="K31" t="s">
         <v>198</v>
@@ -2287,6 +2980,27 @@
       <c r="A32" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="B32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C32" t="s">
+        <v>196</v>
+      </c>
+      <c r="D32" t="s">
+        <v>196</v>
+      </c>
+      <c r="E32" t="s">
+        <v>196</v>
+      </c>
+      <c r="G32" t="s">
+        <v>196</v>
+      </c>
+      <c r="H32" t="s">
+        <v>196</v>
+      </c>
+      <c r="I32" t="s">
+        <v>196</v>
+      </c>
       <c r="K32" t="s">
         <v>283</v>
       </c>
@@ -2325,8 +3039,29 @@
       <c r="A33" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="B33" t="s">
+        <v>196</v>
+      </c>
       <c r="C33" t="s">
         <v>263</v>
+      </c>
+      <c r="D33" t="s">
+        <v>263</v>
+      </c>
+      <c r="E33" t="s">
+        <v>196</v>
+      </c>
+      <c r="F33" t="s">
+        <v>263</v>
+      </c>
+      <c r="G33" t="s">
+        <v>263</v>
+      </c>
+      <c r="H33" t="s">
+        <v>378</v>
+      </c>
+      <c r="I33" t="s">
+        <v>378</v>
       </c>
       <c r="K33" t="s">
         <v>197</v>
@@ -2369,8 +3104,29 @@
       <c r="A34" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="B34" t="s">
+        <v>196</v>
+      </c>
       <c r="C34" t="s">
         <v>265</v>
+      </c>
+      <c r="D34" t="s">
+        <v>265</v>
+      </c>
+      <c r="E34" t="s">
+        <v>196</v>
+      </c>
+      <c r="F34" t="s">
+        <v>265</v>
+      </c>
+      <c r="G34" t="s">
+        <v>196</v>
+      </c>
+      <c r="H34" t="s">
+        <v>379</v>
+      </c>
+      <c r="I34" t="s">
+        <v>379</v>
       </c>
       <c r="K34" t="s">
         <v>199</v>
@@ -2413,6 +3169,27 @@
       <c r="A35" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="B35" t="s">
+        <v>196</v>
+      </c>
+      <c r="C35" t="s">
+        <v>196</v>
+      </c>
+      <c r="D35" t="s">
+        <v>196</v>
+      </c>
+      <c r="E35" t="s">
+        <v>196</v>
+      </c>
+      <c r="G35" t="s">
+        <v>196</v>
+      </c>
+      <c r="H35" t="s">
+        <v>196</v>
+      </c>
+      <c r="I35" t="s">
+        <v>196</v>
+      </c>
       <c r="K35" t="s">
         <v>284</v>
       </c>
@@ -2451,8 +3228,29 @@
       <c r="A36" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="B36" t="s">
+        <v>196</v>
+      </c>
       <c r="C36" t="s">
         <v>267</v>
+      </c>
+      <c r="D36" t="s">
+        <v>267</v>
+      </c>
+      <c r="E36" t="s">
+        <v>196</v>
+      </c>
+      <c r="F36" t="s">
+        <v>267</v>
+      </c>
+      <c r="G36" t="s">
+        <v>196</v>
+      </c>
+      <c r="H36" t="s">
+        <v>381</v>
+      </c>
+      <c r="I36" t="s">
+        <v>381</v>
       </c>
       <c r="K36" t="s">
         <v>202</v>
@@ -2495,8 +3293,26 @@
       <c r="A37" s="1" t="s">
         <v>74</v>
       </c>
+      <c r="B37" t="s">
+        <v>196</v>
+      </c>
       <c r="C37" t="s">
         <v>266</v>
+      </c>
+      <c r="D37" t="s">
+        <v>266</v>
+      </c>
+      <c r="E37" t="s">
+        <v>196</v>
+      </c>
+      <c r="G37" t="s">
+        <v>266</v>
+      </c>
+      <c r="H37" t="s">
+        <v>380</v>
+      </c>
+      <c r="I37" t="s">
+        <v>380</v>
       </c>
       <c r="K37" t="s">
         <v>201</v>
@@ -2539,8 +3355,29 @@
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
+      <c r="B38" t="s">
+        <v>196</v>
+      </c>
       <c r="C38" t="s">
         <v>281</v>
+      </c>
+      <c r="D38" t="s">
+        <v>281</v>
+      </c>
+      <c r="E38" t="s">
+        <v>196</v>
+      </c>
+      <c r="F38" t="s">
+        <v>281</v>
+      </c>
+      <c r="G38" t="s">
+        <v>281</v>
+      </c>
+      <c r="H38" t="s">
+        <v>196</v>
+      </c>
+      <c r="I38" t="s">
+        <v>196</v>
       </c>
       <c r="K38" t="s">
         <v>200</v>
@@ -2583,6 +3420,27 @@
       <c r="A39" s="1" t="s">
         <v>76</v>
       </c>
+      <c r="B39" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" t="s">
+        <v>196</v>
+      </c>
+      <c r="D39" t="s">
+        <v>196</v>
+      </c>
+      <c r="E39" t="s">
+        <v>196</v>
+      </c>
+      <c r="G39" t="s">
+        <v>196</v>
+      </c>
+      <c r="H39" t="s">
+        <v>196</v>
+      </c>
+      <c r="I39" t="s">
+        <v>196</v>
+      </c>
       <c r="K39" t="s">
         <v>285</v>
       </c>
@@ -2621,8 +3479,29 @@
       <c r="A40" s="1" t="s">
         <v>218</v>
       </c>
+      <c r="B40" t="s">
+        <v>196</v>
+      </c>
       <c r="C40" t="s">
         <v>269</v>
+      </c>
+      <c r="D40" t="s">
+        <v>269</v>
+      </c>
+      <c r="E40" t="s">
+        <v>196</v>
+      </c>
+      <c r="F40" t="s">
+        <v>269</v>
+      </c>
+      <c r="G40" t="s">
+        <v>196</v>
+      </c>
+      <c r="H40" t="s">
+        <v>196</v>
+      </c>
+      <c r="I40" t="s">
+        <v>390</v>
       </c>
       <c r="K40" t="s">
         <v>196</v>
@@ -2665,8 +3544,26 @@
       <c r="A41" s="1" t="s">
         <v>219</v>
       </c>
+      <c r="B41" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="C41" t="s">
         <v>280</v>
+      </c>
+      <c r="D41" t="s">
+        <v>196</v>
+      </c>
+      <c r="E41" t="s">
+        <v>196</v>
+      </c>
+      <c r="G41" t="s">
+        <v>196</v>
+      </c>
+      <c r="H41" t="s">
+        <v>196</v>
+      </c>
+      <c r="I41" t="s">
+        <v>196</v>
       </c>
       <c r="K41" t="s">
         <v>196</v>
@@ -2706,6 +3603,27 @@
       <c r="A42" s="1" t="s">
         <v>220</v>
       </c>
+      <c r="B42" t="s">
+        <v>196</v>
+      </c>
+      <c r="C42" t="s">
+        <v>196</v>
+      </c>
+      <c r="D42" t="s">
+        <v>196</v>
+      </c>
+      <c r="E42" t="s">
+        <v>196</v>
+      </c>
+      <c r="G42" t="s">
+        <v>196</v>
+      </c>
+      <c r="H42" t="s">
+        <v>384</v>
+      </c>
+      <c r="I42" t="s">
+        <v>384</v>
+      </c>
       <c r="K42" t="s">
         <v>196</v>
       </c>
@@ -2744,6 +3662,27 @@
       <c r="A43" s="1" t="s">
         <v>232</v>
       </c>
+      <c r="B43" t="s">
+        <v>196</v>
+      </c>
+      <c r="C43" t="s">
+        <v>196</v>
+      </c>
+      <c r="D43" t="s">
+        <v>196</v>
+      </c>
+      <c r="E43" t="s">
+        <v>196</v>
+      </c>
+      <c r="G43" t="s">
+        <v>196</v>
+      </c>
+      <c r="H43" t="s">
+        <v>196</v>
+      </c>
+      <c r="I43" t="s">
+        <v>391</v>
+      </c>
       <c r="K43" t="s">
         <v>196</v>
       </c>
@@ -2782,8 +3721,29 @@
       <c r="A44" s="1" t="s">
         <v>221</v>
       </c>
+      <c r="B44" t="s">
+        <v>196</v>
+      </c>
       <c r="C44" t="s">
         <v>271</v>
+      </c>
+      <c r="D44" t="s">
+        <v>271</v>
+      </c>
+      <c r="E44" t="s">
+        <v>196</v>
+      </c>
+      <c r="F44" t="s">
+        <v>271</v>
+      </c>
+      <c r="G44" t="s">
+        <v>271</v>
+      </c>
+      <c r="H44" t="s">
+        <v>385</v>
+      </c>
+      <c r="I44" t="s">
+        <v>385</v>
       </c>
       <c r="K44" t="s">
         <v>196</v>
@@ -2826,8 +3786,29 @@
       <c r="A45" s="1" t="s">
         <v>222</v>
       </c>
+      <c r="B45" t="s">
+        <v>196</v>
+      </c>
       <c r="C45" t="s">
         <v>282</v>
+      </c>
+      <c r="D45" t="s">
+        <v>282</v>
+      </c>
+      <c r="E45" t="s">
+        <v>196</v>
+      </c>
+      <c r="F45" t="s">
+        <v>282</v>
+      </c>
+      <c r="G45" t="s">
+        <v>282</v>
+      </c>
+      <c r="H45" t="s">
+        <v>196</v>
+      </c>
+      <c r="I45" t="s">
+        <v>196</v>
       </c>
       <c r="K45" t="s">
         <v>196</v>
@@ -2870,8 +3851,29 @@
       <c r="A46" s="1" t="s">
         <v>223</v>
       </c>
+      <c r="B46" t="s">
+        <v>196</v>
+      </c>
       <c r="C46" t="s">
         <v>272</v>
+      </c>
+      <c r="D46" t="s">
+        <v>272</v>
+      </c>
+      <c r="E46" t="s">
+        <v>196</v>
+      </c>
+      <c r="F46" t="s">
+        <v>272</v>
+      </c>
+      <c r="G46" t="s">
+        <v>272</v>
+      </c>
+      <c r="H46" t="s">
+        <v>386</v>
+      </c>
+      <c r="I46" t="s">
+        <v>386</v>
       </c>
       <c r="K46" t="s">
         <v>196</v>
@@ -2914,8 +3916,29 @@
       <c r="A47" s="1" t="s">
         <v>224</v>
       </c>
+      <c r="B47" t="s">
+        <v>196</v>
+      </c>
       <c r="C47" t="s">
         <v>273</v>
+      </c>
+      <c r="D47" t="s">
+        <v>273</v>
+      </c>
+      <c r="E47" t="s">
+        <v>196</v>
+      </c>
+      <c r="F47" t="s">
+        <v>273</v>
+      </c>
+      <c r="G47" t="s">
+        <v>273</v>
+      </c>
+      <c r="H47" t="s">
+        <v>392</v>
+      </c>
+      <c r="I47" t="s">
+        <v>392</v>
       </c>
       <c r="K47" t="s">
         <v>196</v>
@@ -2958,8 +3981,29 @@
       <c r="A48" s="1" t="s">
         <v>225</v>
       </c>
+      <c r="B48" t="s">
+        <v>196</v>
+      </c>
       <c r="C48" t="s">
         <v>276</v>
+      </c>
+      <c r="D48" t="s">
+        <v>276</v>
+      </c>
+      <c r="E48" t="s">
+        <v>196</v>
+      </c>
+      <c r="F48" t="s">
+        <v>276</v>
+      </c>
+      <c r="G48" t="s">
+        <v>276</v>
+      </c>
+      <c r="H48" t="s">
+        <v>387</v>
+      </c>
+      <c r="I48" t="s">
+        <v>387</v>
       </c>
       <c r="K48" t="s">
         <v>196</v>
@@ -3002,8 +4046,29 @@
       <c r="A49" s="1" t="s">
         <v>226</v>
       </c>
+      <c r="B49" t="s">
+        <v>196</v>
+      </c>
       <c r="C49" t="s">
         <v>277</v>
+      </c>
+      <c r="D49" t="s">
+        <v>277</v>
+      </c>
+      <c r="E49" t="s">
+        <v>196</v>
+      </c>
+      <c r="F49" t="s">
+        <v>277</v>
+      </c>
+      <c r="G49" t="s">
+        <v>277</v>
+      </c>
+      <c r="H49" t="s">
+        <v>388</v>
+      </c>
+      <c r="I49" t="s">
+        <v>388</v>
       </c>
       <c r="K49" t="s">
         <v>196</v>
@@ -3046,8 +4111,29 @@
       <c r="A50" s="1" t="s">
         <v>227</v>
       </c>
+      <c r="B50" t="s">
+        <v>196</v>
+      </c>
       <c r="C50" t="s">
         <v>270</v>
+      </c>
+      <c r="D50" t="s">
+        <v>270</v>
+      </c>
+      <c r="E50" t="s">
+        <v>196</v>
+      </c>
+      <c r="F50" t="s">
+        <v>270</v>
+      </c>
+      <c r="G50" t="s">
+        <v>270</v>
+      </c>
+      <c r="H50" t="s">
+        <v>383</v>
+      </c>
+      <c r="I50" t="s">
+        <v>383</v>
       </c>
       <c r="K50" t="s">
         <v>196</v>
@@ -3090,8 +4176,29 @@
       <c r="A51" s="1" t="s">
         <v>77</v>
       </c>
+      <c r="B51" t="s">
+        <v>196</v>
+      </c>
       <c r="C51" t="s">
         <v>181</v>
+      </c>
+      <c r="D51" t="s">
+        <v>181</v>
+      </c>
+      <c r="E51" t="s">
+        <v>196</v>
+      </c>
+      <c r="F51" t="s">
+        <v>181</v>
+      </c>
+      <c r="G51" t="s">
+        <v>196</v>
+      </c>
+      <c r="H51" t="s">
+        <v>196</v>
+      </c>
+      <c r="I51" t="s">
+        <v>196</v>
       </c>
       <c r="K51" t="s">
         <v>93</v>
@@ -3134,6 +4241,27 @@
       <c r="A52" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="B52" t="s">
+        <v>196</v>
+      </c>
+      <c r="C52" t="s">
+        <v>196</v>
+      </c>
+      <c r="D52" t="s">
+        <v>196</v>
+      </c>
+      <c r="E52" t="s">
+        <v>196</v>
+      </c>
+      <c r="G52" t="s">
+        <v>196</v>
+      </c>
+      <c r="H52" t="s">
+        <v>196</v>
+      </c>
+      <c r="I52" t="s">
+        <v>196</v>
+      </c>
       <c r="K52" t="s">
         <v>94</v>
       </c>
@@ -3175,8 +4303,29 @@
       <c r="A53" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="B53" t="s">
+        <v>196</v>
+      </c>
       <c r="C53" t="s">
         <v>182</v>
+      </c>
+      <c r="D53" t="s">
+        <v>264</v>
+      </c>
+      <c r="E53" t="s">
+        <v>196</v>
+      </c>
+      <c r="F53" t="s">
+        <v>182</v>
+      </c>
+      <c r="G53" t="s">
+        <v>196</v>
+      </c>
+      <c r="H53" t="s">
+        <v>196</v>
+      </c>
+      <c r="I53" t="s">
+        <v>196</v>
       </c>
       <c r="K53" t="s">
         <v>95</v>
@@ -3219,6 +4368,27 @@
       <c r="A54" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="B54" t="s">
+        <v>196</v>
+      </c>
+      <c r="C54" t="s">
+        <v>196</v>
+      </c>
+      <c r="D54" t="s">
+        <v>196</v>
+      </c>
+      <c r="E54" t="s">
+        <v>196</v>
+      </c>
+      <c r="G54" t="s">
+        <v>196</v>
+      </c>
+      <c r="H54" t="s">
+        <v>196</v>
+      </c>
+      <c r="I54" t="s">
+        <v>196</v>
+      </c>
       <c r="K54" t="s">
         <v>96</v>
       </c>
@@ -3260,8 +4430,29 @@
       <c r="A55" s="1" t="s">
         <v>81</v>
       </c>
+      <c r="B55" t="s">
+        <v>196</v>
+      </c>
       <c r="C55" t="s">
         <v>183</v>
+      </c>
+      <c r="D55" t="s">
+        <v>183</v>
+      </c>
+      <c r="E55" t="s">
+        <v>196</v>
+      </c>
+      <c r="F55" t="s">
+        <v>183</v>
+      </c>
+      <c r="G55" t="s">
+        <v>196</v>
+      </c>
+      <c r="H55" t="s">
+        <v>196</v>
+      </c>
+      <c r="I55" t="s">
+        <v>196</v>
       </c>
       <c r="K55" t="s">
         <v>97</v>
@@ -3304,6 +4495,27 @@
       <c r="A56" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="B56" t="s">
+        <v>196</v>
+      </c>
+      <c r="C56" t="s">
+        <v>196</v>
+      </c>
+      <c r="D56" t="s">
+        <v>196</v>
+      </c>
+      <c r="E56" t="s">
+        <v>196</v>
+      </c>
+      <c r="G56" t="s">
+        <v>196</v>
+      </c>
+      <c r="H56" t="s">
+        <v>196</v>
+      </c>
+      <c r="I56" t="s">
+        <v>196</v>
+      </c>
       <c r="K56" t="s">
         <v>98</v>
       </c>
@@ -3345,8 +4557,29 @@
       <c r="A57" s="1" t="s">
         <v>83</v>
       </c>
+      <c r="B57" t="s">
+        <v>196</v>
+      </c>
       <c r="C57" t="s">
         <v>184</v>
+      </c>
+      <c r="D57" t="s">
+        <v>184</v>
+      </c>
+      <c r="E57" t="s">
+        <v>196</v>
+      </c>
+      <c r="F57" t="s">
+        <v>184</v>
+      </c>
+      <c r="G57" t="s">
+        <v>196</v>
+      </c>
+      <c r="H57" t="s">
+        <v>196</v>
+      </c>
+      <c r="I57" t="s">
+        <v>196</v>
       </c>
       <c r="K57" t="s">
         <v>99</v>
@@ -3389,6 +4622,27 @@
       <c r="A58" s="1" t="s">
         <v>84</v>
       </c>
+      <c r="B58" t="s">
+        <v>196</v>
+      </c>
+      <c r="C58" t="s">
+        <v>196</v>
+      </c>
+      <c r="D58" t="s">
+        <v>196</v>
+      </c>
+      <c r="E58" t="s">
+        <v>196</v>
+      </c>
+      <c r="G58" t="s">
+        <v>196</v>
+      </c>
+      <c r="H58" t="s">
+        <v>196</v>
+      </c>
+      <c r="I58" t="s">
+        <v>196</v>
+      </c>
       <c r="K58" t="s">
         <v>100</v>
       </c>
@@ -3430,8 +4684,29 @@
       <c r="A59" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="B59" t="s">
+        <v>196</v>
+      </c>
       <c r="C59" t="s">
         <v>193</v>
+      </c>
+      <c r="D59" t="s">
+        <v>193</v>
+      </c>
+      <c r="E59" t="s">
+        <v>196</v>
+      </c>
+      <c r="F59" t="s">
+        <v>193</v>
+      </c>
+      <c r="G59" t="s">
+        <v>196</v>
+      </c>
+      <c r="H59" t="s">
+        <v>196</v>
+      </c>
+      <c r="I59" t="s">
+        <v>196</v>
       </c>
       <c r="K59" t="s">
         <v>101</v>
@@ -3474,8 +4749,29 @@
       <c r="A60" s="1" t="s">
         <v>86</v>
       </c>
+      <c r="B60" t="s">
+        <v>196</v>
+      </c>
       <c r="C60" t="s">
         <v>185</v>
+      </c>
+      <c r="D60" t="s">
+        <v>185</v>
+      </c>
+      <c r="E60" t="s">
+        <v>196</v>
+      </c>
+      <c r="F60" t="s">
+        <v>185</v>
+      </c>
+      <c r="G60" t="s">
+        <v>196</v>
+      </c>
+      <c r="H60" t="s">
+        <v>196</v>
+      </c>
+      <c r="I60" t="s">
+        <v>196</v>
       </c>
       <c r="K60" t="s">
         <v>102</v>
@@ -3518,6 +4814,27 @@
       <c r="A61" s="1" t="s">
         <v>87</v>
       </c>
+      <c r="B61" t="s">
+        <v>196</v>
+      </c>
+      <c r="C61" t="s">
+        <v>196</v>
+      </c>
+      <c r="D61" t="s">
+        <v>196</v>
+      </c>
+      <c r="E61" t="s">
+        <v>196</v>
+      </c>
+      <c r="G61" t="s">
+        <v>196</v>
+      </c>
+      <c r="H61" t="s">
+        <v>196</v>
+      </c>
+      <c r="I61" t="s">
+        <v>196</v>
+      </c>
       <c r="K61" t="s">
         <v>103</v>
       </c>
@@ -3559,8 +4876,26 @@
       <c r="A62" s="1" t="s">
         <v>88</v>
       </c>
+      <c r="B62" t="s">
+        <v>196</v>
+      </c>
       <c r="C62" t="s">
         <v>186</v>
+      </c>
+      <c r="D62" t="s">
+        <v>186</v>
+      </c>
+      <c r="E62" t="s">
+        <v>196</v>
+      </c>
+      <c r="G62" t="s">
+        <v>196</v>
+      </c>
+      <c r="H62" t="s">
+        <v>196</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="K62" t="s">
         <v>104</v>
@@ -3603,6 +4938,27 @@
       <c r="A63" s="1" t="s">
         <v>89</v>
       </c>
+      <c r="B63" t="s">
+        <v>196</v>
+      </c>
+      <c r="C63" t="s">
+        <v>196</v>
+      </c>
+      <c r="D63" t="s">
+        <v>196</v>
+      </c>
+      <c r="E63" t="s">
+        <v>196</v>
+      </c>
+      <c r="G63" t="s">
+        <v>196</v>
+      </c>
+      <c r="H63" t="s">
+        <v>196</v>
+      </c>
+      <c r="I63" t="s">
+        <v>196</v>
+      </c>
       <c r="K63" t="s">
         <v>105</v>
       </c>
@@ -3644,6 +5000,27 @@
       <c r="A64" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="B64" t="s">
+        <v>196</v>
+      </c>
+      <c r="C64" t="s">
+        <v>196</v>
+      </c>
+      <c r="D64" t="s">
+        <v>196</v>
+      </c>
+      <c r="E64" t="s">
+        <v>196</v>
+      </c>
+      <c r="G64" t="s">
+        <v>196</v>
+      </c>
+      <c r="H64" t="s">
+        <v>196</v>
+      </c>
+      <c r="I64" t="s">
+        <v>196</v>
+      </c>
       <c r="K64" t="s">
         <v>106</v>
       </c>
@@ -3685,8 +5062,29 @@
       <c r="A65" s="1" t="s">
         <v>135</v>
       </c>
+      <c r="B65" t="s">
+        <v>196</v>
+      </c>
       <c r="C65" t="s">
         <v>187</v>
+      </c>
+      <c r="D65" t="s">
+        <v>187</v>
+      </c>
+      <c r="E65" t="s">
+        <v>196</v>
+      </c>
+      <c r="F65" t="s">
+        <v>186</v>
+      </c>
+      <c r="G65" t="s">
+        <v>196</v>
+      </c>
+      <c r="H65" t="s">
+        <v>196</v>
+      </c>
+      <c r="I65" t="s">
+        <v>196</v>
       </c>
       <c r="K65" t="s">
         <v>196</v>
@@ -3729,40 +5127,162 @@
       <c r="A66" s="1" t="s">
         <v>356</v>
       </c>
+      <c r="B66" t="s">
+        <v>196</v>
+      </c>
       <c r="C66" t="s">
         <v>357</v>
+      </c>
+      <c r="D66" t="s">
+        <v>265</v>
+      </c>
+      <c r="E66" t="s">
+        <v>196</v>
+      </c>
+      <c r="F66" t="s">
+        <v>357</v>
+      </c>
+      <c r="G66" t="s">
+        <v>196</v>
+      </c>
+      <c r="H66" t="s">
+        <v>196</v>
+      </c>
+      <c r="I66" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>358</v>
       </c>
+      <c r="B67" t="s">
+        <v>196</v>
+      </c>
       <c r="C67" t="s">
         <v>188</v>
+      </c>
+      <c r="D67" t="s">
+        <v>196</v>
+      </c>
+      <c r="E67" t="s">
+        <v>196</v>
+      </c>
+      <c r="G67" t="s">
+        <v>196</v>
+      </c>
+      <c r="H67" t="s">
+        <v>196</v>
+      </c>
+      <c r="I67" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>359</v>
       </c>
+      <c r="B68" t="s">
+        <v>196</v>
+      </c>
       <c r="C68" t="s">
         <v>189</v>
+      </c>
+      <c r="D68" t="s">
+        <v>196</v>
+      </c>
+      <c r="E68" t="s">
+        <v>196</v>
+      </c>
+      <c r="G68" t="s">
+        <v>196</v>
+      </c>
+      <c r="H68" t="s">
+        <v>196</v>
+      </c>
+      <c r="I68" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>360</v>
       </c>
+      <c r="B69" t="s">
+        <v>196</v>
+      </c>
       <c r="C69" t="s">
         <v>361</v>
+      </c>
+      <c r="D69" t="s">
+        <v>196</v>
+      </c>
+      <c r="E69" t="s">
+        <v>196</v>
+      </c>
+      <c r="F69" t="s">
+        <v>361</v>
+      </c>
+      <c r="G69" t="s">
+        <v>196</v>
+      </c>
+      <c r="H69" t="s">
+        <v>196</v>
+      </c>
+      <c r="I69" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>362</v>
       </c>
+      <c r="B70" t="s">
+        <v>196</v>
+      </c>
       <c r="C70" t="s">
         <v>363</v>
+      </c>
+      <c r="D70" t="s">
+        <v>196</v>
+      </c>
+      <c r="E70" t="s">
+        <v>196</v>
+      </c>
+      <c r="G70" t="s">
+        <v>196</v>
+      </c>
+      <c r="H70" t="s">
+        <v>196</v>
+      </c>
+      <c r="I70" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B71" t="s">
+        <v>196</v>
+      </c>
+      <c r="C71" t="s">
+        <v>196</v>
+      </c>
+      <c r="D71" t="s">
+        <v>374</v>
+      </c>
+      <c r="E71" t="s">
+        <v>196</v>
+      </c>
+      <c r="G71" t="s">
+        <v>196</v>
+      </c>
+      <c r="H71" t="s">
+        <v>196</v>
+      </c>
+      <c r="I71" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/Monadisk overblik.xlsx
+++ b/Monadisk overblik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aaudk-my.sharepoint.com/personal/bo62rk_id_aau_dk/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1122" documentId="8_{6C2A7B69-2C62-4B80-ACF4-E8008D3DDFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F17C4624-94B3-4AC8-B807-EB0B5E8C0666}"/>
+  <xr:revisionPtr revIDLastSave="1422" documentId="8_{6C2A7B69-2C62-4B80-ACF4-E8008D3DDFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08F1E93D-7987-4EBD-9686-2F568BBE61CF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E14E365F-4887-4C07-BAAD-AE51F23AD0DA}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{E14E365F-4887-4C07-BAAD-AE51F23AD0DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="478">
   <si>
     <t>Corona0</t>
   </si>
@@ -944,12 +944,6 @@
     <t>q30</t>
   </si>
   <si>
-    <t>S05_ØB4</t>
-  </si>
-  <si>
-    <t>S05_ØB5</t>
-  </si>
-  <si>
     <t>Q1</t>
   </si>
   <si>
@@ -965,9 +959,6 @@
     <t>Q26</t>
   </si>
   <si>
-    <t>S07_Q20</t>
-  </si>
-  <si>
     <t>Q50</t>
   </si>
   <si>
@@ -1218,6 +1209,270 @@
   </si>
   <si>
     <t>q1_14</t>
+  </si>
+  <si>
+    <t>køn</t>
+  </si>
+  <si>
+    <t>alder</t>
+  </si>
+  <si>
+    <t>stilling</t>
+  </si>
+  <si>
+    <t>uddann</t>
+  </si>
+  <si>
+    <t>hus_indd</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>ØB4</t>
+  </si>
+  <si>
+    <t>GUT2</t>
+  </si>
+  <si>
+    <t>GUT3_01</t>
+  </si>
+  <si>
+    <t>GUT3_02</t>
+  </si>
+  <si>
+    <t>GUT3_03</t>
+  </si>
+  <si>
+    <t>GUT3_05</t>
+  </si>
+  <si>
+    <t>GUT3_08</t>
+  </si>
+  <si>
+    <t>GUT3_09</t>
+  </si>
+  <si>
+    <t>GUT3_12</t>
+  </si>
+  <si>
+    <t>GUT3_16</t>
+  </si>
+  <si>
+    <t>GUT3_17</t>
+  </si>
+  <si>
+    <t>GUT4_01</t>
+  </si>
+  <si>
+    <t>GUT4_02</t>
+  </si>
+  <si>
+    <t>GUT4_05</t>
+  </si>
+  <si>
+    <t>GUT4_03</t>
+  </si>
+  <si>
+    <t>GUT4_04</t>
+  </si>
+  <si>
+    <t>GUT4_06</t>
+  </si>
+  <si>
+    <t>GUT4_07</t>
+  </si>
+  <si>
+    <t>GUT4_08</t>
+  </si>
+  <si>
+    <t>GUT4_09</t>
+  </si>
+  <si>
+    <t>GUT4_10</t>
+  </si>
+  <si>
+    <t>GUT4_11</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>GUT1</t>
+  </si>
+  <si>
+    <t>hus_ind</t>
+  </si>
+  <si>
+    <t>ØB5</t>
+  </si>
+  <si>
+    <t>Q9</t>
+  </si>
+  <si>
+    <t>Q13</t>
+  </si>
+  <si>
+    <t>Q14</t>
+  </si>
+  <si>
+    <t>Q19</t>
+  </si>
+  <si>
+    <t>Q16</t>
+  </si>
+  <si>
+    <t>Q18</t>
+  </si>
+  <si>
+    <t>Q20</t>
+  </si>
+  <si>
+    <t>S09_Q6</t>
+  </si>
+  <si>
+    <t>S09_Q8</t>
+  </si>
+  <si>
+    <t>S09_Q5</t>
+  </si>
+  <si>
+    <t>S09_Q10_1</t>
+  </si>
+  <si>
+    <t>S09_Q12</t>
+  </si>
+  <si>
+    <t>S09_Q14</t>
+  </si>
+  <si>
+    <t>S09_Q16</t>
+  </si>
+  <si>
+    <t>S09_Q17</t>
+  </si>
+  <si>
+    <t>S09_Q38_1</t>
+  </si>
+  <si>
+    <t>S09_Q38_2</t>
+  </si>
+  <si>
+    <t>S09_Q38_3</t>
+  </si>
+  <si>
+    <t>S09_Q38_4</t>
+  </si>
+  <si>
+    <t>S09_Q38_5</t>
+  </si>
+  <si>
+    <t>S09_Q38_6</t>
+  </si>
+  <si>
+    <t>S09_Q38_7</t>
+  </si>
+  <si>
+    <t>S09_Q38_8</t>
+  </si>
+  <si>
+    <t>S09_Q38_10</t>
+  </si>
+  <si>
+    <t>S09_Q38_9</t>
+  </si>
+  <si>
+    <t>Q6</t>
+  </si>
+  <si>
+    <t>Q12</t>
+  </si>
+  <si>
+    <t>Q17</t>
+  </si>
+  <si>
+    <t>S09_Q18</t>
+  </si>
+  <si>
+    <t>Q23</t>
+  </si>
+  <si>
+    <t>Q24</t>
+  </si>
+  <si>
+    <t>Q25_12</t>
+  </si>
+  <si>
+    <t>Q25_2</t>
+  </si>
+  <si>
+    <t>Q25_4</t>
+  </si>
+  <si>
+    <t>Q25_1</t>
+  </si>
+  <si>
+    <t>Q25_3</t>
+  </si>
+  <si>
+    <t>Q25_7</t>
+  </si>
+  <si>
+    <t>Q25_10</t>
+  </si>
+  <si>
+    <t>Q25_9</t>
+  </si>
+  <si>
+    <t>Q25_8</t>
+  </si>
+  <si>
+    <t>Q25_13</t>
+  </si>
+  <si>
+    <t>Q25_14</t>
+  </si>
+  <si>
+    <t>Q25_19</t>
+  </si>
+  <si>
+    <t>Q25_20</t>
+  </si>
+  <si>
+    <t>Q25_17</t>
+  </si>
+  <si>
+    <t>Q25_21</t>
+  </si>
+  <si>
+    <t>Q25_15</t>
+  </si>
+  <si>
+    <t>education</t>
+  </si>
+  <si>
+    <t>q5</t>
+  </si>
+  <si>
+    <t>q12</t>
+  </si>
+  <si>
+    <t>q8</t>
+  </si>
+  <si>
+    <t>q9</t>
+  </si>
+  <si>
+    <t>q11</t>
+  </si>
+  <si>
+    <t>q20</t>
+  </si>
+  <si>
+    <t>q7</t>
   </si>
 </sst>
 </file>
@@ -1781,7 +2036,7 @@
         <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C2" t="s">
         <v>91</v>
@@ -1804,11 +2059,20 @@
       <c r="I2" t="s">
         <v>91</v>
       </c>
+      <c r="J2" t="s">
+        <v>390</v>
+      </c>
+      <c r="K2" t="s">
+        <v>390</v>
+      </c>
       <c r="L2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="M2" t="s">
-        <v>310</v>
+        <v>307</v>
+      </c>
+      <c r="N2" t="s">
+        <v>40</v>
       </c>
       <c r="O2" t="s">
         <v>91</v>
@@ -1843,7 +2107,7 @@
         <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C3" t="s">
         <v>92</v>
@@ -1866,11 +2130,20 @@
       <c r="I3" t="s">
         <v>92</v>
       </c>
+      <c r="J3" t="s">
+        <v>391</v>
+      </c>
+      <c r="K3" t="s">
+        <v>391</v>
+      </c>
       <c r="L3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="M3" t="s">
-        <v>311</v>
+        <v>308</v>
+      </c>
+      <c r="N3" t="s">
+        <v>41</v>
       </c>
       <c r="O3" t="s">
         <v>92</v>
@@ -1905,28 +2178,52 @@
         <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="I4" t="s">
-        <v>346</v>
+        <v>343</v>
+      </c>
+      <c r="J4" t="s">
+        <v>393</v>
+      </c>
+      <c r="K4" t="s">
+        <v>393</v>
+      </c>
+      <c r="L4" t="s">
+        <v>423</v>
+      </c>
+      <c r="M4" t="s">
+        <v>430</v>
+      </c>
+      <c r="N4" t="s">
+        <v>448</v>
+      </c>
+      <c r="O4" t="s">
+        <v>470</v>
+      </c>
+      <c r="P4" t="s">
+        <v>470</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
@@ -1937,25 +2234,49 @@
         <v>196</v>
       </c>
       <c r="C5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E5" t="s">
         <v>196</v>
       </c>
       <c r="F5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H5" t="s">
         <v>196</v>
       </c>
       <c r="I5" t="s">
         <v>196</v>
+      </c>
+      <c r="J5" t="s">
+        <v>392</v>
+      </c>
+      <c r="K5" t="s">
+        <v>392</v>
+      </c>
+      <c r="L5" t="s">
+        <v>424</v>
+      </c>
+      <c r="M5" t="s">
+        <v>431</v>
+      </c>
+      <c r="N5" t="s">
+        <v>196</v>
+      </c>
+      <c r="O5" t="s">
+        <v>473</v>
+      </c>
+      <c r="P5" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
@@ -1963,13 +2284,13 @@
         <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E6" t="s">
         <v>196</v>
@@ -1985,6 +2306,30 @@
       </c>
       <c r="I6" t="s">
         <v>196</v>
+      </c>
+      <c r="J6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K6" t="s">
+        <v>196</v>
+      </c>
+      <c r="L6" t="s">
+        <v>425</v>
+      </c>
+      <c r="M6" t="s">
+        <v>433</v>
+      </c>
+      <c r="N6" t="s">
+        <v>196</v>
+      </c>
+      <c r="O6" t="s">
+        <v>474</v>
+      </c>
+      <c r="P6" t="s">
+        <v>474</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
@@ -1995,25 +2340,49 @@
         <v>196</v>
       </c>
       <c r="C7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I7" t="s">
-        <v>348</v>
+        <v>345</v>
+      </c>
+      <c r="J7" t="s">
+        <v>196</v>
+      </c>
+      <c r="K7" t="s">
+        <v>196</v>
+      </c>
+      <c r="L7" t="s">
+        <v>196</v>
+      </c>
+      <c r="M7" t="s">
+        <v>196</v>
+      </c>
+      <c r="N7" t="s">
+        <v>196</v>
+      </c>
+      <c r="O7" t="s">
+        <v>345</v>
+      </c>
+      <c r="P7" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.25">
@@ -2024,25 +2393,46 @@
         <v>196</v>
       </c>
       <c r="C8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="G8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H8" t="s">
         <v>196</v>
       </c>
       <c r="I8" t="s">
         <v>196</v>
+      </c>
+      <c r="J8" t="s">
+        <v>396</v>
+      </c>
+      <c r="L8" t="s">
+        <v>426</v>
+      </c>
+      <c r="M8" t="s">
+        <v>432</v>
+      </c>
+      <c r="N8" t="s">
+        <v>196</v>
+      </c>
+      <c r="O8" t="s">
+        <v>471</v>
+      </c>
+      <c r="P8" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
@@ -2068,10 +2458,34 @@
         <v>196</v>
       </c>
       <c r="H9" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="I9" t="s">
         <v>196</v>
+      </c>
+      <c r="J9" t="s">
+        <v>196</v>
+      </c>
+      <c r="K9" t="s">
+        <v>196</v>
+      </c>
+      <c r="L9" t="s">
+        <v>196</v>
+      </c>
+      <c r="M9" t="s">
+        <v>434</v>
+      </c>
+      <c r="N9" t="s">
+        <v>449</v>
+      </c>
+      <c r="O9" t="s">
+        <v>344</v>
+      </c>
+      <c r="P9" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
@@ -2079,10 +2493,10 @@
         <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D10" t="s">
         <v>196</v>
@@ -2094,13 +2508,37 @@
         <v>196</v>
       </c>
       <c r="G10" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="H10" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I10" t="s">
         <v>196</v>
+      </c>
+      <c r="J10" t="s">
+        <v>394</v>
+      </c>
+      <c r="K10" t="s">
+        <v>421</v>
+      </c>
+      <c r="L10" t="s">
+        <v>427</v>
+      </c>
+      <c r="M10" t="s">
+        <v>435</v>
+      </c>
+      <c r="N10" t="s">
+        <v>196</v>
+      </c>
+      <c r="O10" t="s">
+        <v>472</v>
+      </c>
+      <c r="P10" t="s">
+        <v>472</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
@@ -2108,19 +2546,19 @@
         <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C11" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D11" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E11" t="s">
         <v>196</v>
       </c>
       <c r="F11" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G11" t="s">
         <v>196</v>
@@ -2130,6 +2568,30 @@
       </c>
       <c r="I11" t="s">
         <v>196</v>
+      </c>
+      <c r="J11" t="s">
+        <v>196</v>
+      </c>
+      <c r="K11" t="s">
+        <v>196</v>
+      </c>
+      <c r="L11" t="s">
+        <v>196</v>
+      </c>
+      <c r="M11" t="s">
+        <v>437</v>
+      </c>
+      <c r="N11" t="s">
+        <v>450</v>
+      </c>
+      <c r="O11" t="s">
+        <v>351</v>
+      </c>
+      <c r="P11" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
@@ -2140,16 +2602,16 @@
         <v>196</v>
       </c>
       <c r="C12" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D12" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E12" t="s">
         <v>196</v>
       </c>
       <c r="F12" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G12" t="s">
         <v>196</v>
@@ -2158,6 +2620,30 @@
         <v>196</v>
       </c>
       <c r="I12" t="s">
+        <v>196</v>
+      </c>
+      <c r="J12" t="s">
+        <v>395</v>
+      </c>
+      <c r="K12" t="s">
+        <v>196</v>
+      </c>
+      <c r="L12" t="s">
+        <v>428</v>
+      </c>
+      <c r="M12" t="s">
+        <v>436</v>
+      </c>
+      <c r="N12" t="s">
+        <v>427</v>
+      </c>
+      <c r="O12" t="s">
+        <v>316</v>
+      </c>
+      <c r="P12" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q12" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2166,22 +2652,22 @@
         <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C13" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D13" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E13" t="s">
         <v>196</v>
       </c>
       <c r="F13" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G13" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H13" t="s">
         <v>196</v>
@@ -2189,41 +2675,47 @@
       <c r="I13" t="s">
         <v>196</v>
       </c>
+      <c r="J13" t="s">
+        <v>196</v>
+      </c>
       <c r="K13" t="s">
-        <v>302</v>
+        <v>422</v>
       </c>
       <c r="L13" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="M13" t="s">
-        <v>314</v>
+        <v>311</v>
+      </c>
+      <c r="N13" t="s">
+        <v>196</v>
       </c>
       <c r="O13" t="s">
+        <v>317</v>
+      </c>
+      <c r="P13" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q13" t="s">
         <v>320</v>
       </c>
-      <c r="P13" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>323</v>
-      </c>
       <c r="R13" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="S13" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="U13" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="V13" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="W13" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="X13" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.25">
@@ -2254,17 +2746,26 @@
       <c r="I14" t="s">
         <v>196</v>
       </c>
+      <c r="J14" t="s">
+        <v>397</v>
+      </c>
       <c r="K14" t="s">
-        <v>301</v>
+        <v>397</v>
       </c>
       <c r="L14" t="s">
-        <v>308</v>
+        <v>429</v>
+      </c>
+      <c r="M14" t="s">
+        <v>451</v>
+      </c>
+      <c r="N14" t="s">
+        <v>428</v>
       </c>
       <c r="O14" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="P14" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="Q14" t="s">
         <v>300</v>
@@ -2287,10 +2788,10 @@
         <v>196</v>
       </c>
       <c r="C15" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D15" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E15" t="s">
         <v>196</v>
@@ -2307,35 +2808,47 @@
       <c r="I15" t="s">
         <v>196</v>
       </c>
+      <c r="J15" t="s">
+        <v>419</v>
+      </c>
+      <c r="K15" t="s">
+        <v>419</v>
+      </c>
+      <c r="L15" t="s">
+        <v>419</v>
+      </c>
       <c r="M15" t="s">
+        <v>323</v>
+      </c>
+      <c r="N15" t="s">
+        <v>196</v>
+      </c>
+      <c r="O15" t="s">
+        <v>324</v>
+      </c>
+      <c r="P15" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q15" t="s">
         <v>326</v>
       </c>
-      <c r="O15" t="s">
-        <v>327</v>
-      </c>
-      <c r="P15" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>329</v>
-      </c>
       <c r="R15" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="S15" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="U15" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="W15" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="AE15" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="AF15" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
@@ -2346,16 +2859,16 @@
         <v>196</v>
       </c>
       <c r="C16" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D16" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E16" t="s">
         <v>196</v>
       </c>
       <c r="F16" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G16" t="s">
         <v>196</v>
@@ -2364,6 +2877,30 @@
         <v>196</v>
       </c>
       <c r="I16" t="s">
+        <v>196</v>
+      </c>
+      <c r="J16" t="s">
+        <v>196</v>
+      </c>
+      <c r="K16" t="s">
+        <v>196</v>
+      </c>
+      <c r="L16" t="s">
+        <v>196</v>
+      </c>
+      <c r="M16" t="s">
+        <v>438</v>
+      </c>
+      <c r="N16" t="s">
+        <v>196</v>
+      </c>
+      <c r="O16" t="s">
+        <v>196</v>
+      </c>
+      <c r="P16" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q16" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2375,16 +2912,16 @@
         <v>196</v>
       </c>
       <c r="C17" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D17" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E17" t="s">
         <v>196</v>
       </c>
       <c r="F17" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G17" t="s">
         <v>196</v>
@@ -2393,6 +2930,30 @@
         <v>196</v>
       </c>
       <c r="I17" t="s">
+        <v>196</v>
+      </c>
+      <c r="J17" t="s">
+        <v>196</v>
+      </c>
+      <c r="K17" t="s">
+        <v>196</v>
+      </c>
+      <c r="L17" t="s">
+        <v>196</v>
+      </c>
+      <c r="M17" t="s">
+        <v>439</v>
+      </c>
+      <c r="N17" t="s">
+        <v>196</v>
+      </c>
+      <c r="O17" t="s">
+        <v>196</v>
+      </c>
+      <c r="P17" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q17" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2404,16 +2965,16 @@
         <v>196</v>
       </c>
       <c r="C18" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D18" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E18" t="s">
         <v>196</v>
       </c>
       <c r="F18" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G18" t="s">
         <v>196</v>
@@ -2422,6 +2983,30 @@
         <v>196</v>
       </c>
       <c r="I18" t="s">
+        <v>196</v>
+      </c>
+      <c r="J18" t="s">
+        <v>196</v>
+      </c>
+      <c r="K18" t="s">
+        <v>196</v>
+      </c>
+      <c r="L18" t="s">
+        <v>196</v>
+      </c>
+      <c r="M18" t="s">
+        <v>440</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="O18" t="s">
+        <v>196</v>
+      </c>
+      <c r="P18" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q18" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2436,13 +3021,13 @@
         <v>196</v>
       </c>
       <c r="D19" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E19" t="s">
         <v>196</v>
       </c>
       <c r="F19" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G19" t="s">
         <v>196</v>
@@ -2451,6 +3036,30 @@
         <v>196</v>
       </c>
       <c r="I19" t="s">
+        <v>196</v>
+      </c>
+      <c r="J19" t="s">
+        <v>196</v>
+      </c>
+      <c r="K19" t="s">
+        <v>196</v>
+      </c>
+      <c r="L19" t="s">
+        <v>196</v>
+      </c>
+      <c r="M19" t="s">
+        <v>441</v>
+      </c>
+      <c r="N19" t="s">
+        <v>196</v>
+      </c>
+      <c r="O19" t="s">
+        <v>196</v>
+      </c>
+      <c r="P19" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q19" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2465,13 +3074,13 @@
         <v>196</v>
       </c>
       <c r="D20" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E20" t="s">
         <v>196</v>
       </c>
       <c r="F20" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="G20" t="s">
         <v>196</v>
@@ -2480,6 +3089,30 @@
         <v>196</v>
       </c>
       <c r="I20" t="s">
+        <v>196</v>
+      </c>
+      <c r="J20" t="s">
+        <v>196</v>
+      </c>
+      <c r="K20" t="s">
+        <v>196</v>
+      </c>
+      <c r="L20" t="s">
+        <v>196</v>
+      </c>
+      <c r="M20" t="s">
+        <v>442</v>
+      </c>
+      <c r="N20" t="s">
+        <v>196</v>
+      </c>
+      <c r="O20" t="s">
+        <v>196</v>
+      </c>
+      <c r="P20" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q20" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2491,16 +3124,16 @@
         <v>196</v>
       </c>
       <c r="C21" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D21" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E21" t="s">
         <v>196</v>
       </c>
       <c r="F21" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G21" t="s">
         <v>196</v>
@@ -2509,6 +3142,30 @@
         <v>196</v>
       </c>
       <c r="I21" t="s">
+        <v>196</v>
+      </c>
+      <c r="J21" t="s">
+        <v>196</v>
+      </c>
+      <c r="K21" t="s">
+        <v>196</v>
+      </c>
+      <c r="L21" t="s">
+        <v>196</v>
+      </c>
+      <c r="M21" t="s">
+        <v>443</v>
+      </c>
+      <c r="N21" t="s">
+        <v>196</v>
+      </c>
+      <c r="O21" t="s">
+        <v>196</v>
+      </c>
+      <c r="P21" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q21" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2523,13 +3180,13 @@
         <v>196</v>
       </c>
       <c r="D22" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E22" t="s">
         <v>196</v>
       </c>
       <c r="F22" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G22" t="s">
         <v>196</v>
@@ -2538,6 +3195,30 @@
         <v>196</v>
       </c>
       <c r="I22" t="s">
+        <v>196</v>
+      </c>
+      <c r="J22" t="s">
+        <v>196</v>
+      </c>
+      <c r="K22" t="s">
+        <v>196</v>
+      </c>
+      <c r="L22" t="s">
+        <v>196</v>
+      </c>
+      <c r="M22" t="s">
+        <v>444</v>
+      </c>
+      <c r="N22" t="s">
+        <v>196</v>
+      </c>
+      <c r="O22" t="s">
+        <v>196</v>
+      </c>
+      <c r="P22" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q22" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2569,6 +3250,30 @@
       <c r="I23" t="s">
         <v>196</v>
       </c>
+      <c r="J23" t="s">
+        <v>196</v>
+      </c>
+      <c r="K23" t="s">
+        <v>196</v>
+      </c>
+      <c r="L23" t="s">
+        <v>196</v>
+      </c>
+      <c r="M23" t="s">
+        <v>445</v>
+      </c>
+      <c r="N23" t="s">
+        <v>196</v>
+      </c>
+      <c r="O23" t="s">
+        <v>196</v>
+      </c>
+      <c r="P23" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -2581,13 +3286,13 @@
         <v>196</v>
       </c>
       <c r="D24" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E24" t="s">
         <v>196</v>
       </c>
       <c r="F24" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="G24" t="s">
         <v>196</v>
@@ -2596,6 +3301,30 @@
         <v>196</v>
       </c>
       <c r="I24" t="s">
+        <v>196</v>
+      </c>
+      <c r="J24" t="s">
+        <v>196</v>
+      </c>
+      <c r="K24" t="s">
+        <v>196</v>
+      </c>
+      <c r="L24" t="s">
+        <v>196</v>
+      </c>
+      <c r="M24" t="s">
+        <v>447</v>
+      </c>
+      <c r="N24" t="s">
+        <v>196</v>
+      </c>
+      <c r="O24" t="s">
+        <v>196</v>
+      </c>
+      <c r="P24" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q24" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2610,13 +3339,13 @@
         <v>196</v>
       </c>
       <c r="D25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E25" t="s">
         <v>196</v>
       </c>
       <c r="F25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="G25" t="s">
         <v>196</v>
@@ -2625,6 +3354,30 @@
         <v>196</v>
       </c>
       <c r="I25" t="s">
+        <v>196</v>
+      </c>
+      <c r="J25" t="s">
+        <v>196</v>
+      </c>
+      <c r="K25" t="s">
+        <v>196</v>
+      </c>
+      <c r="L25" t="s">
+        <v>196</v>
+      </c>
+      <c r="M25" t="s">
+        <v>446</v>
+      </c>
+      <c r="N25" t="s">
+        <v>196</v>
+      </c>
+      <c r="O25" t="s">
+        <v>196</v>
+      </c>
+      <c r="P25" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q25" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2633,64 +3386,73 @@
         <v>64</v>
       </c>
       <c r="B26" t="s">
+        <v>327</v>
+      </c>
+      <c r="C26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D26" t="s">
+        <v>328</v>
+      </c>
+      <c r="E26" t="s">
+        <v>196</v>
+      </c>
+      <c r="F26" t="s">
+        <v>328</v>
+      </c>
+      <c r="G26" t="s">
+        <v>328</v>
+      </c>
+      <c r="H26" t="s">
+        <v>196</v>
+      </c>
+      <c r="I26" t="s">
+        <v>196</v>
+      </c>
+      <c r="J26" t="s">
+        <v>196</v>
+      </c>
+      <c r="K26" t="s">
+        <v>196</v>
+      </c>
+      <c r="L26" t="s">
+        <v>329</v>
+      </c>
+      <c r="M26" t="s">
         <v>330</v>
       </c>
-      <c r="C26" t="s">
-        <v>196</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="N26" t="s">
+        <v>196</v>
+      </c>
+      <c r="O26" t="s">
         <v>331</v>
       </c>
-      <c r="E26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F26" t="s">
-        <v>331</v>
-      </c>
-      <c r="G26" t="s">
-        <v>331</v>
-      </c>
-      <c r="H26" t="s">
-        <v>196</v>
-      </c>
-      <c r="I26" t="s">
-        <v>196</v>
-      </c>
-      <c r="L26" t="s">
+      <c r="P26" t="s">
         <v>332</v>
       </c>
-      <c r="M26" t="s">
+      <c r="Q26" t="s">
         <v>333</v>
       </c>
-      <c r="O26" t="s">
+      <c r="R26" t="s">
         <v>334</v>
       </c>
-      <c r="P26" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>336</v>
-      </c>
-      <c r="R26" t="s">
-        <v>337</v>
-      </c>
       <c r="S26" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="U26" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="X26" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AE26" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AF26" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AG26" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
@@ -2710,7 +3472,7 @@
         <v>196</v>
       </c>
       <c r="F27" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G27" t="s">
         <v>196</v>
@@ -2720,26 +3482,50 @@
       </c>
       <c r="I27" t="s">
         <v>196</v>
+      </c>
+      <c r="J27" t="s">
+        <v>196</v>
+      </c>
+      <c r="K27" t="s">
+        <v>196</v>
+      </c>
+      <c r="L27" t="s">
+        <v>196</v>
+      </c>
+      <c r="M27" t="s">
+        <v>196</v>
+      </c>
+      <c r="N27" t="s">
+        <v>196</v>
+      </c>
+      <c r="O27" t="s">
+        <v>196</v>
+      </c>
+      <c r="P27" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B28" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C28" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D28" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E28" t="s">
         <v>196</v>
       </c>
       <c r="F28" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G28" t="s">
         <v>196</v>
@@ -2750,38 +3536,47 @@
       <c r="I28" t="s">
         <v>196</v>
       </c>
+      <c r="J28" t="s">
+        <v>420</v>
+      </c>
+      <c r="K28" t="s">
+        <v>420</v>
+      </c>
       <c r="L28" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M28" t="s">
+        <v>309</v>
+      </c>
+      <c r="N28" t="s">
+        <v>452</v>
+      </c>
+      <c r="O28" t="s">
         <v>312</v>
       </c>
-      <c r="O28" t="s">
-        <v>315</v>
-      </c>
       <c r="P28" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Q28" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="R28" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="S28" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="U28" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="V28" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="W28" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="X28" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
@@ -2812,38 +3607,47 @@
       <c r="I29" t="s">
         <v>196</v>
       </c>
+      <c r="J29" t="s">
+        <v>398</v>
+      </c>
+      <c r="K29" t="s">
+        <v>398</v>
+      </c>
       <c r="L29" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="M29" t="s">
+        <v>310</v>
+      </c>
+      <c r="N29" t="s">
+        <v>453</v>
+      </c>
+      <c r="O29" t="s">
         <v>313</v>
       </c>
-      <c r="O29" t="s">
-        <v>316</v>
-      </c>
       <c r="P29" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="Q29" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="R29" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="S29" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="U29" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="V29" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="W29" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="X29" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
@@ -2869,10 +3673,13 @@
         <v>196</v>
       </c>
       <c r="H30" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="I30" t="s">
-        <v>382</v>
+        <v>379</v>
+      </c>
+      <c r="J30" t="s">
+        <v>407</v>
       </c>
       <c r="K30" t="s">
         <v>203</v>
@@ -2882,6 +3689,9 @@
       </c>
       <c r="M30" t="s">
         <v>217</v>
+      </c>
+      <c r="N30" t="s">
+        <v>463</v>
       </c>
       <c r="O30" t="s">
         <v>241</v>
@@ -2934,10 +3744,13 @@
         <v>264</v>
       </c>
       <c r="H31" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="I31" t="s">
-        <v>389</v>
+        <v>386</v>
+      </c>
+      <c r="J31" t="s">
+        <v>400</v>
       </c>
       <c r="K31" t="s">
         <v>198</v>
@@ -2947,6 +3760,9 @@
       </c>
       <c r="M31" t="s">
         <v>212</v>
+      </c>
+      <c r="N31" t="s">
+        <v>455</v>
       </c>
       <c r="O31" t="s">
         <v>236</v>
@@ -3001,6 +3817,9 @@
       <c r="I32" t="s">
         <v>196</v>
       </c>
+      <c r="J32" t="s">
+        <v>402</v>
+      </c>
       <c r="K32" t="s">
         <v>283</v>
       </c>
@@ -3009,6 +3828,9 @@
       </c>
       <c r="M32" t="s">
         <v>289</v>
+      </c>
+      <c r="N32" t="s">
+        <v>456</v>
       </c>
       <c r="O32" t="s">
         <v>291</v>
@@ -3058,10 +3880,13 @@
         <v>263</v>
       </c>
       <c r="H33" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I33" t="s">
-        <v>378</v>
+        <v>375</v>
+      </c>
+      <c r="J33" t="s">
+        <v>399</v>
       </c>
       <c r="K33" t="s">
         <v>197</v>
@@ -3071,6 +3896,9 @@
       </c>
       <c r="M33" t="s">
         <v>211</v>
+      </c>
+      <c r="N33" t="s">
+        <v>457</v>
       </c>
       <c r="O33" t="s">
         <v>235</v>
@@ -3123,10 +3951,13 @@
         <v>196</v>
       </c>
       <c r="H34" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I34" t="s">
-        <v>379</v>
+        <v>376</v>
+      </c>
+      <c r="J34" t="s">
+        <v>401</v>
       </c>
       <c r="K34" t="s">
         <v>199</v>
@@ -3136,6 +3967,9 @@
       </c>
       <c r="M34" t="s">
         <v>213</v>
+      </c>
+      <c r="N34" t="s">
+        <v>458</v>
       </c>
       <c r="O34" t="s">
         <v>237</v>
@@ -3190,6 +4024,9 @@
       <c r="I35" t="s">
         <v>196</v>
       </c>
+      <c r="J35" t="s">
+        <v>403</v>
+      </c>
       <c r="K35" t="s">
         <v>284</v>
       </c>
@@ -3198,6 +4035,9 @@
       </c>
       <c r="M35" t="s">
         <v>290</v>
+      </c>
+      <c r="N35" t="s">
+        <v>459</v>
       </c>
       <c r="O35" t="s">
         <v>292</v>
@@ -3247,10 +4087,13 @@
         <v>196</v>
       </c>
       <c r="H36" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="I36" t="s">
-        <v>381</v>
+        <v>378</v>
+      </c>
+      <c r="J36" t="s">
+        <v>405</v>
       </c>
       <c r="K36" t="s">
         <v>202</v>
@@ -3260,6 +4103,9 @@
       </c>
       <c r="M36" t="s">
         <v>216</v>
+      </c>
+      <c r="N36" t="s">
+        <v>460</v>
       </c>
       <c r="O36" t="s">
         <v>240</v>
@@ -3309,10 +4155,13 @@
         <v>266</v>
       </c>
       <c r="H37" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I37" t="s">
-        <v>380</v>
+        <v>377</v>
+      </c>
+      <c r="J37" t="s">
+        <v>285</v>
       </c>
       <c r="K37" t="s">
         <v>201</v>
@@ -3322,6 +4171,9 @@
       </c>
       <c r="M37" t="s">
         <v>215</v>
+      </c>
+      <c r="N37" t="s">
+        <v>461</v>
       </c>
       <c r="O37" t="s">
         <v>239</v>
@@ -3379,6 +4231,9 @@
       <c r="I38" t="s">
         <v>196</v>
       </c>
+      <c r="J38" t="s">
+        <v>404</v>
+      </c>
       <c r="K38" t="s">
         <v>200</v>
       </c>
@@ -3387,6 +4242,9 @@
       </c>
       <c r="M38" t="s">
         <v>214</v>
+      </c>
+      <c r="N38" t="s">
+        <v>462</v>
       </c>
       <c r="O38" t="s">
         <v>238</v>
@@ -3441,6 +4299,9 @@
       <c r="I39" t="s">
         <v>196</v>
       </c>
+      <c r="J39" t="s">
+        <v>406</v>
+      </c>
       <c r="K39" t="s">
         <v>285</v>
       </c>
@@ -3449,6 +4310,9 @@
       </c>
       <c r="M39" t="s">
         <v>290</v>
+      </c>
+      <c r="N39" t="s">
+        <v>454</v>
       </c>
       <c r="O39" t="s">
         <v>293</v>
@@ -3501,7 +4365,10 @@
         <v>196</v>
       </c>
       <c r="I40" t="s">
-        <v>390</v>
+        <v>387</v>
+      </c>
+      <c r="J40" t="s">
+        <v>196</v>
       </c>
       <c r="K40" t="s">
         <v>196</v>
@@ -3511,6 +4378,9 @@
       </c>
       <c r="M40" t="s">
         <v>228</v>
+      </c>
+      <c r="N40" t="s">
+        <v>464</v>
       </c>
       <c r="O40" t="s">
         <v>242</v>
@@ -3565,6 +4435,9 @@
       <c r="I41" t="s">
         <v>196</v>
       </c>
+      <c r="J41" t="s">
+        <v>196</v>
+      </c>
       <c r="K41" t="s">
         <v>196</v>
       </c>
@@ -3573,6 +4446,9 @@
       </c>
       <c r="M41" t="s">
         <v>229</v>
+      </c>
+      <c r="N41" t="s">
+        <v>469</v>
       </c>
       <c r="O41" t="s">
         <v>243</v>
@@ -3619,10 +4495,13 @@
         <v>196</v>
       </c>
       <c r="H42" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="I42" t="s">
-        <v>384</v>
+        <v>381</v>
+      </c>
+      <c r="J42" t="s">
+        <v>196</v>
       </c>
       <c r="K42" t="s">
         <v>196</v>
@@ -3632,6 +4511,9 @@
       </c>
       <c r="M42" t="s">
         <v>230</v>
+      </c>
+      <c r="N42" t="s">
+        <v>467</v>
       </c>
       <c r="O42" t="s">
         <v>244</v>
@@ -3681,7 +4563,10 @@
         <v>196</v>
       </c>
       <c r="I43" t="s">
-        <v>391</v>
+        <v>388</v>
+      </c>
+      <c r="J43" t="s">
+        <v>196</v>
       </c>
       <c r="K43" t="s">
         <v>196</v>
@@ -3691,6 +4576,9 @@
       </c>
       <c r="M43" t="s">
         <v>233</v>
+      </c>
+      <c r="N43" t="s">
+        <v>465</v>
       </c>
       <c r="O43" t="s">
         <v>245</v>
@@ -3740,10 +4628,13 @@
         <v>271</v>
       </c>
       <c r="H44" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I44" t="s">
-        <v>385</v>
+        <v>382</v>
+      </c>
+      <c r="J44" t="s">
+        <v>196</v>
       </c>
       <c r="K44" t="s">
         <v>196</v>
@@ -3753,6 +4644,9 @@
       </c>
       <c r="M44" t="s">
         <v>231</v>
+      </c>
+      <c r="N44" t="s">
+        <v>466</v>
       </c>
       <c r="O44" t="s">
         <v>246</v>
@@ -3810,6 +4704,9 @@
       <c r="I45" t="s">
         <v>196</v>
       </c>
+      <c r="J45" t="s">
+        <v>196</v>
+      </c>
       <c r="K45" t="s">
         <v>196</v>
       </c>
@@ -3818,6 +4715,9 @@
       </c>
       <c r="M45" t="s">
         <v>234</v>
+      </c>
+      <c r="N45" t="s">
+        <v>468</v>
       </c>
       <c r="O45" t="s">
         <v>247</v>
@@ -3870,10 +4770,13 @@
         <v>272</v>
       </c>
       <c r="H46" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="I46" t="s">
-        <v>386</v>
+        <v>383</v>
+      </c>
+      <c r="J46" t="s">
+        <v>196</v>
       </c>
       <c r="K46" t="s">
         <v>196</v>
@@ -3882,6 +4785,9 @@
         <v>196</v>
       </c>
       <c r="M46" t="s">
+        <v>196</v>
+      </c>
+      <c r="N46" t="s">
         <v>196</v>
       </c>
       <c r="O46" t="s">
@@ -3935,10 +4841,13 @@
         <v>273</v>
       </c>
       <c r="H47" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I47" t="s">
-        <v>392</v>
+        <v>389</v>
+      </c>
+      <c r="J47" t="s">
+        <v>196</v>
       </c>
       <c r="K47" t="s">
         <v>196</v>
@@ -3947,6 +4856,9 @@
         <v>196</v>
       </c>
       <c r="M47" t="s">
+        <v>196</v>
+      </c>
+      <c r="N47" t="s">
         <v>196</v>
       </c>
       <c r="O47" t="s">
@@ -4000,10 +4912,13 @@
         <v>276</v>
       </c>
       <c r="H48" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="I48" t="s">
-        <v>387</v>
+        <v>384</v>
+      </c>
+      <c r="J48" t="s">
+        <v>196</v>
       </c>
       <c r="K48" t="s">
         <v>196</v>
@@ -4012,6 +4927,9 @@
         <v>196</v>
       </c>
       <c r="M48" t="s">
+        <v>196</v>
+      </c>
+      <c r="N48" t="s">
         <v>196</v>
       </c>
       <c r="O48" t="s">
@@ -4065,10 +4983,13 @@
         <v>277</v>
       </c>
       <c r="H49" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I49" t="s">
-        <v>388</v>
+        <v>385</v>
+      </c>
+      <c r="J49" t="s">
+        <v>196</v>
       </c>
       <c r="K49" t="s">
         <v>196</v>
@@ -4077,6 +4998,9 @@
         <v>196</v>
       </c>
       <c r="M49" t="s">
+        <v>196</v>
+      </c>
+      <c r="N49" t="s">
         <v>196</v>
       </c>
       <c r="O49" t="s">
@@ -4130,10 +5054,13 @@
         <v>270</v>
       </c>
       <c r="H50" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I50" t="s">
-        <v>383</v>
+        <v>380</v>
+      </c>
+      <c r="J50" t="s">
+        <v>196</v>
       </c>
       <c r="K50" t="s">
         <v>196</v>
@@ -4142,6 +5069,9 @@
         <v>196</v>
       </c>
       <c r="M50" t="s">
+        <v>196</v>
+      </c>
+      <c r="N50" t="s">
         <v>196</v>
       </c>
       <c r="O50" t="s">
@@ -4200,6 +5130,9 @@
       <c r="I51" t="s">
         <v>196</v>
       </c>
+      <c r="J51" t="s">
+        <v>414</v>
+      </c>
       <c r="K51" t="s">
         <v>93</v>
       </c>
@@ -4208,6 +5141,9 @@
       </c>
       <c r="M51" t="s">
         <v>121</v>
+      </c>
+      <c r="N51" t="s">
+        <v>196</v>
       </c>
       <c r="O51" t="s">
         <v>137</v>
@@ -4262,6 +5198,9 @@
       <c r="I52" t="s">
         <v>196</v>
       </c>
+      <c r="J52" t="s">
+        <v>418</v>
+      </c>
       <c r="K52" t="s">
         <v>94</v>
       </c>
@@ -4270,6 +5209,9 @@
       </c>
       <c r="M52" t="s">
         <v>122</v>
+      </c>
+      <c r="N52" t="s">
+        <v>196</v>
       </c>
       <c r="O52" t="s">
         <v>138</v>
@@ -4327,6 +5269,9 @@
       <c r="I53" t="s">
         <v>196</v>
       </c>
+      <c r="J53" t="s">
+        <v>409</v>
+      </c>
       <c r="K53" t="s">
         <v>95</v>
       </c>
@@ -4335,6 +5280,9 @@
       </c>
       <c r="M53" t="s">
         <v>123</v>
+      </c>
+      <c r="N53" t="s">
+        <v>196</v>
       </c>
       <c r="O53" t="s">
         <v>139</v>
@@ -4389,6 +5337,9 @@
       <c r="I54" t="s">
         <v>196</v>
       </c>
+      <c r="J54" t="s">
+        <v>196</v>
+      </c>
       <c r="K54" t="s">
         <v>96</v>
       </c>
@@ -4397,6 +5348,9 @@
       </c>
       <c r="M54" t="s">
         <v>124</v>
+      </c>
+      <c r="N54" t="s">
+        <v>196</v>
       </c>
       <c r="O54" t="s">
         <v>140</v>
@@ -4454,6 +5408,9 @@
       <c r="I55" t="s">
         <v>196</v>
       </c>
+      <c r="J55" t="s">
+        <v>410</v>
+      </c>
       <c r="K55" t="s">
         <v>97</v>
       </c>
@@ -4462,6 +5419,9 @@
       </c>
       <c r="M55" t="s">
         <v>125</v>
+      </c>
+      <c r="N55" t="s">
+        <v>196</v>
       </c>
       <c r="O55" t="s">
         <v>141</v>
@@ -4516,6 +5476,9 @@
       <c r="I56" t="s">
         <v>196</v>
       </c>
+      <c r="J56" t="s">
+        <v>417</v>
+      </c>
       <c r="K56" t="s">
         <v>98</v>
       </c>
@@ -4524,6 +5487,9 @@
       </c>
       <c r="M56" t="s">
         <v>126</v>
+      </c>
+      <c r="N56" t="s">
+        <v>196</v>
       </c>
       <c r="O56" t="s">
         <v>142</v>
@@ -4581,6 +5547,9 @@
       <c r="I57" t="s">
         <v>196</v>
       </c>
+      <c r="J57" t="s">
+        <v>408</v>
+      </c>
       <c r="K57" t="s">
         <v>99</v>
       </c>
@@ -4589,6 +5558,9 @@
       </c>
       <c r="M57" t="s">
         <v>127</v>
+      </c>
+      <c r="N57" t="s">
+        <v>196</v>
       </c>
       <c r="O57" t="s">
         <v>143</v>
@@ -4643,6 +5615,9 @@
       <c r="I58" t="s">
         <v>196</v>
       </c>
+      <c r="J58" t="s">
+        <v>411</v>
+      </c>
       <c r="K58" t="s">
         <v>100</v>
       </c>
@@ -4651,6 +5626,9 @@
       </c>
       <c r="M58" t="s">
         <v>128</v>
+      </c>
+      <c r="N58" t="s">
+        <v>196</v>
       </c>
       <c r="O58" t="s">
         <v>144</v>
@@ -4708,6 +5686,9 @@
       <c r="I59" t="s">
         <v>196</v>
       </c>
+      <c r="J59" t="s">
+        <v>412</v>
+      </c>
       <c r="K59" t="s">
         <v>101</v>
       </c>
@@ -4716,6 +5697,9 @@
       </c>
       <c r="M59" t="s">
         <v>129</v>
+      </c>
+      <c r="N59" t="s">
+        <v>196</v>
       </c>
       <c r="O59" t="s">
         <v>145</v>
@@ -4773,6 +5757,9 @@
       <c r="I60" t="s">
         <v>196</v>
       </c>
+      <c r="J60" t="s">
+        <v>413</v>
+      </c>
       <c r="K60" t="s">
         <v>102</v>
       </c>
@@ -4781,6 +5768,9 @@
       </c>
       <c r="M60" t="s">
         <v>130</v>
+      </c>
+      <c r="N60" t="s">
+        <v>196</v>
       </c>
       <c r="O60" t="s">
         <v>146</v>
@@ -4835,6 +5825,9 @@
       <c r="I61" t="s">
         <v>196</v>
       </c>
+      <c r="J61" t="s">
+        <v>416</v>
+      </c>
       <c r="K61" t="s">
         <v>103</v>
       </c>
@@ -4843,6 +5836,9 @@
       </c>
       <c r="M61" t="s">
         <v>131</v>
+      </c>
+      <c r="N61" t="s">
+        <v>196</v>
       </c>
       <c r="O61" t="s">
         <v>147</v>
@@ -4897,6 +5893,9 @@
       <c r="I62" s="3" t="s">
         <v>196</v>
       </c>
+      <c r="J62" t="s">
+        <v>196</v>
+      </c>
       <c r="K62" t="s">
         <v>104</v>
       </c>
@@ -4905,6 +5904,9 @@
       </c>
       <c r="M62" t="s">
         <v>132</v>
+      </c>
+      <c r="N62" t="s">
+        <v>196</v>
       </c>
       <c r="O62" t="s">
         <v>148</v>
@@ -4959,6 +5961,9 @@
       <c r="I63" t="s">
         <v>196</v>
       </c>
+      <c r="J63" t="s">
+        <v>196</v>
+      </c>
       <c r="K63" t="s">
         <v>105</v>
       </c>
@@ -4967,6 +5972,9 @@
       </c>
       <c r="M63" t="s">
         <v>133</v>
+      </c>
+      <c r="N63" t="s">
+        <v>196</v>
       </c>
       <c r="O63" t="s">
         <v>149</v>
@@ -5021,6 +6029,9 @@
       <c r="I64" t="s">
         <v>196</v>
       </c>
+      <c r="J64" t="s">
+        <v>196</v>
+      </c>
       <c r="K64" t="s">
         <v>106</v>
       </c>
@@ -5029,6 +6040,9 @@
       </c>
       <c r="M64" t="s">
         <v>134</v>
+      </c>
+      <c r="N64" t="s">
+        <v>196</v>
       </c>
       <c r="O64" t="s">
         <v>150</v>
@@ -5086,6 +6100,9 @@
       <c r="I65" t="s">
         <v>196</v>
       </c>
+      <c r="J65" t="s">
+        <v>415</v>
+      </c>
       <c r="K65" t="s">
         <v>196</v>
       </c>
@@ -5095,6 +6112,9 @@
       <c r="M65" t="s">
         <v>136</v>
       </c>
+      <c r="N65" t="s">
+        <v>196</v>
+      </c>
       <c r="O65" t="s">
         <v>151</v>
       </c>
@@ -5125,13 +6145,13 @@
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B66" t="s">
         <v>196</v>
       </c>
       <c r="C66" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D66" t="s">
         <v>265</v>
@@ -5140,7 +6160,7 @@
         <v>196</v>
       </c>
       <c r="F66" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G66" t="s">
         <v>196</v>
@@ -5149,12 +6169,36 @@
         <v>196</v>
       </c>
       <c r="I66" t="s">
+        <v>196</v>
+      </c>
+      <c r="J66" t="s">
+        <v>196</v>
+      </c>
+      <c r="K66" t="s">
+        <v>196</v>
+      </c>
+      <c r="L66" t="s">
+        <v>196</v>
+      </c>
+      <c r="M66" t="s">
+        <v>196</v>
+      </c>
+      <c r="N66" t="s">
+        <v>196</v>
+      </c>
+      <c r="O66" t="s">
+        <v>196</v>
+      </c>
+      <c r="P66" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q66" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B67" t="s">
         <v>196</v>
@@ -5177,10 +6221,34 @@
       <c r="I67" t="s">
         <v>196</v>
       </c>
+      <c r="J67" t="s">
+        <v>196</v>
+      </c>
+      <c r="K67" t="s">
+        <v>196</v>
+      </c>
+      <c r="L67" t="s">
+        <v>196</v>
+      </c>
+      <c r="M67" t="s">
+        <v>196</v>
+      </c>
+      <c r="N67" t="s">
+        <v>196</v>
+      </c>
+      <c r="O67" t="s">
+        <v>196</v>
+      </c>
+      <c r="P67" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B68" t="s">
         <v>196</v>
@@ -5203,16 +6271,37 @@
       <c r="I68" t="s">
         <v>196</v>
       </c>
+      <c r="J68" t="s">
+        <v>196</v>
+      </c>
+      <c r="K68" t="s">
+        <v>196</v>
+      </c>
+      <c r="L68" t="s">
+        <v>196</v>
+      </c>
+      <c r="M68" t="s">
+        <v>196</v>
+      </c>
+      <c r="N68" t="s">
+        <v>196</v>
+      </c>
+      <c r="O68" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B69" t="s">
         <v>196</v>
       </c>
       <c r="C69" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D69" t="s">
         <v>196</v>
@@ -5221,7 +6310,7 @@
         <v>196</v>
       </c>
       <c r="F69" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G69" t="s">
         <v>196</v>
@@ -5230,18 +6319,42 @@
         <v>196</v>
       </c>
       <c r="I69" t="s">
+        <v>196</v>
+      </c>
+      <c r="J69" t="s">
+        <v>196</v>
+      </c>
+      <c r="K69" t="s">
+        <v>196</v>
+      </c>
+      <c r="L69" t="s">
+        <v>196</v>
+      </c>
+      <c r="M69" t="s">
+        <v>196</v>
+      </c>
+      <c r="N69" t="s">
+        <v>196</v>
+      </c>
+      <c r="O69" t="s">
+        <v>196</v>
+      </c>
+      <c r="P69" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q69" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B70" t="s">
         <v>196</v>
       </c>
       <c r="C70" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D70" t="s">
         <v>196</v>
@@ -5256,12 +6369,36 @@
         <v>196</v>
       </c>
       <c r="I70" t="s">
+        <v>196</v>
+      </c>
+      <c r="J70" t="s">
+        <v>196</v>
+      </c>
+      <c r="K70" t="s">
+        <v>196</v>
+      </c>
+      <c r="L70" t="s">
+        <v>196</v>
+      </c>
+      <c r="M70" t="s">
+        <v>196</v>
+      </c>
+      <c r="N70" t="s">
+        <v>196</v>
+      </c>
+      <c r="O70" t="s">
+        <v>196</v>
+      </c>
+      <c r="P70" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q70" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B71" t="s">
         <v>196</v>
@@ -5270,7 +6407,7 @@
         <v>196</v>
       </c>
       <c r="D71" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E71" t="s">
         <v>196</v>
@@ -5282,6 +6419,30 @@
         <v>196</v>
       </c>
       <c r="I71" t="s">
+        <v>196</v>
+      </c>
+      <c r="J71" t="s">
+        <v>196</v>
+      </c>
+      <c r="K71" t="s">
+        <v>196</v>
+      </c>
+      <c r="L71" t="s">
+        <v>196</v>
+      </c>
+      <c r="M71" t="s">
+        <v>196</v>
+      </c>
+      <c r="N71" t="s">
+        <v>196</v>
+      </c>
+      <c r="O71" t="s">
+        <v>196</v>
+      </c>
+      <c r="P71" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q71" t="s">
         <v>196</v>
       </c>
     </row>

--- a/Monadisk overblik.xlsx
+++ b/Monadisk overblik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aaudk-my.sharepoint.com/personal/bo62rk_id_aau_dk/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1422" documentId="8_{6C2A7B69-2C62-4B80-ACF4-E8008D3DDFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08F1E93D-7987-4EBD-9686-2F568BBE61CF}"/>
+  <xr:revisionPtr revIDLastSave="1914" documentId="8_{6C2A7B69-2C62-4B80-ACF4-E8008D3DDFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F86A2DB0-E533-46FC-A9E2-D9D5B285A0BF}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{E14E365F-4887-4C07-BAAD-AE51F23AD0DA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="502">
   <si>
     <t>Corona0</t>
   </si>
@@ -1473,6 +1473,78 @@
   </si>
   <si>
     <t>q7</t>
+  </si>
+  <si>
+    <t>q3</t>
+  </si>
+  <si>
+    <t>FT15</t>
+  </si>
+  <si>
+    <t>q45b_4</t>
+  </si>
+  <si>
+    <t>q45c_6</t>
+  </si>
+  <si>
+    <t>q45c_11</t>
+  </si>
+  <si>
+    <t>q45c_8</t>
+  </si>
+  <si>
+    <t>FT19</t>
+  </si>
+  <si>
+    <t>q34_4</t>
+  </si>
+  <si>
+    <t>q45a_18</t>
+  </si>
+  <si>
+    <t>q45a_19</t>
+  </si>
+  <si>
+    <t>q45a_20</t>
+  </si>
+  <si>
+    <t>q45a_23</t>
+  </si>
+  <si>
+    <t>q45b_12</t>
+  </si>
+  <si>
+    <t>q45b_19</t>
+  </si>
+  <si>
+    <t>q45a_29</t>
+  </si>
+  <si>
+    <t>Q58B2_4</t>
+  </si>
+  <si>
+    <t>FT22</t>
+  </si>
+  <si>
+    <t>FT_next</t>
+  </si>
+  <si>
+    <t>Q7</t>
+  </si>
+  <si>
+    <t>q45a_15</t>
+  </si>
+  <si>
+    <t>q60_10</t>
+  </si>
+  <si>
+    <t>Q69_4_3</t>
+  </si>
+  <si>
+    <t>Q39G_5</t>
+  </si>
+  <si>
+    <t>FT26</t>
   </si>
 </sst>
 </file>
@@ -2089,6 +2161,9 @@
       <c r="S2" t="s">
         <v>91</v>
       </c>
+      <c r="T2" t="s">
+        <v>91</v>
+      </c>
       <c r="U2" t="s">
         <v>91</v>
       </c>
@@ -2099,6 +2174,18 @@
         <v>91</v>
       </c>
       <c r="X2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB2" t="s">
         <v>91</v>
       </c>
     </row>
@@ -2160,6 +2247,9 @@
       <c r="S3" t="s">
         <v>92</v>
       </c>
+      <c r="T3" t="s">
+        <v>92</v>
+      </c>
       <c r="U3" t="s">
         <v>92</v>
       </c>
@@ -2170,6 +2260,18 @@
         <v>92</v>
       </c>
       <c r="X3" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB3" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2225,6 +2327,39 @@
       <c r="Q4" t="s">
         <v>343</v>
       </c>
+      <c r="R4" t="s">
+        <v>343</v>
+      </c>
+      <c r="S4" t="s">
+        <v>343</v>
+      </c>
+      <c r="T4" t="s">
+        <v>343</v>
+      </c>
+      <c r="U4" t="s">
+        <v>343</v>
+      </c>
+      <c r="V4" t="s">
+        <v>343</v>
+      </c>
+      <c r="W4" t="s">
+        <v>343</v>
+      </c>
+      <c r="X4" t="s">
+        <v>343</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>343</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>343</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>343</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -2278,6 +2413,39 @@
       <c r="Q5" t="s">
         <v>344</v>
       </c>
+      <c r="R5" t="s">
+        <v>344</v>
+      </c>
+      <c r="S5" t="s">
+        <v>344</v>
+      </c>
+      <c r="T5" t="s">
+        <v>344</v>
+      </c>
+      <c r="U5" t="s">
+        <v>344</v>
+      </c>
+      <c r="V5" t="s">
+        <v>344</v>
+      </c>
+      <c r="W5" t="s">
+        <v>344</v>
+      </c>
+      <c r="X5" t="s">
+        <v>344</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>344</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>344</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -2331,6 +2499,39 @@
       <c r="Q6" t="s">
         <v>314</v>
       </c>
+      <c r="R6" t="s">
+        <v>351</v>
+      </c>
+      <c r="S6" t="s">
+        <v>351</v>
+      </c>
+      <c r="T6" t="s">
+        <v>351</v>
+      </c>
+      <c r="U6" t="s">
+        <v>196</v>
+      </c>
+      <c r="V6" t="s">
+        <v>351</v>
+      </c>
+      <c r="W6" t="s">
+        <v>196</v>
+      </c>
+      <c r="X6" t="s">
+        <v>351</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>351</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -2384,6 +2585,39 @@
       <c r="Q7" t="s">
         <v>345</v>
       </c>
+      <c r="R7" t="s">
+        <v>345</v>
+      </c>
+      <c r="S7" t="s">
+        <v>345</v>
+      </c>
+      <c r="T7" t="s">
+        <v>345</v>
+      </c>
+      <c r="U7" t="s">
+        <v>345</v>
+      </c>
+      <c r="V7" t="s">
+        <v>345</v>
+      </c>
+      <c r="W7" t="s">
+        <v>345</v>
+      </c>
+      <c r="X7" t="s">
+        <v>345</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>345</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>345</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>345</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -2434,6 +2668,39 @@
       <c r="Q8" t="s">
         <v>477</v>
       </c>
+      <c r="R8" t="s">
+        <v>478</v>
+      </c>
+      <c r="S8" t="s">
+        <v>478</v>
+      </c>
+      <c r="T8" t="s">
+        <v>478</v>
+      </c>
+      <c r="U8" t="s">
+        <v>478</v>
+      </c>
+      <c r="V8" t="s">
+        <v>478</v>
+      </c>
+      <c r="W8" t="s">
+        <v>478</v>
+      </c>
+      <c r="X8" t="s">
+        <v>478</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>478</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>478</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -2487,6 +2754,39 @@
       <c r="Q9" t="s">
         <v>312</v>
       </c>
+      <c r="R9" t="s">
+        <v>325</v>
+      </c>
+      <c r="S9" t="s">
+        <v>325</v>
+      </c>
+      <c r="T9" t="s">
+        <v>325</v>
+      </c>
+      <c r="U9" t="s">
+        <v>325</v>
+      </c>
+      <c r="V9" t="s">
+        <v>196</v>
+      </c>
+      <c r="W9" t="s">
+        <v>374</v>
+      </c>
+      <c r="X9" t="s">
+        <v>374</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>374</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>374</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>325</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -2540,6 +2840,39 @@
       <c r="Q10" t="s">
         <v>313</v>
       </c>
+      <c r="R10" t="s">
+        <v>322</v>
+      </c>
+      <c r="S10" t="s">
+        <v>322</v>
+      </c>
+      <c r="T10" t="s">
+        <v>322</v>
+      </c>
+      <c r="U10" t="s">
+        <v>373</v>
+      </c>
+      <c r="V10" t="s">
+        <v>322</v>
+      </c>
+      <c r="W10" t="s">
+        <v>322</v>
+      </c>
+      <c r="X10" t="s">
+        <v>322</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>322</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -2593,6 +2926,39 @@
       <c r="Q11" t="s">
         <v>352</v>
       </c>
+      <c r="R11" t="s">
+        <v>479</v>
+      </c>
+      <c r="S11" t="s">
+        <v>484</v>
+      </c>
+      <c r="T11" t="s">
+        <v>484</v>
+      </c>
+      <c r="U11" t="s">
+        <v>324</v>
+      </c>
+      <c r="V11" t="s">
+        <v>494</v>
+      </c>
+      <c r="W11" t="s">
+        <v>494</v>
+      </c>
+      <c r="X11" t="s">
+        <v>494</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>494</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>494</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>494</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>501</v>
+      </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -2646,6 +3012,39 @@
       <c r="Q12" t="s">
         <v>196</v>
       </c>
+      <c r="R12" t="s">
+        <v>352</v>
+      </c>
+      <c r="S12" t="s">
+        <v>352</v>
+      </c>
+      <c r="T12" t="s">
+        <v>352</v>
+      </c>
+      <c r="U12" t="s">
+        <v>352</v>
+      </c>
+      <c r="V12" t="s">
+        <v>495</v>
+      </c>
+      <c r="W12" t="s">
+        <v>495</v>
+      </c>
+      <c r="X12" t="s">
+        <v>495</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>495</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>495</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>495</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>495</v>
+      </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -2705,6 +3104,9 @@
       <c r="S13" t="s">
         <v>320</v>
       </c>
+      <c r="T13" t="s">
+        <v>320</v>
+      </c>
       <c r="U13" t="s">
         <v>320</v>
       </c>
@@ -2716,6 +3118,18 @@
       </c>
       <c r="X13" t="s">
         <v>320</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>320</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>320</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.25">
@@ -2776,8 +3190,32 @@
       <c r="S14" t="s">
         <v>300</v>
       </c>
+      <c r="T14" t="s">
+        <v>300</v>
+      </c>
       <c r="U14" t="s">
         <v>300</v>
+      </c>
+      <c r="V14" t="s">
+        <v>196</v>
+      </c>
+      <c r="W14" t="s">
+        <v>496</v>
+      </c>
+      <c r="X14" t="s">
+        <v>496</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>496</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>496</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.25">
@@ -2838,10 +3276,31 @@
       <c r="S15" t="s">
         <v>326</v>
       </c>
+      <c r="T15" t="s">
+        <v>326</v>
+      </c>
       <c r="U15" t="s">
         <v>326</v>
       </c>
+      <c r="V15" t="s">
+        <v>196</v>
+      </c>
       <c r="W15" t="s">
+        <v>326</v>
+      </c>
+      <c r="X15" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>326</v>
+      </c>
+      <c r="AB15" t="s">
         <v>326</v>
       </c>
       <c r="AE15" t="s">
@@ -2903,6 +3362,39 @@
       <c r="Q16" t="s">
         <v>196</v>
       </c>
+      <c r="R16" t="s">
+        <v>361</v>
+      </c>
+      <c r="S16" t="s">
+        <v>361</v>
+      </c>
+      <c r="T16" t="s">
+        <v>361</v>
+      </c>
+      <c r="U16" t="s">
+        <v>361</v>
+      </c>
+      <c r="V16" t="s">
+        <v>361</v>
+      </c>
+      <c r="W16" t="s">
+        <v>196</v>
+      </c>
+      <c r="X16" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>361</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>361</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -2956,6 +3448,39 @@
       <c r="Q17" t="s">
         <v>196</v>
       </c>
+      <c r="R17" t="s">
+        <v>362</v>
+      </c>
+      <c r="S17" t="s">
+        <v>362</v>
+      </c>
+      <c r="T17" t="s">
+        <v>362</v>
+      </c>
+      <c r="U17" t="s">
+        <v>362</v>
+      </c>
+      <c r="V17" t="s">
+        <v>362</v>
+      </c>
+      <c r="W17" t="s">
+        <v>196</v>
+      </c>
+      <c r="X17" t="s">
+        <v>362</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>362</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>362</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -3009,6 +3534,39 @@
       <c r="Q18" t="s">
         <v>196</v>
       </c>
+      <c r="R18" t="s">
+        <v>363</v>
+      </c>
+      <c r="S18" t="s">
+        <v>363</v>
+      </c>
+      <c r="T18" t="s">
+        <v>363</v>
+      </c>
+      <c r="U18" t="s">
+        <v>363</v>
+      </c>
+      <c r="V18" t="s">
+        <v>363</v>
+      </c>
+      <c r="W18" t="s">
+        <v>196</v>
+      </c>
+      <c r="X18" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>363</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>363</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -3062,6 +3620,39 @@
       <c r="Q19" t="s">
         <v>196</v>
       </c>
+      <c r="R19" t="s">
+        <v>364</v>
+      </c>
+      <c r="S19" t="s">
+        <v>364</v>
+      </c>
+      <c r="T19" t="s">
+        <v>364</v>
+      </c>
+      <c r="U19" t="s">
+        <v>364</v>
+      </c>
+      <c r="V19" t="s">
+        <v>364</v>
+      </c>
+      <c r="W19" t="s">
+        <v>196</v>
+      </c>
+      <c r="X19" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>364</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -3115,6 +3706,39 @@
       <c r="Q20" t="s">
         <v>196</v>
       </c>
+      <c r="R20" t="s">
+        <v>365</v>
+      </c>
+      <c r="S20" t="s">
+        <v>365</v>
+      </c>
+      <c r="T20" t="s">
+        <v>365</v>
+      </c>
+      <c r="U20" t="s">
+        <v>365</v>
+      </c>
+      <c r="V20" t="s">
+        <v>365</v>
+      </c>
+      <c r="W20" t="s">
+        <v>196</v>
+      </c>
+      <c r="X20" t="s">
+        <v>365</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>365</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>365</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -3168,6 +3792,39 @@
       <c r="Q21" t="s">
         <v>196</v>
       </c>
+      <c r="R21" t="s">
+        <v>366</v>
+      </c>
+      <c r="S21" t="s">
+        <v>366</v>
+      </c>
+      <c r="T21" t="s">
+        <v>366</v>
+      </c>
+      <c r="U21" t="s">
+        <v>366</v>
+      </c>
+      <c r="V21" t="s">
+        <v>366</v>
+      </c>
+      <c r="W21" t="s">
+        <v>196</v>
+      </c>
+      <c r="X21" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>366</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>366</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -3221,6 +3878,39 @@
       <c r="Q22" t="s">
         <v>196</v>
       </c>
+      <c r="R22" t="s">
+        <v>367</v>
+      </c>
+      <c r="S22" t="s">
+        <v>367</v>
+      </c>
+      <c r="T22" t="s">
+        <v>367</v>
+      </c>
+      <c r="U22" t="s">
+        <v>367</v>
+      </c>
+      <c r="V22" t="s">
+        <v>367</v>
+      </c>
+      <c r="W22" t="s">
+        <v>196</v>
+      </c>
+      <c r="X22" t="s">
+        <v>367</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>367</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>367</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -3274,6 +3964,39 @@
       <c r="Q23" t="s">
         <v>196</v>
       </c>
+      <c r="R23" t="s">
+        <v>196</v>
+      </c>
+      <c r="S23" t="s">
+        <v>196</v>
+      </c>
+      <c r="T23" t="s">
+        <v>196</v>
+      </c>
+      <c r="U23" t="s">
+        <v>196</v>
+      </c>
+      <c r="V23" t="s">
+        <v>196</v>
+      </c>
+      <c r="W23" t="s">
+        <v>196</v>
+      </c>
+      <c r="X23" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB23" s="3" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -3327,6 +4050,39 @@
       <c r="Q24" t="s">
         <v>196</v>
       </c>
+      <c r="R24" t="s">
+        <v>368</v>
+      </c>
+      <c r="S24" t="s">
+        <v>368</v>
+      </c>
+      <c r="T24" t="s">
+        <v>368</v>
+      </c>
+      <c r="U24" t="s">
+        <v>368</v>
+      </c>
+      <c r="V24" t="s">
+        <v>368</v>
+      </c>
+      <c r="W24" t="s">
+        <v>196</v>
+      </c>
+      <c r="X24" t="s">
+        <v>369</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>368</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -3380,6 +4136,39 @@
       <c r="Q25" t="s">
         <v>196</v>
       </c>
+      <c r="R25" t="s">
+        <v>369</v>
+      </c>
+      <c r="S25" t="s">
+        <v>369</v>
+      </c>
+      <c r="T25" t="s">
+        <v>369</v>
+      </c>
+      <c r="U25" t="s">
+        <v>369</v>
+      </c>
+      <c r="V25" t="s">
+        <v>369</v>
+      </c>
+      <c r="W25" t="s">
+        <v>196</v>
+      </c>
+      <c r="X25" t="s">
+        <v>498</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>498</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>369</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -3439,11 +4228,32 @@
       <c r="S26" t="s">
         <v>328</v>
       </c>
+      <c r="T26" t="s">
+        <v>328</v>
+      </c>
       <c r="U26" t="s">
-        <v>334</v>
+        <v>328</v>
+      </c>
+      <c r="V26" t="s">
+        <v>493</v>
+      </c>
+      <c r="W26" t="s">
+        <v>328</v>
       </c>
       <c r="X26" t="s">
+        <v>499</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>500</v>
+      </c>
+      <c r="AA26" t="s">
         <v>328</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>196</v>
       </c>
       <c r="AE26" t="s">
         <v>328</v>
@@ -3507,6 +4317,39 @@
       <c r="Q27" t="s">
         <v>372</v>
       </c>
+      <c r="R27" t="s">
+        <v>372</v>
+      </c>
+      <c r="S27" t="s">
+        <v>372</v>
+      </c>
+      <c r="T27" t="s">
+        <v>372</v>
+      </c>
+      <c r="U27" t="s">
+        <v>372</v>
+      </c>
+      <c r="V27" t="s">
+        <v>196</v>
+      </c>
+      <c r="W27" t="s">
+        <v>196</v>
+      </c>
+      <c r="X27" t="s">
+        <v>372</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>372</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -3566,6 +4409,9 @@
       <c r="S28" t="s">
         <v>318</v>
       </c>
+      <c r="T28" t="s">
+        <v>318</v>
+      </c>
       <c r="U28" t="s">
         <v>318</v>
       </c>
@@ -3576,6 +4422,18 @@
         <v>318</v>
       </c>
       <c r="X28" t="s">
+        <v>318</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>318</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>318</v>
+      </c>
+      <c r="AB28" t="s">
         <v>318</v>
       </c>
     </row>
@@ -3637,6 +4495,9 @@
       <c r="S29" t="s">
         <v>319</v>
       </c>
+      <c r="T29" t="s">
+        <v>319</v>
+      </c>
       <c r="U29" t="s">
         <v>319</v>
       </c>
@@ -3647,7 +4508,19 @@
         <v>319</v>
       </c>
       <c r="X29" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA29" t="s">
         <v>319</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
@@ -3708,6 +4581,9 @@
       <c r="S30" t="s">
         <v>268</v>
       </c>
+      <c r="T30" t="s">
+        <v>268</v>
+      </c>
       <c r="U30" t="s">
         <v>268</v>
       </c>
@@ -3715,9 +4591,21 @@
         <v>268</v>
       </c>
       <c r="W30" t="s">
-        <v>196</v>
+        <v>268</v>
       </c>
       <c r="X30" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>268</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>268</v>
+      </c>
+      <c r="AB30" t="s">
         <v>268</v>
       </c>
     </row>
@@ -3779,6 +4667,9 @@
       <c r="S31" t="s">
         <v>264</v>
       </c>
+      <c r="T31" t="s">
+        <v>264</v>
+      </c>
       <c r="U31" t="s">
         <v>264</v>
       </c>
@@ -3786,9 +4677,21 @@
         <v>264</v>
       </c>
       <c r="W31" t="s">
-        <v>196</v>
+        <v>264</v>
       </c>
       <c r="X31" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>264</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB31" t="s">
         <v>264</v>
       </c>
     </row>
@@ -3844,6 +4747,12 @@
       <c r="R32" t="s">
         <v>196</v>
       </c>
+      <c r="S32" t="s">
+        <v>196</v>
+      </c>
+      <c r="T32" t="s">
+        <v>196</v>
+      </c>
       <c r="U32" t="s">
         <v>196</v>
       </c>
@@ -3856,8 +4765,20 @@
       <c r="X32" t="s">
         <v>196</v>
       </c>
+      <c r="Y32" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>67</v>
       </c>
@@ -3915,6 +4836,9 @@
       <c r="S33" t="s">
         <v>263</v>
       </c>
+      <c r="T33" t="s">
+        <v>263</v>
+      </c>
       <c r="U33" t="s">
         <v>263</v>
       </c>
@@ -3927,8 +4851,20 @@
       <c r="X33" t="s">
         <v>263</v>
       </c>
+      <c r="Y33" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>263</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>69</v>
       </c>
@@ -3986,6 +4922,9 @@
       <c r="S34" t="s">
         <v>265</v>
       </c>
+      <c r="T34" t="s">
+        <v>265</v>
+      </c>
       <c r="U34" t="s">
         <v>265</v>
       </c>
@@ -3998,8 +4937,20 @@
       <c r="X34" t="s">
         <v>265</v>
       </c>
+      <c r="Y34" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>265</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>265</v>
+      </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>72</v>
       </c>
@@ -4051,6 +5002,12 @@
       <c r="R35" t="s">
         <v>196</v>
       </c>
+      <c r="S35" t="s">
+        <v>196</v>
+      </c>
+      <c r="T35" t="s">
+        <v>196</v>
+      </c>
       <c r="U35" t="s">
         <v>196</v>
       </c>
@@ -4063,8 +5020,20 @@
       <c r="X35" t="s">
         <v>196</v>
       </c>
+      <c r="Y35" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,6 +5091,9 @@
       <c r="S36" t="s">
         <v>267</v>
       </c>
+      <c r="T36" t="s">
+        <v>267</v>
+      </c>
       <c r="U36" t="s">
         <v>267</v>
       </c>
@@ -4134,8 +5106,20 @@
       <c r="X36" t="s">
         <v>196</v>
       </c>
+      <c r="Y36" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>74</v>
       </c>
@@ -4190,6 +5174,9 @@
       <c r="S37" t="s">
         <v>266</v>
       </c>
+      <c r="T37" t="s">
+        <v>266</v>
+      </c>
       <c r="U37" t="s">
         <v>266</v>
       </c>
@@ -4197,13 +5184,25 @@
         <v>266</v>
       </c>
       <c r="W37" t="s">
-        <v>196</v>
+        <v>266</v>
       </c>
       <c r="X37" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA37" t="s">
         <v>266</v>
       </c>
+      <c r="AB37" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
@@ -4261,6 +5260,9 @@
       <c r="S38" t="s">
         <v>281</v>
       </c>
+      <c r="T38" t="s">
+        <v>485</v>
+      </c>
       <c r="U38" t="s">
         <v>281</v>
       </c>
@@ -4268,13 +5270,25 @@
         <v>281</v>
       </c>
       <c r="W38" t="s">
-        <v>196</v>
+        <v>281</v>
       </c>
       <c r="X38" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA38" t="s">
         <v>281</v>
       </c>
+      <c r="AB38" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>76</v>
       </c>
@@ -4326,6 +5340,12 @@
       <c r="R39" t="s">
         <v>196</v>
       </c>
+      <c r="S39" t="s">
+        <v>196</v>
+      </c>
+      <c r="T39" t="s">
+        <v>196</v>
+      </c>
       <c r="U39" t="s">
         <v>196</v>
       </c>
@@ -4338,8 +5358,20 @@
       <c r="X39" t="s">
         <v>196</v>
       </c>
+      <c r="Y39" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>218</v>
       </c>
@@ -4397,6 +5429,9 @@
       <c r="S40" t="s">
         <v>269</v>
       </c>
+      <c r="T40" t="s">
+        <v>269</v>
+      </c>
       <c r="U40" t="s">
         <v>269</v>
       </c>
@@ -4404,13 +5439,25 @@
         <v>269</v>
       </c>
       <c r="W40" t="s">
-        <v>196</v>
+        <v>269</v>
       </c>
       <c r="X40" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA40" t="s">
         <v>269</v>
       </c>
+      <c r="AB40" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>219</v>
       </c>
@@ -4462,8 +5509,14 @@
       <c r="R41" t="s">
         <v>280</v>
       </c>
+      <c r="S41" t="s">
+        <v>196</v>
+      </c>
+      <c r="T41" t="s">
+        <v>196</v>
+      </c>
       <c r="U41" t="s">
-        <v>196</v>
+        <v>492</v>
       </c>
       <c r="V41" t="s">
         <v>297</v>
@@ -4474,8 +5527,20 @@
       <c r="X41" t="s">
         <v>196</v>
       </c>
+      <c r="Y41" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>297</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>220</v>
       </c>
@@ -4527,6 +5592,12 @@
       <c r="R42" t="s">
         <v>196</v>
       </c>
+      <c r="S42" t="s">
+        <v>196</v>
+      </c>
+      <c r="T42" t="s">
+        <v>196</v>
+      </c>
       <c r="U42" t="s">
         <v>196</v>
       </c>
@@ -4534,13 +5605,25 @@
         <v>298</v>
       </c>
       <c r="W42" t="s">
-        <v>196</v>
+        <v>298</v>
       </c>
       <c r="X42" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z42" t="s">
         <v>298</v>
       </c>
+      <c r="AA42" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>232</v>
       </c>
@@ -4592,6 +5675,12 @@
       <c r="R43" t="s">
         <v>196</v>
       </c>
+      <c r="S43" t="s">
+        <v>196</v>
+      </c>
+      <c r="T43" t="s">
+        <v>196</v>
+      </c>
       <c r="U43" t="s">
         <v>196</v>
       </c>
@@ -4604,8 +5693,20 @@
       <c r="X43" t="s">
         <v>299</v>
       </c>
+      <c r="Y43" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>221</v>
       </c>
@@ -4663,6 +5764,9 @@
       <c r="S44" t="s">
         <v>271</v>
       </c>
+      <c r="T44" t="s">
+        <v>271</v>
+      </c>
       <c r="U44" t="s">
         <v>271</v>
       </c>
@@ -4675,8 +5779,20 @@
       <c r="X44" t="s">
         <v>271</v>
       </c>
+      <c r="Y44" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>271</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>271</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>271</v>
+      </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>222</v>
       </c>
@@ -4734,6 +5850,9 @@
       <c r="S45" t="s">
         <v>282</v>
       </c>
+      <c r="T45" t="s">
+        <v>282</v>
+      </c>
       <c r="U45" t="s">
         <v>282</v>
       </c>
@@ -4746,8 +5865,20 @@
       <c r="X45" t="s">
         <v>282</v>
       </c>
+      <c r="Y45" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>282</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>223</v>
       </c>
@@ -4805,6 +5936,9 @@
       <c r="S46" t="s">
         <v>272</v>
       </c>
+      <c r="T46" t="s">
+        <v>272</v>
+      </c>
       <c r="U46" t="s">
         <v>272</v>
       </c>
@@ -4812,13 +5946,25 @@
         <v>272</v>
       </c>
       <c r="W46" t="s">
-        <v>196</v>
+        <v>272</v>
       </c>
       <c r="X46" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA46" t="s">
         <v>272</v>
       </c>
+      <c r="AB46" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>224</v>
       </c>
@@ -4876,6 +6022,9 @@
       <c r="S47" t="s">
         <v>273</v>
       </c>
+      <c r="T47" t="s">
+        <v>273</v>
+      </c>
       <c r="U47" t="s">
         <v>273</v>
       </c>
@@ -4888,8 +6037,20 @@
       <c r="X47" t="s">
         <v>196</v>
       </c>
+      <c r="Y47" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>225</v>
       </c>
@@ -4947,6 +6108,9 @@
       <c r="S48" t="s">
         <v>276</v>
       </c>
+      <c r="T48" t="s">
+        <v>276</v>
+      </c>
       <c r="U48" t="s">
         <v>276</v>
       </c>
@@ -4954,13 +6118,25 @@
         <v>276</v>
       </c>
       <c r="W48" t="s">
-        <v>196</v>
+        <v>276</v>
       </c>
       <c r="X48" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA48" t="s">
         <v>276</v>
       </c>
+      <c r="AB48" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>226</v>
       </c>
@@ -5018,20 +6194,32 @@
       <c r="S49" t="s">
         <v>277</v>
       </c>
+      <c r="T49" t="s">
+        <v>277</v>
+      </c>
       <c r="U49" t="s">
         <v>277</v>
       </c>
       <c r="V49" t="s">
-        <v>196</v>
-      </c>
-      <c r="W49" t="s">
-        <v>196</v>
+        <v>277</v>
       </c>
       <c r="X49" t="s">
         <v>196</v>
       </c>
+      <c r="Y49" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>277</v>
+      </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>227</v>
       </c>
@@ -5089,6 +6277,9 @@
       <c r="S50" t="s">
         <v>270</v>
       </c>
+      <c r="T50" t="s">
+        <v>270</v>
+      </c>
       <c r="U50" t="s">
         <v>270</v>
       </c>
@@ -5099,10 +6290,22 @@
         <v>196</v>
       </c>
       <c r="X50" t="s">
-        <v>270</v>
+        <v>196</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>196</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>77</v>
       </c>
@@ -5160,6 +6363,9 @@
       <c r="S51" t="s">
         <v>181</v>
       </c>
+      <c r="T51" t="s">
+        <v>181</v>
+      </c>
       <c r="U51" t="s">
         <v>181</v>
       </c>
@@ -5172,8 +6378,20 @@
       <c r="X51" t="s">
         <v>181</v>
       </c>
+      <c r="Y51" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>181</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>78</v>
       </c>
@@ -5228,6 +6446,9 @@
       <c r="S52" t="s">
         <v>182</v>
       </c>
+      <c r="T52" t="s">
+        <v>196</v>
+      </c>
       <c r="U52" t="s">
         <v>196</v>
       </c>
@@ -5240,8 +6461,20 @@
       <c r="X52" t="s">
         <v>196</v>
       </c>
+      <c r="Y52" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>79</v>
       </c>
@@ -5299,6 +6532,9 @@
       <c r="S53" t="s">
         <v>183</v>
       </c>
+      <c r="T53" t="s">
+        <v>486</v>
+      </c>
       <c r="U53" t="s">
         <v>182</v>
       </c>
@@ -5306,13 +6542,25 @@
         <v>182</v>
       </c>
       <c r="W53" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="X53" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA53" t="s">
         <v>182</v>
       </c>
+      <c r="AB53" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>80</v>
       </c>
@@ -5367,6 +6615,9 @@
       <c r="S54" t="s">
         <v>196</v>
       </c>
+      <c r="T54" t="s">
+        <v>196</v>
+      </c>
       <c r="U54" t="s">
         <v>196</v>
       </c>
@@ -5379,8 +6630,20 @@
       <c r="X54" t="s">
         <v>196</v>
       </c>
+      <c r="Y54" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>81</v>
       </c>
@@ -5438,6 +6701,9 @@
       <c r="S55" t="s">
         <v>185</v>
       </c>
+      <c r="T55" t="s">
+        <v>185</v>
+      </c>
       <c r="U55" t="s">
         <v>183</v>
       </c>
@@ -5450,8 +6716,20 @@
       <c r="X55" t="s">
         <v>196</v>
       </c>
+      <c r="Y55" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>183</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>82</v>
       </c>
@@ -5506,6 +6784,9 @@
       <c r="S56" t="s">
         <v>196</v>
       </c>
+      <c r="T56" t="s">
+        <v>196</v>
+      </c>
       <c r="U56" t="s">
         <v>196</v>
       </c>
@@ -5518,8 +6799,20 @@
       <c r="X56" t="s">
         <v>196</v>
       </c>
+      <c r="Y56" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>83</v>
       </c>
@@ -5577,6 +6870,9 @@
       <c r="S57" t="s">
         <v>195</v>
       </c>
+      <c r="T57" t="s">
+        <v>186</v>
+      </c>
       <c r="U57" t="s">
         <v>184</v>
       </c>
@@ -5589,8 +6885,20 @@
       <c r="X57" t="s">
         <v>184</v>
       </c>
+      <c r="Y57" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB57" t="s">
+        <v>184</v>
+      </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>84</v>
       </c>
@@ -5645,6 +6953,9 @@
       <c r="S58" t="s">
         <v>187</v>
       </c>
+      <c r="T58" t="s">
+        <v>187</v>
+      </c>
       <c r="U58" t="s">
         <v>196</v>
       </c>
@@ -5657,8 +6968,20 @@
       <c r="X58" t="s">
         <v>196</v>
       </c>
+      <c r="Y58" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB58" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>85</v>
       </c>
@@ -5716,6 +7039,9 @@
       <c r="S59" t="s">
         <v>188</v>
       </c>
+      <c r="T59" t="s">
+        <v>188</v>
+      </c>
       <c r="U59" t="s">
         <v>193</v>
       </c>
@@ -5728,8 +7054,20 @@
       <c r="X59" t="s">
         <v>193</v>
       </c>
+      <c r="Y59" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>193</v>
+      </c>
+      <c r="AB59" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>86</v>
       </c>
@@ -5787,6 +7125,9 @@
       <c r="S60" t="s">
         <v>189</v>
       </c>
+      <c r="T60" t="s">
+        <v>189</v>
+      </c>
       <c r="U60" t="s">
         <v>185</v>
       </c>
@@ -5799,8 +7140,20 @@
       <c r="X60" t="s">
         <v>185</v>
       </c>
+      <c r="Y60" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB60" t="s">
+        <v>185</v>
+      </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>87</v>
       </c>
@@ -5855,6 +7208,9 @@
       <c r="S61" t="s">
         <v>190</v>
       </c>
+      <c r="T61" t="s">
+        <v>190</v>
+      </c>
       <c r="U61" t="s">
         <v>196</v>
       </c>
@@ -5867,8 +7223,20 @@
       <c r="X61" t="s">
         <v>190</v>
       </c>
+      <c r="Y61" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB61" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>88</v>
       </c>
@@ -5923,6 +7291,9 @@
       <c r="S62" t="s">
         <v>191</v>
       </c>
+      <c r="T62" t="s">
+        <v>191</v>
+      </c>
       <c r="U62" t="s">
         <v>186</v>
       </c>
@@ -5935,8 +7306,20 @@
       <c r="X62" t="s">
         <v>186</v>
       </c>
+      <c r="Y62" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB62" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>89</v>
       </c>
@@ -5991,6 +7374,9 @@
       <c r="S63" t="s">
         <v>192</v>
       </c>
+      <c r="T63" t="s">
+        <v>196</v>
+      </c>
       <c r="U63" t="s">
         <v>196</v>
       </c>
@@ -6003,8 +7389,20 @@
       <c r="X63" t="s">
         <v>196</v>
       </c>
+      <c r="Y63" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB63" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>90</v>
       </c>
@@ -6059,6 +7457,9 @@
       <c r="S64" t="s">
         <v>196</v>
       </c>
+      <c r="T64" t="s">
+        <v>196</v>
+      </c>
       <c r="U64" t="s">
         <v>196</v>
       </c>
@@ -6071,8 +7472,20 @@
       <c r="X64" t="s">
         <v>196</v>
       </c>
+      <c r="Y64" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA64" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB64" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>135</v>
       </c>
@@ -6130,6 +7543,9 @@
       <c r="S65" t="s">
         <v>194</v>
       </c>
+      <c r="T65" t="s">
+        <v>194</v>
+      </c>
       <c r="U65" t="s">
         <v>187</v>
       </c>
@@ -6142,8 +7558,20 @@
       <c r="X65" t="s">
         <v>187</v>
       </c>
+      <c r="Y65" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB65" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>353</v>
       </c>
@@ -6195,8 +7623,41 @@
       <c r="Q66" t="s">
         <v>196</v>
       </c>
+      <c r="R66" t="s">
+        <v>196</v>
+      </c>
+      <c r="S66" t="s">
+        <v>184</v>
+      </c>
+      <c r="T66" t="s">
+        <v>487</v>
+      </c>
+      <c r="U66" t="s">
+        <v>196</v>
+      </c>
+      <c r="V66" t="s">
+        <v>354</v>
+      </c>
+      <c r="W66" t="s">
+        <v>196</v>
+      </c>
+      <c r="X66" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB66" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>355</v>
       </c>
@@ -6245,8 +7706,41 @@
       <c r="Q67" t="s">
         <v>196</v>
       </c>
+      <c r="R67" t="s">
+        <v>480</v>
+      </c>
+      <c r="S67" t="s">
+        <v>480</v>
+      </c>
+      <c r="T67" t="s">
+        <v>480</v>
+      </c>
+      <c r="U67" t="s">
+        <v>196</v>
+      </c>
+      <c r="V67" t="s">
+        <v>188</v>
+      </c>
+      <c r="W67" t="s">
+        <v>188</v>
+      </c>
+      <c r="X67" t="s">
+        <v>188</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>188</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>188</v>
+      </c>
+      <c r="AB67" t="s">
+        <v>188</v>
+      </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>356</v>
       </c>
@@ -6292,8 +7786,41 @@
       <c r="Q68" t="s">
         <v>196</v>
       </c>
+      <c r="R68" t="s">
+        <v>196</v>
+      </c>
+      <c r="S68" t="s">
+        <v>490</v>
+      </c>
+      <c r="T68" t="s">
+        <v>490</v>
+      </c>
+      <c r="U68" t="s">
+        <v>196</v>
+      </c>
+      <c r="V68" t="s">
+        <v>196</v>
+      </c>
+      <c r="W68" t="s">
+        <v>196</v>
+      </c>
+      <c r="X68" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA68" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB68" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>357</v>
       </c>
@@ -6345,8 +7872,41 @@
       <c r="Q69" t="s">
         <v>196</v>
       </c>
+      <c r="R69" t="s">
+        <v>196</v>
+      </c>
+      <c r="S69" t="s">
+        <v>481</v>
+      </c>
+      <c r="T69" t="s">
+        <v>491</v>
+      </c>
+      <c r="U69" t="s">
+        <v>196</v>
+      </c>
+      <c r="V69" t="s">
+        <v>358</v>
+      </c>
+      <c r="W69" t="s">
+        <v>192</v>
+      </c>
+      <c r="X69" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>192</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>192</v>
+      </c>
+      <c r="AB69" t="s">
+        <v>192</v>
+      </c>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>359</v>
       </c>
@@ -6395,8 +7955,41 @@
       <c r="Q70" t="s">
         <v>196</v>
       </c>
+      <c r="R70" t="s">
+        <v>196</v>
+      </c>
+      <c r="S70" t="s">
+        <v>482</v>
+      </c>
+      <c r="T70" t="s">
+        <v>489</v>
+      </c>
+      <c r="U70" t="s">
+        <v>196</v>
+      </c>
+      <c r="V70" t="s">
+        <v>360</v>
+      </c>
+      <c r="W70" t="s">
+        <v>497</v>
+      </c>
+      <c r="X70" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>497</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>497</v>
+      </c>
+      <c r="AB70" t="s">
+        <v>497</v>
+      </c>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>370</v>
       </c>
@@ -6444,6 +8037,39 @@
       </c>
       <c r="Q71" t="s">
         <v>196</v>
+      </c>
+      <c r="R71" t="s">
+        <v>196</v>
+      </c>
+      <c r="S71" t="s">
+        <v>483</v>
+      </c>
+      <c r="T71" t="s">
+        <v>488</v>
+      </c>
+      <c r="U71" t="s">
+        <v>196</v>
+      </c>
+      <c r="V71" t="s">
+        <v>371</v>
+      </c>
+      <c r="W71" t="s">
+        <v>486</v>
+      </c>
+      <c r="X71" t="s">
+        <v>486</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>186</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>486</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>486</v>
+      </c>
+      <c r="AB71" t="s">
+        <v>486</v>
       </c>
     </row>
   </sheetData>

--- a/Monadisk overblik.xlsx
+++ b/Monadisk overblik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aaudk-my.sharepoint.com/personal/bo62rk_id_aau_dk/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1914" documentId="8_{6C2A7B69-2C62-4B80-ACF4-E8008D3DDFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F86A2DB0-E533-46FC-A9E2-D9D5B285A0BF}"/>
+  <xr:revisionPtr revIDLastSave="2400" documentId="8_{6C2A7B69-2C62-4B80-ACF4-E8008D3DDFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00946A99-598D-4418-8707-D248334559AF}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{E14E365F-4887-4C07-BAAD-AE51F23AD0DA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E14E365F-4887-4C07-BAAD-AE51F23AD0DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2830" uniqueCount="561">
   <si>
     <t>Corona0</t>
   </si>
@@ -1545,6 +1545,183 @@
   </si>
   <si>
     <t>FT26</t>
+  </si>
+  <si>
+    <t>q25b</t>
+  </si>
+  <si>
+    <t>q1a_1</t>
+  </si>
+  <si>
+    <t>q1a_2</t>
+  </si>
+  <si>
+    <t>q1a_3</t>
+  </si>
+  <si>
+    <t>q1a_5</t>
+  </si>
+  <si>
+    <t>q1a_8</t>
+  </si>
+  <si>
+    <t>q1a_9</t>
+  </si>
+  <si>
+    <t>q1a_10</t>
+  </si>
+  <si>
+    <t>q1a_11</t>
+  </si>
+  <si>
+    <t>q1a_14</t>
+  </si>
+  <si>
+    <t>urabn</t>
+  </si>
+  <si>
+    <t>q35_33</t>
+  </si>
+  <si>
+    <t>q83_1</t>
+  </si>
+  <si>
+    <t>q86a</t>
+  </si>
+  <si>
+    <t>q86b</t>
+  </si>
+  <si>
+    <t>q92</t>
+  </si>
+  <si>
+    <t>q111</t>
+  </si>
+  <si>
+    <t>q112</t>
+  </si>
+  <si>
+    <t>FT11</t>
+  </si>
+  <si>
+    <t>FT_15</t>
+  </si>
+  <si>
+    <t>q83e_1</t>
+  </si>
+  <si>
+    <t>S11Bgender</t>
+  </si>
+  <si>
+    <t>S11Bage</t>
+  </si>
+  <si>
+    <t>S11Bq25</t>
+  </si>
+  <si>
+    <t>S11Bq24_2</t>
+  </si>
+  <si>
+    <t>S11Bq37</t>
+  </si>
+  <si>
+    <t>S11Bq64</t>
+  </si>
+  <si>
+    <t>S11Bq67</t>
+  </si>
+  <si>
+    <t>S11Bq69</t>
+  </si>
+  <si>
+    <t>S11Bq71</t>
+  </si>
+  <si>
+    <t>S11Bq74</t>
+  </si>
+  <si>
+    <t>q6_5</t>
+  </si>
+  <si>
+    <t>q21b</t>
+  </si>
+  <si>
+    <t>q33a</t>
+  </si>
+  <si>
+    <t>q41a</t>
+  </si>
+  <si>
+    <t>q41c</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>HI</t>
+  </si>
+  <si>
+    <t>profile_education_recoded</t>
+  </si>
+  <si>
+    <t>q2_recoded</t>
+  </si>
+  <si>
+    <t>q23a_1</t>
+  </si>
+  <si>
+    <t>q26</t>
+  </si>
+  <si>
+    <t>Q1b</t>
+  </si>
+  <si>
+    <t>q17a + q17b</t>
+  </si>
+  <si>
+    <t>Q26_1</t>
+  </si>
+  <si>
+    <t>Q26_6</t>
+  </si>
+  <si>
+    <t>Q26_2</t>
+  </si>
+  <si>
+    <t>Q26_4a</t>
+  </si>
+  <si>
+    <t>Q26_4b</t>
+  </si>
+  <si>
+    <t>Q60_4</t>
+  </si>
+  <si>
+    <t>Q60_6</t>
+  </si>
+  <si>
+    <t>Q60_5</t>
+  </si>
+  <si>
+    <t>Q60_2</t>
+  </si>
+  <si>
+    <t>Q60_3</t>
+  </si>
+  <si>
+    <t>Q60_1</t>
+  </si>
+  <si>
+    <t>Q60_7</t>
+  </si>
+  <si>
+    <t>Q60_8</t>
+  </si>
+  <si>
+    <t>Q60_9</t>
+  </si>
+  <si>
+    <t>Q14a_7</t>
   </si>
 </sst>
 </file>
@@ -2188,6 +2365,45 @@
       <c r="AB2" t="s">
         <v>91</v>
       </c>
+      <c r="AC2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>523</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -2274,6 +2490,45 @@
       <c r="AB3" t="s">
         <v>92</v>
       </c>
+      <c r="AC3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>524</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -2360,6 +2615,39 @@
       <c r="AB4" t="s">
         <v>343</v>
       </c>
+      <c r="AC4" t="s">
+        <v>343</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>343</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>343</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>343</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>343</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>540</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>343</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>343</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>470</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -2446,6 +2734,42 @@
       <c r="AB5" t="s">
         <v>344</v>
       </c>
+      <c r="AC5" t="s">
+        <v>344</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>344</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>344</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>344</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>529</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>536</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>344</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>517</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>517</v>
+      </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -2532,6 +2856,42 @@
       <c r="AB6" t="s">
         <v>196</v>
       </c>
+      <c r="AC6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>530</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>537</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>351</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -2618,6 +2978,42 @@
       <c r="AB7" t="s">
         <v>345</v>
       </c>
+      <c r="AC7" t="s">
+        <v>345</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>345</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>345</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>345</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>345</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>345</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>345</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>345</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>345</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>345</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -2701,6 +3097,42 @@
       <c r="AB8" t="s">
         <v>196</v>
       </c>
+      <c r="AC8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>512</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>528</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>478</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>544</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -2787,6 +3219,42 @@
       <c r="AB9" t="s">
         <v>374</v>
       </c>
+      <c r="AC9" t="s">
+        <v>374</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>374</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>374</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>531</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>538</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>374</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>374</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>518</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -2873,6 +3341,42 @@
       <c r="AB10" t="s">
         <v>196</v>
       </c>
+      <c r="AC10" t="s">
+        <v>322</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>373</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>322</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>322</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>532</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>539</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>373</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>373</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>519</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>519</v>
+      </c>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -2959,6 +3463,42 @@
       <c r="AB11" t="s">
         <v>501</v>
       </c>
+      <c r="AC11" t="s">
+        <v>494</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>484</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>484</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>494</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>472</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>541</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>494</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>501</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>520</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -3045,6 +3585,42 @@
       <c r="AB12" t="s">
         <v>495</v>
       </c>
+      <c r="AC12" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>495</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>495</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>495</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>495</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>495</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>495</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>495</v>
+      </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -3131,6 +3707,42 @@
       <c r="AB13" t="s">
         <v>196</v>
       </c>
+      <c r="AC13" t="s">
+        <v>502</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>535</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>320</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>515</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>515</v>
+      </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -3217,6 +3829,45 @@
       <c r="AB14" t="s">
         <v>496</v>
       </c>
+      <c r="AC14" t="s">
+        <v>300</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>472</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>372</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>300</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>302</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>516</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -3303,11 +3954,41 @@
       <c r="AB15" t="s">
         <v>326</v>
       </c>
+      <c r="AC15" t="s">
+        <v>196</v>
+      </c>
       <c r="AE15" t="s">
         <v>326</v>
       </c>
       <c r="AF15" t="s">
         <v>326</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>527</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>318</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>326</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>545</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
@@ -3395,8 +4076,44 @@
       <c r="AB16" t="s">
         <v>196</v>
       </c>
+      <c r="AC16" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>361</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>361</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>361</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>551</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>55</v>
       </c>
@@ -3481,8 +4198,44 @@
       <c r="AB17" t="s">
         <v>196</v>
       </c>
+      <c r="AC17" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>362</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>362</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>362</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>362</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>552</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
@@ -3567,8 +4320,44 @@
       <c r="AB18" t="s">
         <v>196</v>
       </c>
+      <c r="AC18" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>363</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>363</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>363</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>363</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>553</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>57</v>
       </c>
@@ -3653,8 +4442,44 @@
       <c r="AB19" t="s">
         <v>196</v>
       </c>
+      <c r="AC19" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>364</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>364</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>364</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>364</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
@@ -3739,8 +4564,44 @@
       <c r="AB20" t="s">
         <v>196</v>
       </c>
+      <c r="AC20" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>365</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>365</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>365</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>365</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>555</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>59</v>
       </c>
@@ -3825,8 +4686,44 @@
       <c r="AB21" t="s">
         <v>196</v>
       </c>
+      <c r="AC21" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>366</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>366</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>366</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>366</v>
+      </c>
+      <c r="AM21" t="s">
+        <v>556</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>60</v>
       </c>
@@ -3911,8 +4808,44 @@
       <c r="AB22" t="s">
         <v>196</v>
       </c>
+      <c r="AC22" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>367</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>367</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>367</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>367</v>
+      </c>
+      <c r="AM22" t="s">
+        <v>557</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO22" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
@@ -3997,8 +4930,44 @@
       <c r="AB23" s="3" t="s">
         <v>196</v>
       </c>
+      <c r="AC23" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM23" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>62</v>
       </c>
@@ -4083,8 +5052,44 @@
       <c r="AB24" t="s">
         <v>196</v>
       </c>
+      <c r="AC24" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>368</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>368</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>368</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>368</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>558</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>63</v>
       </c>
@@ -4169,8 +5174,44 @@
       <c r="AB25" t="s">
         <v>196</v>
       </c>
+      <c r="AC25" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>369</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>369</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>369</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>369</v>
+      </c>
+      <c r="AM25" t="s">
+        <v>559</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO25" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>64</v>
       </c>
@@ -4255,6 +5296,9 @@
       <c r="AB26" t="s">
         <v>196</v>
       </c>
+      <c r="AC26" t="s">
+        <v>196</v>
+      </c>
       <c r="AE26" t="s">
         <v>328</v>
       </c>
@@ -4264,8 +5308,32 @@
       <c r="AG26" t="s">
         <v>328</v>
       </c>
+      <c r="AH26" t="s">
+        <v>526</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>533</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>542</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>560</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>514</v>
+      </c>
+      <c r="AO26" t="s">
+        <v>522</v>
+      </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>65</v>
       </c>
@@ -4350,8 +5418,44 @@
       <c r="AB27" t="s">
         <v>196</v>
       </c>
+      <c r="AC27" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>525</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>534</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>249</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>543</v>
+      </c>
+      <c r="AM27" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO27" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>303</v>
       </c>
@@ -4436,8 +5540,47 @@
       <c r="AB28" t="s">
         <v>318</v>
       </c>
+      <c r="AC28" t="s">
+        <v>318</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>475</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>318</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>318</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>318</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>320</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM28" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO28" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>66</v>
       </c>
@@ -4522,8 +5665,44 @@
       <c r="AB29" t="s">
         <v>196</v>
       </c>
+      <c r="AC29" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG29" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM29" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO29" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>71</v>
       </c>
@@ -4608,8 +5787,47 @@
       <c r="AB30" t="s">
         <v>268</v>
       </c>
+      <c r="AC30" t="s">
+        <v>196</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>507</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>266</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>268</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>268</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM30" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO30" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>68</v>
       </c>
@@ -4694,8 +5912,47 @@
       <c r="AB31" t="s">
         <v>264</v>
       </c>
+      <c r="AC31" t="s">
+        <v>264</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>503</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>264</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>264</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>264</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM31" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO31" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>70</v>
       </c>
@@ -4777,8 +6034,44 @@
       <c r="AB32" t="s">
         <v>196</v>
       </c>
+      <c r="AC32" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM32" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO32" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>67</v>
       </c>
@@ -4863,8 +6156,44 @@
       <c r="AB33" t="s">
         <v>196</v>
       </c>
+      <c r="AC33" t="s">
+        <v>263</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>263</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>263</v>
+      </c>
+      <c r="AG33" t="s">
+        <v>263</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>263</v>
+      </c>
+      <c r="AM33" t="s">
+        <v>546</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO33" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>69</v>
       </c>
@@ -4949,8 +6278,47 @@
       <c r="AB34" t="s">
         <v>265</v>
       </c>
+      <c r="AC34" t="s">
+        <v>265</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>504</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>265</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>265</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>265</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>264</v>
+      </c>
+      <c r="AM34" t="s">
+        <v>548</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO34" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>72</v>
       </c>
@@ -5032,8 +6400,44 @@
       <c r="AB35" t="s">
         <v>196</v>
       </c>
+      <c r="AC35" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE35" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF35" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG35" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM35" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO35" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>73</v>
       </c>
@@ -5118,8 +6522,47 @@
       <c r="AB36" t="s">
         <v>196</v>
       </c>
+      <c r="AC36" t="s">
+        <v>266</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>506</v>
+      </c>
+      <c r="AE36" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF36" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG36" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM36" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO36" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>74</v>
       </c>
@@ -5201,8 +6644,47 @@
       <c r="AB37" t="s">
         <v>196</v>
       </c>
+      <c r="AC37" t="s">
+        <v>196</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>505</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>281</v>
+      </c>
+      <c r="AF37" t="s">
+        <v>266</v>
+      </c>
+      <c r="AG37" t="s">
+        <v>266</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL37" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM37" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO37" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
@@ -5287,8 +6769,44 @@
       <c r="AB38" t="s">
         <v>196</v>
       </c>
+      <c r="AC38" t="s">
+        <v>281</v>
+      </c>
+      <c r="AE38" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG38" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL38" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM38" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO38" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>76</v>
       </c>
@@ -5370,8 +6888,44 @@
       <c r="AB39" t="s">
         <v>196</v>
       </c>
+      <c r="AC39" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE39" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK39" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM39" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO39" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>218</v>
       </c>
@@ -5456,8 +7010,47 @@
       <c r="AB40" t="s">
         <v>196</v>
       </c>
+      <c r="AC40" t="s">
+        <v>268</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>508</v>
+      </c>
+      <c r="AE40" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF40" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG40" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ40" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK40" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL40" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM40" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO40" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>219</v>
       </c>
@@ -5539,8 +7132,44 @@
       <c r="AB41" t="s">
         <v>196</v>
       </c>
+      <c r="AC41" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE41" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF41" t="s">
+        <v>513</v>
+      </c>
+      <c r="AG41" t="s">
+        <v>513</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ41" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK41" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL41" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM41" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN41" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO41" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>220</v>
       </c>
@@ -5622,8 +7251,44 @@
       <c r="AB42" t="s">
         <v>196</v>
       </c>
+      <c r="AC42" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE42" t="s">
+        <v>298</v>
+      </c>
+      <c r="AF42" t="s">
+        <v>298</v>
+      </c>
+      <c r="AG42" t="s">
+        <v>298</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ42" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK42" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL42" t="s">
+        <v>270</v>
+      </c>
+      <c r="AM42" t="s">
+        <v>547</v>
+      </c>
+      <c r="AN42" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO42" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>232</v>
       </c>
@@ -5705,8 +7370,47 @@
       <c r="AB43" t="s">
         <v>196</v>
       </c>
+      <c r="AC43" t="s">
+        <v>196</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>509</v>
+      </c>
+      <c r="AE43" t="s">
+        <v>299</v>
+      </c>
+      <c r="AF43" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG43" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH43" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI43" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ43" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK43" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL43" t="s">
+        <v>269</v>
+      </c>
+      <c r="AM43" t="s">
+        <v>549</v>
+      </c>
+      <c r="AN43" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO43" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>221</v>
       </c>
@@ -5791,8 +7495,44 @@
       <c r="AB44" t="s">
         <v>271</v>
       </c>
+      <c r="AC44" t="s">
+        <v>270</v>
+      </c>
+      <c r="AE44" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF44" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG44" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH44" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI44" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ44" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK44" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL44" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AN44" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO44" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>222</v>
       </c>
@@ -5877,8 +7617,47 @@
       <c r="AB45" t="s">
         <v>196</v>
       </c>
+      <c r="AC45" t="s">
+        <v>280</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>510</v>
+      </c>
+      <c r="AE45" t="s">
+        <v>282</v>
+      </c>
+      <c r="AF45" t="s">
+        <v>282</v>
+      </c>
+      <c r="AG45" t="s">
+        <v>282</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ45" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK45" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM45" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN45" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO45" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>223</v>
       </c>
@@ -5963,8 +7742,44 @@
       <c r="AB46" t="s">
         <v>196</v>
       </c>
+      <c r="AC46" t="s">
+        <v>271</v>
+      </c>
+      <c r="AE46" t="s">
+        <v>272</v>
+      </c>
+      <c r="AF46" t="s">
+        <v>272</v>
+      </c>
+      <c r="AG46" t="s">
+        <v>272</v>
+      </c>
+      <c r="AH46" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI46" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ46" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK46" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL46" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM46" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN46" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO46" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>224</v>
       </c>
@@ -6049,8 +7864,44 @@
       <c r="AB47" t="s">
         <v>196</v>
       </c>
+      <c r="AC47" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE47" t="s">
+        <v>273</v>
+      </c>
+      <c r="AF47" t="s">
+        <v>273</v>
+      </c>
+      <c r="AG47" t="s">
+        <v>273</v>
+      </c>
+      <c r="AH47" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI47" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK47" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL47" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM47" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN47" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO47" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>225</v>
       </c>
@@ -6135,8 +7986,44 @@
       <c r="AB48" t="s">
         <v>196</v>
       </c>
+      <c r="AC48" t="s">
+        <v>282</v>
+      </c>
+      <c r="AE48" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF48" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG48" t="s">
+        <v>276</v>
+      </c>
+      <c r="AH48" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ48" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK48" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL48" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM48" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN48" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO48" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>226</v>
       </c>
@@ -6218,8 +8105,47 @@
       <c r="AB49" t="s">
         <v>277</v>
       </c>
+      <c r="AC49" t="s">
+        <v>196</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>511</v>
+      </c>
+      <c r="AE49" t="s">
+        <v>277</v>
+      </c>
+      <c r="AF49" t="s">
+        <v>277</v>
+      </c>
+      <c r="AG49" t="s">
+        <v>277</v>
+      </c>
+      <c r="AH49" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI49" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ49" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK49" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL49" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM49" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN49" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO49" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>227</v>
       </c>
@@ -6304,8 +8230,44 @@
       <c r="AB50" t="s">
         <v>196</v>
       </c>
+      <c r="AC50" t="s">
+        <v>269</v>
+      </c>
+      <c r="AE50" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF50" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG50" t="s">
+        <v>270</v>
+      </c>
+      <c r="AH50" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI50" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ50" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK50" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL50" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM50" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO50" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>77</v>
       </c>
@@ -6390,8 +8352,44 @@
       <c r="AB51" t="s">
         <v>181</v>
       </c>
+      <c r="AC51" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>181</v>
+      </c>
+      <c r="AF51" t="s">
+        <v>181</v>
+      </c>
+      <c r="AG51" t="s">
+        <v>181</v>
+      </c>
+      <c r="AH51" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI51" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ51" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK51" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL51" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM51" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN51" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO51" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>78</v>
       </c>
@@ -6473,8 +8471,44 @@
       <c r="AB52" t="s">
         <v>196</v>
       </c>
+      <c r="AC52" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE52" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF52" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG52" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH52" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI52" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ52" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK52" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL52" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM52" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN52" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO52" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>79</v>
       </c>
@@ -6559,8 +8593,44 @@
       <c r="AB53" t="s">
         <v>196</v>
       </c>
+      <c r="AC53" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>182</v>
+      </c>
+      <c r="AF53" t="s">
+        <v>182</v>
+      </c>
+      <c r="AG53" t="s">
+        <v>182</v>
+      </c>
+      <c r="AH53" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI53" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ53" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK53" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL53" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM53" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN53" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO53" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>80</v>
       </c>
@@ -6642,8 +8712,44 @@
       <c r="AB54" t="s">
         <v>196</v>
       </c>
+      <c r="AC54" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE54" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF54" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG54" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH54" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI54" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ54" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK54" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL54" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM54" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN54" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO54" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>81</v>
       </c>
@@ -6728,8 +8834,44 @@
       <c r="AB55" t="s">
         <v>196</v>
       </c>
+      <c r="AC55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE55" t="s">
+        <v>183</v>
+      </c>
+      <c r="AF55" t="s">
+        <v>183</v>
+      </c>
+      <c r="AG55" t="s">
+        <v>183</v>
+      </c>
+      <c r="AH55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL55" t="s">
+        <v>280</v>
+      </c>
+      <c r="AM55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO55" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>82</v>
       </c>
@@ -6811,8 +8953,44 @@
       <c r="AB56" t="s">
         <v>196</v>
       </c>
+      <c r="AC56" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE56" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF56" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG56" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH56" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI56" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ56" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK56" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL56" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM56" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN56" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO56" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>83</v>
       </c>
@@ -6897,8 +9075,44 @@
       <c r="AB57" t="s">
         <v>184</v>
       </c>
+      <c r="AC57" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE57" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF57" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG57" t="s">
+        <v>184</v>
+      </c>
+      <c r="AH57" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI57" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ57" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK57" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL57" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM57" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN57" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO57" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>84</v>
       </c>
@@ -6980,8 +9194,44 @@
       <c r="AB58" t="s">
         <v>196</v>
       </c>
+      <c r="AC58" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE58" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF58" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG58" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH58" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI58" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ58" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK58" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL58" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM58" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN58" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO58" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>85</v>
       </c>
@@ -7066,8 +9316,44 @@
       <c r="AB59" t="s">
         <v>196</v>
       </c>
+      <c r="AC59" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE59" t="s">
+        <v>193</v>
+      </c>
+      <c r="AF59" t="s">
+        <v>193</v>
+      </c>
+      <c r="AG59" t="s">
+        <v>193</v>
+      </c>
+      <c r="AH59" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI59" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ59" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK59" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL59" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM59" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN59" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO59" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>86</v>
       </c>
@@ -7152,8 +9438,44 @@
       <c r="AB60" t="s">
         <v>185</v>
       </c>
+      <c r="AC60" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE60" t="s">
+        <v>185</v>
+      </c>
+      <c r="AF60" t="s">
+        <v>185</v>
+      </c>
+      <c r="AG60" t="s">
+        <v>185</v>
+      </c>
+      <c r="AH60" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI60" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ60" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK60" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL60" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM60" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN60" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO60" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>87</v>
       </c>
@@ -7235,8 +9557,44 @@
       <c r="AB61" t="s">
         <v>196</v>
       </c>
+      <c r="AC61" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE61" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF61" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG61" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH61" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI61" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ61" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK61" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL61" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM61" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN61" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO61" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>88</v>
       </c>
@@ -7318,8 +9676,44 @@
       <c r="AB62" t="s">
         <v>196</v>
       </c>
+      <c r="AC62" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE62" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF62" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG62" t="s">
+        <v>186</v>
+      </c>
+      <c r="AH62" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI62" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ62" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK62" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL62" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM62" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN62" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO62" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>89</v>
       </c>
@@ -7401,8 +9795,44 @@
       <c r="AB63" t="s">
         <v>196</v>
       </c>
+      <c r="AC63" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE63" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF63" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG63" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH63" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI63" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ63" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK63" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL63" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM63" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN63" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO63" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>90</v>
       </c>
@@ -7484,8 +9914,44 @@
       <c r="AB64" t="s">
         <v>196</v>
       </c>
+      <c r="AC64" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE64" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF64" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG64" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH64" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI64" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ64" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK64" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL64" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM64" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN64" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO64" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>135</v>
       </c>
@@ -7570,8 +10036,44 @@
       <c r="AB65" t="s">
         <v>196</v>
       </c>
+      <c r="AC65" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE65" t="s">
+        <v>187</v>
+      </c>
+      <c r="AF65" t="s">
+        <v>187</v>
+      </c>
+      <c r="AG65" t="s">
+        <v>187</v>
+      </c>
+      <c r="AH65" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI65" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ65" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK65" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL65" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM65" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN65" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO65" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>353</v>
       </c>
@@ -7656,8 +10158,44 @@
       <c r="AB66" t="s">
         <v>196</v>
       </c>
+      <c r="AC66" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE66" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF66" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG66" t="s">
+        <v>354</v>
+      </c>
+      <c r="AH66" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI66" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ66" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK66" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL66" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM66" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN66" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO66" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>355</v>
       </c>
@@ -7739,8 +10277,44 @@
       <c r="AB67" t="s">
         <v>188</v>
       </c>
+      <c r="AC67" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE67" t="s">
+        <v>188</v>
+      </c>
+      <c r="AF67" t="s">
+        <v>188</v>
+      </c>
+      <c r="AG67" t="s">
+        <v>188</v>
+      </c>
+      <c r="AH67" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI67" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ67" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK67" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL67" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM67" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN67" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO67" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>356</v>
       </c>
@@ -7819,8 +10393,44 @@
       <c r="AB68" t="s">
         <v>196</v>
       </c>
+      <c r="AC68" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE68" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF68" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG68" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH68" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI68" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ68" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK68" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL68" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM68" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN68" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO68" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>357</v>
       </c>
@@ -7905,8 +10515,44 @@
       <c r="AB69" t="s">
         <v>192</v>
       </c>
+      <c r="AC69" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE69" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF69" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG69" t="s">
+        <v>358</v>
+      </c>
+      <c r="AH69" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI69" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ69" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK69" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL69" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM69" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN69" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO69" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>359</v>
       </c>
@@ -7988,8 +10634,44 @@
       <c r="AB70" t="s">
         <v>497</v>
       </c>
+      <c r="AC70" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE70" t="s">
+        <v>360</v>
+      </c>
+      <c r="AF70" t="s">
+        <v>360</v>
+      </c>
+      <c r="AG70" t="s">
+        <v>360</v>
+      </c>
+      <c r="AH70" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI70" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ70" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK70" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL70" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM70" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN70" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>370</v>
       </c>
@@ -8070,6 +10752,42 @@
       </c>
       <c r="AB71" t="s">
         <v>486</v>
+      </c>
+      <c r="AC71" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE71" t="s">
+        <v>371</v>
+      </c>
+      <c r="AF71" t="s">
+        <v>371</v>
+      </c>
+      <c r="AG71" t="s">
+        <v>371</v>
+      </c>
+      <c r="AH71" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI71" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ71" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK71" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL71" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM71" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN71" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO71" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
